--- a/artfynd/A 10151-2023 artfynd.xlsx
+++ b/artfynd/A 10151-2023 artfynd.xlsx
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118001734</v>
+        <v>118001697</v>
       </c>
       <c r="B9" t="n">
-        <v>91772</v>
+        <v>78217</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>811036</v>
+        <v>811173</v>
       </c>
       <c r="R9" t="n">
-        <v>7391915</v>
+        <v>7391869</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118001720</v>
+        <v>118001734</v>
       </c>
       <c r="B10" t="n">
         <v>91772</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>810930</v>
+        <v>811036</v>
       </c>
       <c r="R10" t="n">
-        <v>7392068</v>
+        <v>7391915</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118001732</v>
+        <v>118001720</v>
       </c>
       <c r="B11" t="n">
         <v>91772</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>811045</v>
+        <v>810930</v>
       </c>
       <c r="R11" t="n">
-        <v>7391904</v>
+        <v>7392068</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118001697</v>
+        <v>118001732</v>
       </c>
       <c r="B12" t="n">
-        <v>78217</v>
+        <v>91772</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1707,25 +1707,25 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>811173</v>
+        <v>811045</v>
       </c>
       <c r="R12" t="n">
-        <v>7391869</v>
+        <v>7391904</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118001657</v>
+        <v>118001740</v>
       </c>
       <c r="B13" t="n">
-        <v>79098</v>
+        <v>91772</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>811173</v>
+        <v>811002</v>
       </c>
       <c r="R13" t="n">
-        <v>7391869</v>
+        <v>7391962</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118001702</v>
+        <v>118001671</v>
       </c>
       <c r="B14" t="n">
-        <v>78216</v>
+        <v>56499</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>810955</v>
+        <v>811031</v>
       </c>
       <c r="R14" t="n">
-        <v>7392254</v>
+        <v>7392108</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1969,12 +1969,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -1983,7 +1983,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2002,10 +2001,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118001701</v>
+        <v>118001657</v>
       </c>
       <c r="B15" t="n">
-        <v>78217</v>
+        <v>79098</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,21 +2017,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2042,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>811130</v>
+        <v>811173</v>
       </c>
       <c r="R15" t="n">
-        <v>7391886</v>
+        <v>7391869</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2104,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118001740</v>
+        <v>118001702</v>
       </c>
       <c r="B16" t="n">
-        <v>91772</v>
+        <v>78216</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2116,25 +2115,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2144,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>811002</v>
+        <v>810955</v>
       </c>
       <c r="R16" t="n">
-        <v>7391962</v>
+        <v>7392254</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2174,12 +2173,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2188,6 +2187,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2206,10 +2206,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118001671</v>
+        <v>118001701</v>
       </c>
       <c r="B17" t="n">
-        <v>56499</v>
+        <v>78217</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2218,25 +2218,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2246,10 +2246,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>811031</v>
+        <v>811130</v>
       </c>
       <c r="R17" t="n">
-        <v>7392108</v>
+        <v>7391886</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2308,10 +2308,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118001715</v>
+        <v>118001696</v>
       </c>
       <c r="B18" t="n">
-        <v>78480</v>
+        <v>78217</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2324,21 +2324,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>810963</v>
+        <v>811066</v>
       </c>
       <c r="R18" t="n">
-        <v>7392266</v>
+        <v>7392110</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2378,12 +2378,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2410,10 +2410,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118001703</v>
+        <v>118001722</v>
       </c>
       <c r="B19" t="n">
-        <v>78216</v>
+        <v>91772</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2422,25 +2422,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>811172</v>
+        <v>811018</v>
       </c>
       <c r="R19" t="n">
-        <v>7391893</v>
+        <v>7392104</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2512,10 +2512,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118001722</v>
+        <v>118001703</v>
       </c>
       <c r="B20" t="n">
-        <v>91772</v>
+        <v>78216</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2524,25 +2524,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2552,10 +2552,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>811018</v>
+        <v>811172</v>
       </c>
       <c r="R20" t="n">
-        <v>7392104</v>
+        <v>7391893</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2614,10 +2614,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118001696</v>
+        <v>118001715</v>
       </c>
       <c r="B21" t="n">
-        <v>78217</v>
+        <v>78480</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2630,21 +2630,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>811066</v>
+        <v>810963</v>
       </c>
       <c r="R21" t="n">
-        <v>7392110</v>
+        <v>7392266</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2684,12 +2684,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4044,10 +4044,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118001726</v>
+        <v>118001660</v>
       </c>
       <c r="B35" t="n">
-        <v>91772</v>
+        <v>79069</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4056,25 +4056,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4084,10 +4084,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>811225</v>
+        <v>811143</v>
       </c>
       <c r="R35" t="n">
-        <v>7391922</v>
+        <v>7391831</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4128,6 +4128,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4146,10 +4147,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118001660</v>
+        <v>118001726</v>
       </c>
       <c r="B36" t="n">
-        <v>79069</v>
+        <v>91772</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4158,25 +4159,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4186,10 +4187,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>811143</v>
+        <v>811225</v>
       </c>
       <c r="R36" t="n">
-        <v>7391831</v>
+        <v>7391922</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4230,7 +4231,6 @@
       <c r="AE36" t="b">
         <v>0</v>
       </c>
-      <c r="AF36" t="inlineStr"/>
       <c r="AG36" t="b">
         <v>0</v>
       </c>
@@ -4249,10 +4249,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118001742</v>
+        <v>118001667</v>
       </c>
       <c r="B37" t="n">
-        <v>91772</v>
+        <v>56499</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4265,21 +4265,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4289,10 +4289,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>810927</v>
+        <v>810924</v>
       </c>
       <c r="R37" t="n">
-        <v>7392000</v>
+        <v>7392048</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4351,7 +4351,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118001723</v>
+        <v>118001742</v>
       </c>
       <c r="B38" t="n">
         <v>91772</v>
@@ -4391,10 +4391,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>811070</v>
+        <v>810927</v>
       </c>
       <c r="R38" t="n">
-        <v>7392098</v>
+        <v>7392000</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4453,10 +4453,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118001707</v>
+        <v>118001723</v>
       </c>
       <c r="B39" t="n">
-        <v>90648</v>
+        <v>91772</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4465,25 +4465,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4493,10 +4493,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>811003</v>
+        <v>811070</v>
       </c>
       <c r="R39" t="n">
-        <v>7392144</v>
+        <v>7392098</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4555,10 +4555,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118001667</v>
+        <v>118001707</v>
       </c>
       <c r="B40" t="n">
-        <v>56499</v>
+        <v>90648</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4567,25 +4567,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>1503</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4595,10 +4595,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>810924</v>
+        <v>811003</v>
       </c>
       <c r="R40" t="n">
-        <v>7392048</v>
+        <v>7392144</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5371,10 +5371,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118001673</v>
+        <v>118001688</v>
       </c>
       <c r="B48" t="n">
-        <v>56499</v>
+        <v>57303</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5383,25 +5383,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>811199</v>
+        <v>811140</v>
       </c>
       <c r="R48" t="n">
-        <v>7392042</v>
+        <v>7391852</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5473,10 +5473,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118001688</v>
+        <v>118001673</v>
       </c>
       <c r="B49" t="n">
-        <v>57303</v>
+        <v>56499</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5485,25 +5485,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5513,10 +5513,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>811140</v>
+        <v>811199</v>
       </c>
       <c r="R49" t="n">
-        <v>7391852</v>
+        <v>7392042</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>

--- a/artfynd/A 10151-2023 artfynd.xlsx
+++ b/artfynd/A 10151-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118001655</v>
+        <v>118001726</v>
       </c>
       <c r="B2" t="n">
-        <v>90464</v>
+        <v>91772</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>811144</v>
+        <v>811225</v>
       </c>
       <c r="R2" t="n">
-        <v>7392075</v>
+        <v>7391922</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118001730</v>
+        <v>118001724</v>
       </c>
       <c r="B3" t="n">
         <v>91772</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>811121</v>
+        <v>811089</v>
       </c>
       <c r="R3" t="n">
-        <v>7391868</v>
+        <v>7392114</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118001728</v>
+        <v>118001735</v>
       </c>
       <c r="B4" t="n">
         <v>91772</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>811172</v>
+        <v>811027</v>
       </c>
       <c r="R4" t="n">
-        <v>7391877</v>
+        <v>7391926</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118001729</v>
+        <v>118001709</v>
       </c>
       <c r="B5" t="n">
-        <v>91772</v>
+        <v>78480</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>811131</v>
+        <v>811212</v>
       </c>
       <c r="R5" t="n">
-        <v>7391868</v>
+        <v>7392000</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118001731</v>
+        <v>118001713</v>
       </c>
       <c r="B6" t="n">
-        <v>91772</v>
+        <v>78480</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>811065</v>
+        <v>810957</v>
       </c>
       <c r="R6" t="n">
-        <v>7391924</v>
+        <v>7391966</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118001704</v>
+        <v>118001670</v>
       </c>
       <c r="B7" t="n">
-        <v>78216</v>
+        <v>56499</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>810991</v>
+        <v>811014</v>
       </c>
       <c r="R7" t="n">
-        <v>7391920</v>
+        <v>7392111</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118001675</v>
+        <v>118001672</v>
       </c>
       <c r="B8" t="n">
         <v>56499</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>811203</v>
+        <v>811166</v>
       </c>
       <c r="R8" t="n">
-        <v>7391977</v>
+        <v>7392067</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118001697</v>
+        <v>118001723</v>
       </c>
       <c r="B9" t="n">
-        <v>78217</v>
+        <v>91772</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>811173</v>
+        <v>811070</v>
       </c>
       <c r="R9" t="n">
-        <v>7391869</v>
+        <v>7392098</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118001734</v>
+        <v>118001741</v>
       </c>
       <c r="B10" t="n">
         <v>91772</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>811036</v>
+        <v>810985</v>
       </c>
       <c r="R10" t="n">
-        <v>7391915</v>
+        <v>7391966</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118001720</v>
+        <v>118001667</v>
       </c>
       <c r="B11" t="n">
-        <v>91772</v>
+        <v>56499</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>810930</v>
+        <v>810924</v>
       </c>
       <c r="R11" t="n">
-        <v>7392068</v>
+        <v>7392048</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1695,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118001732</v>
+        <v>118001675</v>
       </c>
       <c r="B12" t="n">
-        <v>91772</v>
+        <v>56499</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1711,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>811045</v>
+        <v>811203</v>
       </c>
       <c r="R12" t="n">
-        <v>7391904</v>
+        <v>7391977</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1797,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118001740</v>
+        <v>118001664</v>
       </c>
       <c r="B13" t="n">
-        <v>91772</v>
+        <v>89570</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1809,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>811002</v>
+        <v>811168</v>
       </c>
       <c r="R13" t="n">
-        <v>7391962</v>
+        <v>7392005</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118001671</v>
+        <v>118001661</v>
       </c>
       <c r="B14" t="n">
-        <v>56499</v>
+        <v>79069</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1911,25 +1911,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>811031</v>
+        <v>811038</v>
       </c>
       <c r="R14" t="n">
-        <v>7392108</v>
+        <v>7391924</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1983,6 +1983,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2001,10 +2002,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118001657</v>
+        <v>118001697</v>
       </c>
       <c r="B15" t="n">
-        <v>79098</v>
+        <v>78217</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2017,21 +2018,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2103,10 +2104,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118001702</v>
+        <v>118001721</v>
       </c>
       <c r="B16" t="n">
-        <v>78216</v>
+        <v>91772</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2115,25 +2116,25 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2144,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>810955</v>
+        <v>810982</v>
       </c>
       <c r="R16" t="n">
-        <v>7392254</v>
+        <v>7392103</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2173,12 +2174,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2187,7 +2188,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2206,10 +2206,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118001701</v>
+        <v>118001679</v>
       </c>
       <c r="B17" t="n">
-        <v>78217</v>
+        <v>56499</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2218,25 +2218,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2246,10 +2246,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>811130</v>
+        <v>811070</v>
       </c>
       <c r="R17" t="n">
-        <v>7391886</v>
+        <v>7391883</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2308,10 +2308,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118001696</v>
+        <v>118001717</v>
       </c>
       <c r="B18" t="n">
-        <v>78217</v>
+        <v>90743</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2320,25 +2320,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>65</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2348,10 +2348,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>811066</v>
+        <v>810965</v>
       </c>
       <c r="R18" t="n">
-        <v>7392110</v>
+        <v>7391976</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2410,7 +2410,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118001722</v>
+        <v>118001729</v>
       </c>
       <c r="B19" t="n">
         <v>91772</v>
@@ -2450,10 +2450,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>811018</v>
+        <v>811131</v>
       </c>
       <c r="R19" t="n">
-        <v>7392104</v>
+        <v>7391868</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2512,10 +2512,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118001703</v>
+        <v>118001658</v>
       </c>
       <c r="B20" t="n">
-        <v>78216</v>
+        <v>79098</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2528,21 +2528,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2614,10 +2614,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118001715</v>
+        <v>118001669</v>
       </c>
       <c r="B21" t="n">
-        <v>78480</v>
+        <v>56499</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2626,25 +2626,25 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2654,10 +2654,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>810963</v>
+        <v>811004</v>
       </c>
       <c r="R21" t="n">
-        <v>7392266</v>
+        <v>7392125</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2684,12 +2684,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2716,10 +2716,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118001664</v>
+        <v>118001676</v>
       </c>
       <c r="B22" t="n">
-        <v>89570</v>
+        <v>56499</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2728,25 +2728,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1962</v>
+        <v>100138</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2756,10 +2756,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>811168</v>
+        <v>811223</v>
       </c>
       <c r="R22" t="n">
-        <v>7392005</v>
+        <v>7391913</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2818,10 +2818,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118001741</v>
+        <v>118001690</v>
       </c>
       <c r="B23" t="n">
-        <v>91772</v>
+        <v>57303</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2830,25 +2830,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>810985</v>
+        <v>811118</v>
       </c>
       <c r="R23" t="n">
-        <v>7391966</v>
+        <v>7391876</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2920,10 +2920,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118001672</v>
+        <v>118001696</v>
       </c>
       <c r="B24" t="n">
-        <v>56499</v>
+        <v>78217</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2932,25 +2932,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2960,10 +2960,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>811166</v>
+        <v>811066</v>
       </c>
       <c r="R24" t="n">
-        <v>7392067</v>
+        <v>7392110</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3022,10 +3022,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118001661</v>
+        <v>118001703</v>
       </c>
       <c r="B25" t="n">
-        <v>79069</v>
+        <v>78216</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3038,21 +3038,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3062,10 +3062,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>811038</v>
+        <v>811172</v>
       </c>
       <c r="R25" t="n">
-        <v>7391924</v>
+        <v>7391893</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3106,7 +3106,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3125,10 +3124,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118001698</v>
+        <v>118001677</v>
       </c>
       <c r="B26" t="n">
-        <v>78217</v>
+        <v>56499</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3137,25 +3136,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3165,10 +3164,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>810955</v>
+        <v>811100</v>
       </c>
       <c r="R26" t="n">
-        <v>7392254</v>
+        <v>7391902</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3195,12 +3194,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3227,10 +3226,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118001678</v>
+        <v>118001707</v>
       </c>
       <c r="B27" t="n">
-        <v>56499</v>
+        <v>90648</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3239,25 +3238,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>1503</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3267,10 +3266,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811074</v>
+        <v>811003</v>
       </c>
       <c r="R27" t="n">
-        <v>7391900</v>
+        <v>7392144</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3329,10 +3328,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118001712</v>
+        <v>118001668</v>
       </c>
       <c r="B28" t="n">
-        <v>78480</v>
+        <v>56499</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3341,25 +3340,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3369,10 +3368,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>811102</v>
+        <v>810980</v>
       </c>
       <c r="R28" t="n">
-        <v>7391885</v>
+        <v>7392089</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3431,10 +3430,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118001656</v>
+        <v>118001655</v>
       </c>
       <c r="B29" t="n">
-        <v>79098</v>
+        <v>90464</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3443,25 +3442,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3471,10 +3470,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>810986</v>
+        <v>811144</v>
       </c>
       <c r="R29" t="n">
-        <v>7391960</v>
+        <v>7392075</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3515,7 +3514,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3534,10 +3532,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118001709</v>
+        <v>118001673</v>
       </c>
       <c r="B30" t="n">
-        <v>78480</v>
+        <v>56499</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3546,25 +3544,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3574,10 +3572,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>811212</v>
+        <v>811199</v>
       </c>
       <c r="R30" t="n">
-        <v>7392000</v>
+        <v>7392042</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3636,10 +3634,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118001737</v>
+        <v>118001704</v>
       </c>
       <c r="B31" t="n">
-        <v>91772</v>
+        <v>78216</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3648,25 +3646,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3676,10 +3674,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>811001</v>
+        <v>810991</v>
       </c>
       <c r="R31" t="n">
-        <v>7391908</v>
+        <v>7391920</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3738,10 +3736,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118001674</v>
+        <v>118001656</v>
       </c>
       <c r="B32" t="n">
-        <v>56499</v>
+        <v>79098</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3750,25 +3748,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3778,10 +3776,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>811177</v>
+        <v>810986</v>
       </c>
       <c r="R32" t="n">
-        <v>7392015</v>
+        <v>7391960</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3822,6 +3820,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3840,10 +3839,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118001677</v>
+        <v>118001727</v>
       </c>
       <c r="B33" t="n">
-        <v>56499</v>
+        <v>91772</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3856,21 +3855,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3880,10 +3879,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>811100</v>
+        <v>811234</v>
       </c>
       <c r="R33" t="n">
-        <v>7391902</v>
+        <v>7391908</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3942,10 +3941,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118001669</v>
+        <v>118001695</v>
       </c>
       <c r="B34" t="n">
-        <v>56499</v>
+        <v>91962</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3954,25 +3953,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>2079</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3982,10 +3981,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>811004</v>
+        <v>811066</v>
       </c>
       <c r="R34" t="n">
-        <v>7392125</v>
+        <v>7392110</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4044,10 +4043,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118001660</v>
+        <v>118001698</v>
       </c>
       <c r="B35" t="n">
-        <v>79069</v>
+        <v>78217</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4060,21 +4059,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4084,10 +4083,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>811143</v>
+        <v>810955</v>
       </c>
       <c r="R35" t="n">
-        <v>7391831</v>
+        <v>7392254</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4114,12 +4113,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4128,7 +4127,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4147,10 +4145,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118001726</v>
+        <v>118001715</v>
       </c>
       <c r="B36" t="n">
-        <v>91772</v>
+        <v>78480</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4159,25 +4157,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4187,10 +4185,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>811225</v>
+        <v>810963</v>
       </c>
       <c r="R36" t="n">
-        <v>7391922</v>
+        <v>7392266</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4217,12 +4215,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4249,10 +4247,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118001667</v>
+        <v>118001737</v>
       </c>
       <c r="B37" t="n">
-        <v>56499</v>
+        <v>91772</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4265,21 +4263,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4289,10 +4287,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>810924</v>
+        <v>811001</v>
       </c>
       <c r="R37" t="n">
-        <v>7392048</v>
+        <v>7391908</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4351,7 +4349,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118001742</v>
+        <v>118001738</v>
       </c>
       <c r="B38" t="n">
         <v>91772</v>
@@ -4391,10 +4389,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>810927</v>
+        <v>810996</v>
       </c>
       <c r="R38" t="n">
-        <v>7392000</v>
+        <v>7391935</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4453,7 +4451,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118001723</v>
+        <v>118001732</v>
       </c>
       <c r="B39" t="n">
         <v>91772</v>
@@ -4493,10 +4491,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>811070</v>
+        <v>811045</v>
       </c>
       <c r="R39" t="n">
-        <v>7392098</v>
+        <v>7391904</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4555,7 +4553,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118001707</v>
+        <v>118001708</v>
       </c>
       <c r="B40" t="n">
         <v>90648</v>
@@ -4595,10 +4593,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>811003</v>
+        <v>811144</v>
       </c>
       <c r="R40" t="n">
-        <v>7392144</v>
+        <v>7392075</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4657,10 +4655,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118001695</v>
+        <v>118001674</v>
       </c>
       <c r="B41" t="n">
-        <v>91962</v>
+        <v>56499</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4669,25 +4667,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>2079</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4697,10 +4695,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811066</v>
+        <v>811177</v>
       </c>
       <c r="R41" t="n">
-        <v>7392110</v>
+        <v>7392015</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4759,10 +4757,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118001717</v>
+        <v>118001742</v>
       </c>
       <c r="B42" t="n">
-        <v>90743</v>
+        <v>91772</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4771,25 +4769,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>65</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4799,10 +4797,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>810965</v>
+        <v>810927</v>
       </c>
       <c r="R42" t="n">
-        <v>7391976</v>
+        <v>7392000</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4861,10 +4859,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118001724</v>
+        <v>118001714</v>
       </c>
       <c r="B43" t="n">
-        <v>91772</v>
+        <v>78480</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4873,25 +4871,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4901,10 +4899,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>811089</v>
+        <v>810916</v>
       </c>
       <c r="R43" t="n">
-        <v>7392114</v>
+        <v>7392004</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4963,10 +4961,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118001721</v>
+        <v>118001711</v>
       </c>
       <c r="B44" t="n">
-        <v>91772</v>
+        <v>78480</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4975,25 +4973,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5003,10 +5001,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>810982</v>
+        <v>811133</v>
       </c>
       <c r="R44" t="n">
-        <v>7392103</v>
+        <v>7391844</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5065,10 +5063,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118001713</v>
+        <v>118001718</v>
       </c>
       <c r="B45" t="n">
-        <v>78480</v>
+        <v>91772</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5077,25 +5075,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5105,10 +5103,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>810957</v>
+        <v>811031</v>
       </c>
       <c r="R45" t="n">
-        <v>7391966</v>
+        <v>7392108</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5149,6 +5147,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5167,10 +5166,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118001710</v>
+        <v>118001740</v>
       </c>
       <c r="B46" t="n">
-        <v>78480</v>
+        <v>91772</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5179,25 +5178,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5207,10 +5206,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>811207</v>
+        <v>811002</v>
       </c>
       <c r="R46" t="n">
-        <v>7391978</v>
+        <v>7391962</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5269,10 +5268,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118001714</v>
+        <v>118001702</v>
       </c>
       <c r="B47" t="n">
-        <v>78480</v>
+        <v>78216</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5285,21 +5284,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5309,10 +5308,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>810916</v>
+        <v>810955</v>
       </c>
       <c r="R47" t="n">
-        <v>7392004</v>
+        <v>7392254</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5339,12 +5338,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5353,6 +5352,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5371,10 +5371,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118001688</v>
+        <v>118001665</v>
       </c>
       <c r="B48" t="n">
-        <v>57303</v>
+        <v>89570</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5387,21 +5387,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>1962</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>811140</v>
+        <v>810961</v>
       </c>
       <c r="R48" t="n">
-        <v>7391852</v>
+        <v>7391987</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5473,10 +5473,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118001673</v>
+        <v>118001701</v>
       </c>
       <c r="B49" t="n">
-        <v>56499</v>
+        <v>78217</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5485,25 +5485,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5513,10 +5513,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>811199</v>
+        <v>811130</v>
       </c>
       <c r="R49" t="n">
-        <v>7392042</v>
+        <v>7391886</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5575,7 +5575,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118001736</v>
+        <v>118001719</v>
       </c>
       <c r="B50" t="n">
         <v>91772</v>
@@ -5615,10 +5615,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>811013</v>
+        <v>811114</v>
       </c>
       <c r="R50" t="n">
-        <v>7391909</v>
+        <v>7392081</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5659,6 +5659,7 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
+      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5677,7 +5678,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118001727</v>
+        <v>118001722</v>
       </c>
       <c r="B51" t="n">
         <v>91772</v>
@@ -5717,10 +5718,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>811234</v>
+        <v>811018</v>
       </c>
       <c r="R51" t="n">
-        <v>7391908</v>
+        <v>7392104</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5779,10 +5780,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118001708</v>
+        <v>118001730</v>
       </c>
       <c r="B52" t="n">
-        <v>90648</v>
+        <v>91772</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5791,25 +5792,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5819,10 +5820,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>811144</v>
+        <v>811121</v>
       </c>
       <c r="R52" t="n">
-        <v>7392075</v>
+        <v>7391868</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5881,10 +5882,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118001670</v>
+        <v>118001720</v>
       </c>
       <c r="B53" t="n">
-        <v>56499</v>
+        <v>91772</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5897,21 +5898,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5921,10 +5922,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>811014</v>
+        <v>810930</v>
       </c>
       <c r="R53" t="n">
-        <v>7392111</v>
+        <v>7392068</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5983,10 +5984,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118001668</v>
+        <v>118001728</v>
       </c>
       <c r="B54" t="n">
-        <v>56499</v>
+        <v>91772</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -5999,21 +6000,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6023,10 +6024,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>810980</v>
+        <v>811172</v>
       </c>
       <c r="R54" t="n">
-        <v>7392089</v>
+        <v>7391877</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6085,10 +6086,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>118001700</v>
+        <v>118001725</v>
       </c>
       <c r="B55" t="n">
-        <v>78217</v>
+        <v>91772</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6097,25 +6098,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6125,10 +6126,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>811172</v>
+        <v>811196</v>
       </c>
       <c r="R55" t="n">
-        <v>7391893</v>
+        <v>7392065</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6187,7 +6188,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118001738</v>
+        <v>118001731</v>
       </c>
       <c r="B56" t="n">
         <v>91772</v>
@@ -6227,10 +6228,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>810996</v>
+        <v>811065</v>
       </c>
       <c r="R56" t="n">
-        <v>7391935</v>
+        <v>7391924</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6289,7 +6290,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118001658</v>
+        <v>118001657</v>
       </c>
       <c r="B57" t="n">
         <v>79098</v>
@@ -6329,10 +6330,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>811172</v>
+        <v>811173</v>
       </c>
       <c r="R57" t="n">
-        <v>7391893</v>
+        <v>7391869</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6391,7 +6392,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118001690</v>
+        <v>118001688</v>
       </c>
       <c r="B58" t="n">
         <v>57303</v>
@@ -6431,10 +6432,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>811118</v>
+        <v>811140</v>
       </c>
       <c r="R58" t="n">
-        <v>7391876</v>
+        <v>7391852</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6493,10 +6494,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118001665</v>
+        <v>118001660</v>
       </c>
       <c r="B59" t="n">
-        <v>89570</v>
+        <v>79069</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6509,21 +6510,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1962</v>
+        <v>229821</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6533,10 +6534,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>810961</v>
+        <v>811143</v>
       </c>
       <c r="R59" t="n">
-        <v>7391987</v>
+        <v>7391831</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6577,6 +6578,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6595,10 +6597,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118001679</v>
+        <v>118001662</v>
       </c>
       <c r="B60" t="n">
-        <v>56499</v>
+        <v>79069</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6607,25 +6609,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>229821</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6635,10 +6637,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>811070</v>
+        <v>811190</v>
       </c>
       <c r="R60" t="n">
-        <v>7391883</v>
+        <v>7391880</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6697,10 +6699,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118001735</v>
+        <v>118001671</v>
       </c>
       <c r="B61" t="n">
-        <v>91772</v>
+        <v>56499</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6713,21 +6715,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6737,10 +6739,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>811027</v>
+        <v>811031</v>
       </c>
       <c r="R61" t="n">
-        <v>7391926</v>
+        <v>7392108</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6799,10 +6801,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118001676</v>
+        <v>118001712</v>
       </c>
       <c r="B62" t="n">
-        <v>56499</v>
+        <v>78480</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6811,25 +6813,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6839,10 +6841,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>811223</v>
+        <v>811102</v>
       </c>
       <c r="R62" t="n">
-        <v>7391913</v>
+        <v>7391885</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6901,10 +6903,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118001711</v>
+        <v>118001739</v>
       </c>
       <c r="B63" t="n">
-        <v>78480</v>
+        <v>91772</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6913,25 +6915,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6941,10 +6943,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>811133</v>
+        <v>811009</v>
       </c>
       <c r="R63" t="n">
-        <v>7391844</v>
+        <v>7391935</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7003,10 +7005,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118001719</v>
+        <v>118001678</v>
       </c>
       <c r="B64" t="n">
-        <v>91772</v>
+        <v>56499</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7019,21 +7021,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7043,10 +7045,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>811114</v>
+        <v>811074</v>
       </c>
       <c r="R64" t="n">
-        <v>7392081</v>
+        <v>7391900</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7087,7 +7089,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7106,10 +7107,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118001718</v>
+        <v>118001700</v>
       </c>
       <c r="B65" t="n">
-        <v>91772</v>
+        <v>78217</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7118,25 +7119,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7146,10 +7147,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>811031</v>
+        <v>811172</v>
       </c>
       <c r="R65" t="n">
-        <v>7392108</v>
+        <v>7391893</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7190,7 +7191,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7209,7 +7209,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118001725</v>
+        <v>118001736</v>
       </c>
       <c r="B66" t="n">
         <v>91772</v>
@@ -7249,10 +7249,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>811196</v>
+        <v>811013</v>
       </c>
       <c r="R66" t="n">
-        <v>7392065</v>
+        <v>7391909</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7311,7 +7311,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118001739</v>
+        <v>118001734</v>
       </c>
       <c r="B67" t="n">
         <v>91772</v>
@@ -7351,10 +7351,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>811009</v>
+        <v>811036</v>
       </c>
       <c r="R67" t="n">
-        <v>7391935</v>
+        <v>7391915</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7413,10 +7413,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118001662</v>
+        <v>118001710</v>
       </c>
       <c r="B68" t="n">
-        <v>79069</v>
+        <v>78480</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7429,21 +7429,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7453,10 +7453,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>811190</v>
+        <v>811207</v>
       </c>
       <c r="R68" t="n">
-        <v>7391880</v>
+        <v>7391978</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>

--- a/artfynd/A 10151-2023 artfynd.xlsx
+++ b/artfynd/A 10151-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118001726</v>
+        <v>118001714</v>
       </c>
       <c r="B2" t="n">
-        <v>91772</v>
+        <v>78482</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>811225</v>
+        <v>810916</v>
       </c>
       <c r="R2" t="n">
-        <v>7391922</v>
+        <v>7392004</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118001724</v>
+        <v>118001721</v>
       </c>
       <c r="B3" t="n">
-        <v>91772</v>
+        <v>91774</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>811089</v>
+        <v>810982</v>
       </c>
       <c r="R3" t="n">
-        <v>7392114</v>
+        <v>7392103</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118001735</v>
+        <v>118001707</v>
       </c>
       <c r="B4" t="n">
-        <v>91772</v>
+        <v>90650</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>811027</v>
+        <v>811003</v>
       </c>
       <c r="R4" t="n">
-        <v>7391926</v>
+        <v>7392144</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118001709</v>
+        <v>118001734</v>
       </c>
       <c r="B5" t="n">
-        <v>78480</v>
+        <v>91774</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>811212</v>
+        <v>811036</v>
       </c>
       <c r="R5" t="n">
-        <v>7392000</v>
+        <v>7391915</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118001713</v>
+        <v>118001711</v>
       </c>
       <c r="B6" t="n">
-        <v>78480</v>
+        <v>78482</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>810957</v>
+        <v>811133</v>
       </c>
       <c r="R6" t="n">
-        <v>7391966</v>
+        <v>7391844</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118001670</v>
+        <v>118001700</v>
       </c>
       <c r="B7" t="n">
-        <v>56499</v>
+        <v>78219</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>811014</v>
+        <v>811172</v>
       </c>
       <c r="R7" t="n">
-        <v>7392111</v>
+        <v>7391893</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>118001672</v>
+        <v>118001741</v>
       </c>
       <c r="B8" t="n">
-        <v>56499</v>
+        <v>91774</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>811166</v>
+        <v>810985</v>
       </c>
       <c r="R8" t="n">
-        <v>7392067</v>
+        <v>7391966</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>118001723</v>
+        <v>118001661</v>
       </c>
       <c r="B9" t="n">
-        <v>91772</v>
+        <v>79071</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>811070</v>
+        <v>811038</v>
       </c>
       <c r="R9" t="n">
-        <v>7392098</v>
+        <v>7391924</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1473,6 +1473,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1491,10 +1492,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>118001741</v>
+        <v>118001715</v>
       </c>
       <c r="B10" t="n">
-        <v>91772</v>
+        <v>78482</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1503,25 +1504,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1531,10 +1532,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>810985</v>
+        <v>810963</v>
       </c>
       <c r="R10" t="n">
-        <v>7391966</v>
+        <v>7392266</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1561,12 +1562,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1593,10 +1594,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118001667</v>
+        <v>118001737</v>
       </c>
       <c r="B11" t="n">
-        <v>56499</v>
+        <v>91774</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1610,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1634,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>810924</v>
+        <v>811001</v>
       </c>
       <c r="R11" t="n">
-        <v>7392048</v>
+        <v>7391908</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,10 +1696,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118001675</v>
+        <v>118001729</v>
       </c>
       <c r="B12" t="n">
-        <v>56499</v>
+        <v>91774</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1711,21 +1712,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,10 +1736,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>811203</v>
+        <v>811131</v>
       </c>
       <c r="R12" t="n">
-        <v>7391977</v>
+        <v>7391868</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,10 +1798,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>118001664</v>
+        <v>118001739</v>
       </c>
       <c r="B13" t="n">
-        <v>89570</v>
+        <v>91774</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1810,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1838,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>811168</v>
+        <v>811009</v>
       </c>
       <c r="R13" t="n">
-        <v>7392005</v>
+        <v>7391935</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1900,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>118001661</v>
+        <v>118001656</v>
       </c>
       <c r="B14" t="n">
-        <v>79069</v>
+        <v>79100</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1916,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6453</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1940,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>811038</v>
+        <v>810986</v>
       </c>
       <c r="R14" t="n">
-        <v>7391924</v>
+        <v>7391960</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2002,10 +2003,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118001697</v>
+        <v>118001702</v>
       </c>
       <c r="B15" t="n">
-        <v>78217</v>
+        <v>78218</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2018,21 +2019,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2042,10 +2043,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>811173</v>
+        <v>810955</v>
       </c>
       <c r="R15" t="n">
-        <v>7391869</v>
+        <v>7392254</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2072,12 +2073,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2086,6 +2087,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2104,10 +2106,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118001721</v>
+        <v>118001675</v>
       </c>
       <c r="B16" t="n">
-        <v>91772</v>
+        <v>56500</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2120,21 +2122,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2144,10 +2146,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>810982</v>
+        <v>811203</v>
       </c>
       <c r="R16" t="n">
-        <v>7392103</v>
+        <v>7391977</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2206,10 +2208,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118001679</v>
+        <v>118001670</v>
       </c>
       <c r="B17" t="n">
-        <v>56499</v>
+        <v>56500</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2246,10 +2248,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>811070</v>
+        <v>811014</v>
       </c>
       <c r="R17" t="n">
-        <v>7391883</v>
+        <v>7392111</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2308,10 +2310,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118001717</v>
+        <v>118001677</v>
       </c>
       <c r="B18" t="n">
-        <v>90743</v>
+        <v>56500</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2320,25 +2322,25 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>65</v>
+        <v>100138</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2348,10 +2350,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>810965</v>
+        <v>811100</v>
       </c>
       <c r="R18" t="n">
-        <v>7391976</v>
+        <v>7391902</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2410,10 +2412,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118001729</v>
+        <v>118001697</v>
       </c>
       <c r="B19" t="n">
-        <v>91772</v>
+        <v>78219</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2422,25 +2424,25 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2450,10 +2452,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>811131</v>
+        <v>811173</v>
       </c>
       <c r="R19" t="n">
-        <v>7391868</v>
+        <v>7391869</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2512,10 +2514,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118001658</v>
+        <v>118001722</v>
       </c>
       <c r="B20" t="n">
-        <v>79098</v>
+        <v>91774</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2524,25 +2526,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2552,10 +2554,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>811172</v>
+        <v>811018</v>
       </c>
       <c r="R20" t="n">
-        <v>7391893</v>
+        <v>7392104</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2614,10 +2616,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118001669</v>
+        <v>118001674</v>
       </c>
       <c r="B21" t="n">
-        <v>56499</v>
+        <v>56500</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2654,10 +2656,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>811004</v>
+        <v>811177</v>
       </c>
       <c r="R21" t="n">
-        <v>7392125</v>
+        <v>7392015</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2716,10 +2718,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118001676</v>
+        <v>118001728</v>
       </c>
       <c r="B22" t="n">
-        <v>56499</v>
+        <v>91774</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2732,21 +2734,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2756,10 +2758,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>811223</v>
+        <v>811172</v>
       </c>
       <c r="R22" t="n">
-        <v>7391913</v>
+        <v>7391877</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2821,7 +2823,7 @@
         <v>118001690</v>
       </c>
       <c r="B23" t="n">
-        <v>57303</v>
+        <v>57304</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2920,10 +2922,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118001696</v>
+        <v>118001723</v>
       </c>
       <c r="B24" t="n">
-        <v>78217</v>
+        <v>91774</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -2932,25 +2934,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2960,10 +2962,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>811066</v>
+        <v>811070</v>
       </c>
       <c r="R24" t="n">
-        <v>7392110</v>
+        <v>7392098</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3022,10 +3024,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118001703</v>
+        <v>118001727</v>
       </c>
       <c r="B25" t="n">
-        <v>78216</v>
+        <v>91774</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3034,25 +3036,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3062,10 +3064,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>811172</v>
+        <v>811234</v>
       </c>
       <c r="R25" t="n">
-        <v>7391893</v>
+        <v>7391908</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3124,10 +3126,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118001677</v>
+        <v>118001735</v>
       </c>
       <c r="B26" t="n">
-        <v>56499</v>
+        <v>91774</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3140,21 +3142,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3164,10 +3166,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>811100</v>
+        <v>811027</v>
       </c>
       <c r="R26" t="n">
-        <v>7391902</v>
+        <v>7391926</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3226,10 +3228,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118001707</v>
+        <v>118001679</v>
       </c>
       <c r="B27" t="n">
-        <v>90648</v>
+        <v>56500</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3238,25 +3240,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1503</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3266,10 +3268,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>811003</v>
+        <v>811070</v>
       </c>
       <c r="R27" t="n">
-        <v>7392144</v>
+        <v>7391883</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3328,10 +3330,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118001668</v>
+        <v>118001673</v>
       </c>
       <c r="B28" t="n">
-        <v>56499</v>
+        <v>56500</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3368,10 +3370,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>810980</v>
+        <v>811199</v>
       </c>
       <c r="R28" t="n">
-        <v>7392089</v>
+        <v>7392042</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3430,10 +3432,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118001655</v>
+        <v>118001719</v>
       </c>
       <c r="B29" t="n">
-        <v>90464</v>
+        <v>91774</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3446,21 +3448,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3470,10 +3472,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>811144</v>
+        <v>811114</v>
       </c>
       <c r="R29" t="n">
-        <v>7392075</v>
+        <v>7392081</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3514,6 +3516,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3532,10 +3535,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118001673</v>
+        <v>118001720</v>
       </c>
       <c r="B30" t="n">
-        <v>56499</v>
+        <v>91774</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3548,21 +3551,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3572,10 +3575,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>811199</v>
+        <v>810930</v>
       </c>
       <c r="R30" t="n">
-        <v>7392042</v>
+        <v>7392068</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3634,10 +3637,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118001704</v>
+        <v>118001732</v>
       </c>
       <c r="B31" t="n">
-        <v>78216</v>
+        <v>91774</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3646,25 +3649,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3674,10 +3677,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>810991</v>
+        <v>811045</v>
       </c>
       <c r="R31" t="n">
-        <v>7391920</v>
+        <v>7391904</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3736,10 +3739,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118001656</v>
+        <v>118001704</v>
       </c>
       <c r="B32" t="n">
-        <v>79098</v>
+        <v>78218</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3752,21 +3755,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3776,10 +3779,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>810986</v>
+        <v>810991</v>
       </c>
       <c r="R32" t="n">
-        <v>7391960</v>
+        <v>7391920</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3820,7 +3823,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3839,10 +3841,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118001727</v>
+        <v>118001678</v>
       </c>
       <c r="B33" t="n">
-        <v>91772</v>
+        <v>56500</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3855,21 +3857,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3879,10 +3881,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>811234</v>
+        <v>811074</v>
       </c>
       <c r="R33" t="n">
-        <v>7391908</v>
+        <v>7391900</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3941,10 +3943,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118001695</v>
+        <v>118001717</v>
       </c>
       <c r="B34" t="n">
-        <v>91962</v>
+        <v>90745</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3953,25 +3955,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>2079</v>
+        <v>65</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Nordtagging</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Odonticium romellii</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(S.Lundell) Parmasto</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3981,10 +3983,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>811066</v>
+        <v>810965</v>
       </c>
       <c r="R34" t="n">
-        <v>7392110</v>
+        <v>7391976</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4043,10 +4045,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118001698</v>
+        <v>118001667</v>
       </c>
       <c r="B35" t="n">
-        <v>78217</v>
+        <v>56500</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4055,25 +4057,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4083,10 +4085,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>810955</v>
+        <v>810924</v>
       </c>
       <c r="R35" t="n">
-        <v>7392254</v>
+        <v>7392048</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4113,12 +4115,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4145,10 +4147,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118001715</v>
+        <v>118001655</v>
       </c>
       <c r="B36" t="n">
-        <v>78480</v>
+        <v>90466</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4157,25 +4159,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4185,10 +4187,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>810963</v>
+        <v>811144</v>
       </c>
       <c r="R36" t="n">
-        <v>7392266</v>
+        <v>7392075</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4215,12 +4217,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4247,10 +4249,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118001737</v>
+        <v>118001738</v>
       </c>
       <c r="B37" t="n">
-        <v>91772</v>
+        <v>91774</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4287,10 +4289,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>811001</v>
+        <v>810996</v>
       </c>
       <c r="R37" t="n">
-        <v>7391908</v>
+        <v>7391935</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4349,10 +4351,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118001738</v>
+        <v>118001669</v>
       </c>
       <c r="B38" t="n">
-        <v>91772</v>
+        <v>56500</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4365,21 +4367,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4389,10 +4391,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>810996</v>
+        <v>811004</v>
       </c>
       <c r="R38" t="n">
-        <v>7391935</v>
+        <v>7392125</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4451,10 +4453,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>118001732</v>
+        <v>118001658</v>
       </c>
       <c r="B39" t="n">
-        <v>91772</v>
+        <v>79100</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4463,25 +4465,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4491,10 +4493,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>811045</v>
+        <v>811172</v>
       </c>
       <c r="R39" t="n">
-        <v>7391904</v>
+        <v>7391893</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4553,10 +4555,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>118001708</v>
+        <v>118001736</v>
       </c>
       <c r="B40" t="n">
-        <v>90648</v>
+        <v>91774</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4565,25 +4567,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1503</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4593,10 +4595,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>811144</v>
+        <v>811013</v>
       </c>
       <c r="R40" t="n">
-        <v>7392075</v>
+        <v>7391909</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4655,10 +4657,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>118001674</v>
+        <v>118001695</v>
       </c>
       <c r="B41" t="n">
-        <v>56499</v>
+        <v>91964</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4667,25 +4669,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100138</v>
+        <v>2079</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4695,10 +4697,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>811177</v>
+        <v>811066</v>
       </c>
       <c r="R41" t="n">
-        <v>7392015</v>
+        <v>7392110</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4757,10 +4759,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>118001742</v>
+        <v>118001730</v>
       </c>
       <c r="B42" t="n">
-        <v>91772</v>
+        <v>91774</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4797,10 +4799,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>810927</v>
+        <v>811121</v>
       </c>
       <c r="R42" t="n">
-        <v>7392000</v>
+        <v>7391868</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4859,10 +4861,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>118001714</v>
+        <v>118001664</v>
       </c>
       <c r="B43" t="n">
-        <v>78480</v>
+        <v>89572</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -4875,21 +4877,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4899,10 +4901,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>810916</v>
+        <v>811168</v>
       </c>
       <c r="R43" t="n">
-        <v>7392004</v>
+        <v>7392005</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4961,10 +4963,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>118001711</v>
+        <v>118001671</v>
       </c>
       <c r="B44" t="n">
-        <v>78480</v>
+        <v>56500</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -4973,25 +4975,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5001,10 +5003,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>811133</v>
+        <v>811031</v>
       </c>
       <c r="R44" t="n">
-        <v>7391844</v>
+        <v>7392108</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5063,10 +5065,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>118001718</v>
+        <v>118001660</v>
       </c>
       <c r="B45" t="n">
-        <v>91772</v>
+        <v>79071</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5075,25 +5077,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5103,10 +5105,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>811031</v>
+        <v>811143</v>
       </c>
       <c r="R45" t="n">
-        <v>7392108</v>
+        <v>7391831</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5166,10 +5168,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>118001740</v>
+        <v>118001710</v>
       </c>
       <c r="B46" t="n">
-        <v>91772</v>
+        <v>78482</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5178,25 +5180,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5206,10 +5208,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>811002</v>
+        <v>811207</v>
       </c>
       <c r="R46" t="n">
-        <v>7391962</v>
+        <v>7391978</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5268,10 +5270,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>118001702</v>
+        <v>118001724</v>
       </c>
       <c r="B47" t="n">
-        <v>78216</v>
+        <v>91774</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5280,25 +5282,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5308,10 +5310,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>810955</v>
+        <v>811089</v>
       </c>
       <c r="R47" t="n">
-        <v>7392254</v>
+        <v>7392114</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5338,12 +5340,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5352,7 +5354,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5371,10 +5372,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>118001665</v>
+        <v>118001731</v>
       </c>
       <c r="B48" t="n">
-        <v>89570</v>
+        <v>91774</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5383,25 +5384,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5411,10 +5412,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>810961</v>
+        <v>811065</v>
       </c>
       <c r="R48" t="n">
-        <v>7391987</v>
+        <v>7391924</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5473,10 +5474,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>118001701</v>
+        <v>118001657</v>
       </c>
       <c r="B49" t="n">
-        <v>78217</v>
+        <v>79100</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5489,21 +5490,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5513,10 +5514,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>811130</v>
+        <v>811173</v>
       </c>
       <c r="R49" t="n">
-        <v>7391886</v>
+        <v>7391869</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5575,10 +5576,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>118001719</v>
+        <v>118001696</v>
       </c>
       <c r="B50" t="n">
-        <v>91772</v>
+        <v>78219</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5587,25 +5588,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5615,10 +5616,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>811114</v>
+        <v>811066</v>
       </c>
       <c r="R50" t="n">
-        <v>7392081</v>
+        <v>7392110</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5659,7 +5660,6 @@
       <c r="AE50" t="b">
         <v>0</v>
       </c>
-      <c r="AF50" t="inlineStr"/>
       <c r="AG50" t="b">
         <v>0</v>
       </c>
@@ -5678,10 +5678,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>118001722</v>
+        <v>118001713</v>
       </c>
       <c r="B51" t="n">
-        <v>91772</v>
+        <v>78482</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5690,25 +5690,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5718,10 +5718,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>811018</v>
+        <v>810957</v>
       </c>
       <c r="R51" t="n">
-        <v>7392104</v>
+        <v>7391966</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5780,10 +5780,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>118001730</v>
+        <v>118001740</v>
       </c>
       <c r="B52" t="n">
-        <v>91772</v>
+        <v>91774</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5820,10 +5820,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>811121</v>
+        <v>811002</v>
       </c>
       <c r="R52" t="n">
-        <v>7391868</v>
+        <v>7391962</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5882,10 +5882,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>118001720</v>
+        <v>118001662</v>
       </c>
       <c r="B53" t="n">
-        <v>91772</v>
+        <v>79071</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -5894,25 +5894,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5922,10 +5922,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>810930</v>
+        <v>811190</v>
       </c>
       <c r="R53" t="n">
-        <v>7392068</v>
+        <v>7391880</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5984,10 +5984,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>118001728</v>
+        <v>118001672</v>
       </c>
       <c r="B54" t="n">
-        <v>91772</v>
+        <v>56500</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6000,21 +6000,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6024,10 +6024,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>811172</v>
+        <v>811166</v>
       </c>
       <c r="R54" t="n">
-        <v>7391877</v>
+        <v>7392067</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6089,7 +6089,7 @@
         <v>118001725</v>
       </c>
       <c r="B55" t="n">
-        <v>91772</v>
+        <v>91774</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6188,10 +6188,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118001731</v>
+        <v>118001698</v>
       </c>
       <c r="B56" t="n">
-        <v>91772</v>
+        <v>78219</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6200,25 +6200,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6228,10 +6228,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>811065</v>
+        <v>810955</v>
       </c>
       <c r="R56" t="n">
-        <v>7391924</v>
+        <v>7392254</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6290,10 +6290,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118001657</v>
+        <v>118001742</v>
       </c>
       <c r="B57" t="n">
-        <v>79098</v>
+        <v>91774</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6302,25 +6302,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6330,10 +6330,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>811173</v>
+        <v>810927</v>
       </c>
       <c r="R57" t="n">
-        <v>7391869</v>
+        <v>7392000</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6392,10 +6392,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>118001688</v>
+        <v>118001668</v>
       </c>
       <c r="B58" t="n">
-        <v>57303</v>
+        <v>56500</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6404,25 +6404,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6432,10 +6432,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>811140</v>
+        <v>810980</v>
       </c>
       <c r="R58" t="n">
-        <v>7391852</v>
+        <v>7392089</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6494,10 +6494,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>118001660</v>
+        <v>118001665</v>
       </c>
       <c r="B59" t="n">
-        <v>79069</v>
+        <v>89572</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6510,21 +6510,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>229821</v>
+        <v>1962</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6534,10 +6534,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>811143</v>
+        <v>810961</v>
       </c>
       <c r="R59" t="n">
-        <v>7391831</v>
+        <v>7391987</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6578,7 +6578,6 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
-      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -6597,10 +6596,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>118001662</v>
+        <v>118001712</v>
       </c>
       <c r="B60" t="n">
-        <v>79069</v>
+        <v>78482</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6613,21 +6612,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6637,10 +6636,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>811190</v>
+        <v>811102</v>
       </c>
       <c r="R60" t="n">
-        <v>7391880</v>
+        <v>7391885</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6699,10 +6698,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>118001671</v>
+        <v>118001718</v>
       </c>
       <c r="B61" t="n">
-        <v>56499</v>
+        <v>91774</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6715,21 +6714,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6783,6 +6782,7 @@
       <c r="AE61" t="b">
         <v>0</v>
       </c>
+      <c r="AF61" t="inlineStr"/>
       <c r="AG61" t="b">
         <v>0</v>
       </c>
@@ -6801,10 +6801,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118001712</v>
+        <v>118001676</v>
       </c>
       <c r="B62" t="n">
-        <v>78480</v>
+        <v>56500</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6813,25 +6813,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6841,10 +6841,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>811102</v>
+        <v>811223</v>
       </c>
       <c r="R62" t="n">
-        <v>7391885</v>
+        <v>7391913</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6903,10 +6903,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118001739</v>
+        <v>118001701</v>
       </c>
       <c r="B63" t="n">
-        <v>91772</v>
+        <v>78219</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6915,25 +6915,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6943,10 +6943,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>811009</v>
+        <v>811130</v>
       </c>
       <c r="R63" t="n">
-        <v>7391935</v>
+        <v>7391886</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7005,10 +7005,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>118001678</v>
+        <v>118001726</v>
       </c>
       <c r="B64" t="n">
-        <v>56499</v>
+        <v>91774</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7021,21 +7021,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7045,10 +7045,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>811074</v>
+        <v>811225</v>
       </c>
       <c r="R64" t="n">
-        <v>7391900</v>
+        <v>7391922</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7107,10 +7107,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>118001700</v>
+        <v>118001708</v>
       </c>
       <c r="B65" t="n">
-        <v>78217</v>
+        <v>90650</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7119,25 +7119,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7147,10 +7147,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>811172</v>
+        <v>811144</v>
       </c>
       <c r="R65" t="n">
-        <v>7391893</v>
+        <v>7392075</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7209,10 +7209,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>118001736</v>
+        <v>118001709</v>
       </c>
       <c r="B66" t="n">
-        <v>91772</v>
+        <v>78482</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7221,25 +7221,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7249,10 +7249,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>811013</v>
+        <v>811212</v>
       </c>
       <c r="R66" t="n">
-        <v>7391909</v>
+        <v>7392000</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7311,10 +7311,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>118001734</v>
+        <v>118001688</v>
       </c>
       <c r="B67" t="n">
-        <v>91772</v>
+        <v>57304</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7323,25 +7323,25 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7351,10 +7351,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>811036</v>
+        <v>811140</v>
       </c>
       <c r="R67" t="n">
-        <v>7391915</v>
+        <v>7391852</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7413,10 +7413,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>118001710</v>
+        <v>118001703</v>
       </c>
       <c r="B68" t="n">
-        <v>78480</v>
+        <v>78218</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7429,21 +7429,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7453,10 +7453,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>811207</v>
+        <v>811172</v>
       </c>
       <c r="R68" t="n">
-        <v>7391978</v>
+        <v>7391893</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>

--- a/artfynd/A 10151-2023 artfynd.xlsx
+++ b/artfynd/A 10151-2023 artfynd.xlsx
@@ -2514,10 +2514,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118001722</v>
+        <v>118001674</v>
       </c>
       <c r="B20" t="n">
-        <v>91774</v>
+        <v>56500</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2530,21 +2530,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2554,10 +2554,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>811018</v>
+        <v>811177</v>
       </c>
       <c r="R20" t="n">
-        <v>7392104</v>
+        <v>7392015</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2616,10 +2616,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118001674</v>
+        <v>118001722</v>
       </c>
       <c r="B21" t="n">
-        <v>56500</v>
+        <v>91774</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2632,21 +2632,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2656,10 +2656,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>811177</v>
+        <v>811018</v>
       </c>
       <c r="R21" t="n">
-        <v>7392015</v>
+        <v>7392104</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2718,10 +2718,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118001728</v>
+        <v>118001690</v>
       </c>
       <c r="B22" t="n">
-        <v>91774</v>
+        <v>57304</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2730,25 +2730,25 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2758,10 +2758,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>811172</v>
+        <v>811118</v>
       </c>
       <c r="R22" t="n">
-        <v>7391877</v>
+        <v>7391876</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2820,10 +2820,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118001690</v>
+        <v>118001728</v>
       </c>
       <c r="B23" t="n">
-        <v>57304</v>
+        <v>91774</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2832,25 +2832,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2860,10 +2860,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>811118</v>
+        <v>811172</v>
       </c>
       <c r="R23" t="n">
-        <v>7391876</v>
+        <v>7391877</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3943,10 +3943,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118001717</v>
+        <v>118001667</v>
       </c>
       <c r="B34" t="n">
-        <v>90745</v>
+        <v>56500</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -3955,25 +3955,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>65</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Fläckporing</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Anthoporia albobrunnea</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Romell) Karasiński &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3983,10 +3983,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>810965</v>
+        <v>810924</v>
       </c>
       <c r="R34" t="n">
-        <v>7391976</v>
+        <v>7392048</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4045,10 +4045,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118001667</v>
+        <v>118001717</v>
       </c>
       <c r="B35" t="n">
-        <v>56500</v>
+        <v>90745</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4057,25 +4057,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>65</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläckporing</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Anthoporia albobrunnea</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Romell) Karasiński &amp; Niemelä</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4085,10 +4085,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>810924</v>
+        <v>810965</v>
       </c>
       <c r="R35" t="n">
-        <v>7392048</v>
+        <v>7391976</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -6188,10 +6188,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>118001698</v>
+        <v>118001742</v>
       </c>
       <c r="B56" t="n">
-        <v>78219</v>
+        <v>91774</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6200,25 +6200,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6228,10 +6228,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>810955</v>
+        <v>810927</v>
       </c>
       <c r="R56" t="n">
-        <v>7392254</v>
+        <v>7392000</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6258,12 +6258,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2024-06-11</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6290,10 +6290,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>118001742</v>
+        <v>118001698</v>
       </c>
       <c r="B57" t="n">
-        <v>91774</v>
+        <v>78219</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6302,25 +6302,25 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6330,10 +6330,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>810927</v>
+        <v>810955</v>
       </c>
       <c r="R57" t="n">
-        <v>7392000</v>
+        <v>7392254</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6360,12 +6360,12 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-06-11</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6801,10 +6801,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>118001676</v>
+        <v>118001701</v>
       </c>
       <c r="B62" t="n">
-        <v>56500</v>
+        <v>78219</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -6813,25 +6813,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6841,10 +6841,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>811223</v>
+        <v>811130</v>
       </c>
       <c r="R62" t="n">
-        <v>7391913</v>
+        <v>7391886</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6903,10 +6903,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>118001701</v>
+        <v>118001676</v>
       </c>
       <c r="B63" t="n">
-        <v>78219</v>
+        <v>56500</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -6915,25 +6915,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6943,10 +6943,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>811130</v>
+        <v>811223</v>
       </c>
       <c r="R63" t="n">
-        <v>7391886</v>
+        <v>7391913</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>

--- a/artfynd/A 10151-2023 artfynd.xlsx
+++ b/artfynd/A 10151-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AY95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7513,6 +7513,2764 @@
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>119002511</v>
+      </c>
+      <c r="B69" t="n">
+        <v>91788</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>810940</v>
+      </c>
+      <c r="R69" t="n">
+        <v>7392082</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>119002486</v>
+      </c>
+      <c r="B70" t="n">
+        <v>78229</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>811068</v>
+      </c>
+      <c r="R70" t="n">
+        <v>7392105</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>119002517</v>
+      </c>
+      <c r="B71" t="n">
+        <v>91788</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>810895</v>
+      </c>
+      <c r="R71" t="n">
+        <v>7392137</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>119002477</v>
+      </c>
+      <c r="B72" t="n">
+        <v>78229</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>810954</v>
+      </c>
+      <c r="R72" t="n">
+        <v>7392254</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2024-06-11</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF72" t="inlineStr"/>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>119002513</v>
+      </c>
+      <c r="B73" t="n">
+        <v>91788</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>811015</v>
+      </c>
+      <c r="R73" t="n">
+        <v>7392183</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>119002444</v>
+      </c>
+      <c r="B74" t="n">
+        <v>56504</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>810842</v>
+      </c>
+      <c r="R74" t="n">
+        <v>7392089</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>119002495</v>
+      </c>
+      <c r="B75" t="n">
+        <v>91788</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>811113</v>
+      </c>
+      <c r="R75" t="n">
+        <v>7392080</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="inlineStr"/>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>119002529</v>
+      </c>
+      <c r="B76" t="n">
+        <v>91782</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>810957</v>
+      </c>
+      <c r="R76" t="n">
+        <v>7392094</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>119002512</v>
+      </c>
+      <c r="B77" t="n">
+        <v>91788</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>810956</v>
+      </c>
+      <c r="R77" t="n">
+        <v>7392097</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>119002448</v>
+      </c>
+      <c r="B78" t="n">
+        <v>90533</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>811095</v>
+      </c>
+      <c r="R78" t="n">
+        <v>7392087</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>119002510</v>
+      </c>
+      <c r="B79" t="n">
+        <v>91788</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>811138</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7392062</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>119002515</v>
+      </c>
+      <c r="B80" t="n">
+        <v>91788</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>810906</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7392235</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>119002464</v>
+      </c>
+      <c r="B81" t="n">
+        <v>96816</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>810805</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7392208</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>119002483</v>
+      </c>
+      <c r="B82" t="n">
+        <v>78229</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>811085</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7392105</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>119002475</v>
+      </c>
+      <c r="B83" t="n">
+        <v>91811</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>810799</v>
+      </c>
+      <c r="R83" t="n">
+        <v>7392130</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>119002492</v>
+      </c>
+      <c r="B84" t="n">
+        <v>78493</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>810813</v>
+      </c>
+      <c r="R84" t="n">
+        <v>7392224</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>119002470</v>
+      </c>
+      <c r="B85" t="n">
+        <v>78230</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>810800</v>
+      </c>
+      <c r="R85" t="n">
+        <v>7392149</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF85" t="inlineStr"/>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>119002442</v>
+      </c>
+      <c r="B86" t="n">
+        <v>56504</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>811015</v>
+      </c>
+      <c r="R86" t="n">
+        <v>7392166</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>119002518</v>
+      </c>
+      <c r="B87" t="n">
+        <v>91788</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>810861</v>
+      </c>
+      <c r="R87" t="n">
+        <v>7392180</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>119002516</v>
+      </c>
+      <c r="B88" t="n">
+        <v>91788</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>810901</v>
+      </c>
+      <c r="R88" t="n">
+        <v>7392216</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>119002509</v>
+      </c>
+      <c r="B89" t="n">
+        <v>91788</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>811164</v>
+      </c>
+      <c r="R89" t="n">
+        <v>7392146</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>119002433</v>
+      </c>
+      <c r="B90" t="n">
+        <v>79111</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>810800</v>
+      </c>
+      <c r="R90" t="n">
+        <v>7392149</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>119002431</v>
+      </c>
+      <c r="B91" t="n">
+        <v>79111</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>811078</v>
+      </c>
+      <c r="R91" t="n">
+        <v>7392109</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>119002438</v>
+      </c>
+      <c r="B92" t="n">
+        <v>56504</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>811011</v>
+      </c>
+      <c r="R92" t="n">
+        <v>7392154</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>119002519</v>
+      </c>
+      <c r="B93" t="n">
+        <v>91788</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>810833</v>
+      </c>
+      <c r="R93" t="n">
+        <v>7392097</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>119002531</v>
+      </c>
+      <c r="B94" t="n">
+        <v>77877</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>6437</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Blanksvart spiklav</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Calicium denigratum</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Vain.) Tibell</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>810883</v>
+      </c>
+      <c r="R94" t="n">
+        <v>7392128</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2024-08-07</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>119002494</v>
+      </c>
+      <c r="B95" t="n">
+        <v>91788</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>811030</v>
+      </c>
+      <c r="R95" t="n">
+        <v>7392108</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF95" t="inlineStr"/>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10151-2023 artfynd.xlsx
+++ b/artfynd/A 10151-2023 artfynd.xlsx
@@ -10273,10 +10273,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119541045</v>
+        <v>119541083</v>
       </c>
       <c r="B96" t="n">
-        <v>91463</v>
+        <v>91832</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10289,21 +10289,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4745</v>
+        <v>4361</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10313,10 +10313,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>811207</v>
+        <v>811752</v>
       </c>
       <c r="R96" t="n">
-        <v>7391947</v>
+        <v>7391915</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10375,10 +10375,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119541056</v>
+        <v>119541104</v>
       </c>
       <c r="B97" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10391,21 +10391,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10415,10 +10415,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>811402</v>
+        <v>811313</v>
       </c>
       <c r="R97" t="n">
-        <v>7391791</v>
+        <v>7391795</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10477,10 +10477,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119541083</v>
+        <v>119541125</v>
       </c>
       <c r="B98" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10489,25 +10489,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10517,10 +10517,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>811752</v>
+        <v>811502</v>
       </c>
       <c r="R98" t="n">
-        <v>7391915</v>
+        <v>7391976</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10579,10 +10579,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119541104</v>
+        <v>119541183</v>
       </c>
       <c r="B99" t="n">
-        <v>78526</v>
+        <v>91834</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10595,21 +10595,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10619,10 +10619,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>811313</v>
+        <v>811180</v>
       </c>
       <c r="R99" t="n">
-        <v>7391795</v>
+        <v>7391829</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10681,10 +10681,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119541125</v>
+        <v>119541177</v>
       </c>
       <c r="B100" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10693,25 +10693,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10721,10 +10721,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>811502</v>
+        <v>811607</v>
       </c>
       <c r="R100" t="n">
-        <v>7391976</v>
+        <v>7391859</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10783,10 +10783,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119541183</v>
+        <v>119541045</v>
       </c>
       <c r="B101" t="n">
-        <v>91834</v>
+        <v>91463</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -10799,21 +10799,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -10823,10 +10823,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>811180</v>
+        <v>811207</v>
       </c>
       <c r="R101" t="n">
-        <v>7391829</v>
+        <v>7391947</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10885,10 +10885,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119541177</v>
+        <v>119541056</v>
       </c>
       <c r="B102" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10901,21 +10901,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10925,10 +10925,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>811607</v>
+        <v>811402</v>
       </c>
       <c r="R102" t="n">
-        <v>7391859</v>
+        <v>7391791</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11293,10 +11293,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119541089</v>
+        <v>119541129</v>
       </c>
       <c r="B106" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11305,25 +11305,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11333,10 +11333,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>811635</v>
+        <v>811545</v>
       </c>
       <c r="R106" t="n">
-        <v>7391860</v>
+        <v>7391850</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11395,7 +11395,7 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119541092</v>
+        <v>119541089</v>
       </c>
       <c r="B107" t="n">
         <v>78263</v>
@@ -11435,10 +11435,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>811155</v>
+        <v>811635</v>
       </c>
       <c r="R107" t="n">
-        <v>7391931</v>
+        <v>7391860</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11497,10 +11497,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119541129</v>
+        <v>119541092</v>
       </c>
       <c r="B108" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11509,25 +11509,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11537,10 +11537,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>811545</v>
+        <v>811155</v>
       </c>
       <c r="R108" t="n">
-        <v>7391850</v>
+        <v>7391931</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -13441,10 +13441,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119541040</v>
+        <v>119541061</v>
       </c>
       <c r="B127" t="n">
-        <v>56522</v>
+        <v>91856</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13453,25 +13453,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>100138</v>
+        <v>2059</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13481,10 +13481,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>811186</v>
+        <v>811158</v>
       </c>
       <c r="R127" t="n">
-        <v>7391822</v>
+        <v>7391914</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13543,10 +13543,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>119541158</v>
+        <v>119541040</v>
       </c>
       <c r="B128" t="n">
-        <v>91840</v>
+        <v>56522</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13559,21 +13559,21 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13583,10 +13583,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>811003</v>
+        <v>811186</v>
       </c>
       <c r="R128" t="n">
-        <v>7392012</v>
+        <v>7391822</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13645,7 +13645,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>119541110</v>
+        <v>119541158</v>
       </c>
       <c r="B129" t="n">
         <v>91840</v>
@@ -13685,10 +13685,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>811189</v>
+        <v>811003</v>
       </c>
       <c r="R129" t="n">
-        <v>7391809</v>
+        <v>7392012</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13747,7 +13747,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119541113</v>
+        <v>119541110</v>
       </c>
       <c r="B130" t="n">
         <v>91840</v>
@@ -13787,10 +13787,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>811489</v>
+        <v>811189</v>
       </c>
       <c r="R130" t="n">
-        <v>7391792</v>
+        <v>7391809</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13849,7 +13849,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>119541117</v>
+        <v>119541113</v>
       </c>
       <c r="B131" t="n">
         <v>91840</v>
@@ -13889,10 +13889,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>811616</v>
+        <v>811489</v>
       </c>
       <c r="R131" t="n">
-        <v>7391803</v>
+        <v>7391792</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13951,7 +13951,7 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119541159</v>
+        <v>119541117</v>
       </c>
       <c r="B132" t="n">
         <v>91840</v>
@@ -13991,10 +13991,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>811018</v>
+        <v>811616</v>
       </c>
       <c r="R132" t="n">
-        <v>7392016</v>
+        <v>7391803</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14053,10 +14053,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>119541061</v>
+        <v>119541159</v>
       </c>
       <c r="B133" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14065,25 +14065,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14093,10 +14093,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>811158</v>
+        <v>811018</v>
       </c>
       <c r="R133" t="n">
-        <v>7391914</v>
+        <v>7392016</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -15073,10 +15073,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119541098</v>
+        <v>119541057</v>
       </c>
       <c r="B143" t="n">
-        <v>78262</v>
+        <v>91884</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15089,21 +15089,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6446</v>
+        <v>5449</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15113,10 +15113,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>811353</v>
+        <v>811123</v>
       </c>
       <c r="R143" t="n">
-        <v>7391859</v>
+        <v>7391919</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15175,10 +15175,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119541102</v>
+        <v>119541098</v>
       </c>
       <c r="B144" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15191,21 +15191,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15215,10 +15215,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>811751</v>
+        <v>811353</v>
       </c>
       <c r="R144" t="n">
-        <v>7391929</v>
+        <v>7391859</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15277,10 +15277,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119541146</v>
+        <v>119541102</v>
       </c>
       <c r="B145" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15289,25 +15289,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15317,10 +15317,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>811255</v>
+        <v>811751</v>
       </c>
       <c r="R145" t="n">
-        <v>7391871</v>
+        <v>7391929</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15379,7 +15379,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119541130</v>
+        <v>119541146</v>
       </c>
       <c r="B146" t="n">
         <v>91840</v>
@@ -15419,10 +15419,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>811571</v>
+        <v>811255</v>
       </c>
       <c r="R146" t="n">
-        <v>7391809</v>
+        <v>7391871</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15481,7 +15481,7 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119541164</v>
+        <v>119541130</v>
       </c>
       <c r="B147" t="n">
         <v>91840</v>
@@ -15521,10 +15521,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>810929</v>
+        <v>811571</v>
       </c>
       <c r="R147" t="n">
-        <v>7392042</v>
+        <v>7391809</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15583,10 +15583,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119541186</v>
+        <v>119541164</v>
       </c>
       <c r="B148" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15595,25 +15595,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15623,10 +15623,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>811144</v>
+        <v>810929</v>
       </c>
       <c r="R148" t="n">
-        <v>7391927</v>
+        <v>7392042</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15685,10 +15685,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119541057</v>
+        <v>119541186</v>
       </c>
       <c r="B149" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15701,21 +15701,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15725,10 +15725,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>811123</v>
+        <v>811144</v>
       </c>
       <c r="R149" t="n">
-        <v>7391919</v>
+        <v>7391927</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15787,10 +15787,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119541039</v>
+        <v>119541093</v>
       </c>
       <c r="B150" t="n">
-        <v>56522</v>
+        <v>78263</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15799,25 +15799,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15827,10 +15827,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>811215</v>
+        <v>811120</v>
       </c>
       <c r="R150" t="n">
-        <v>7391820</v>
+        <v>7391955</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16399,10 +16399,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119541093</v>
+        <v>119541039</v>
       </c>
       <c r="B156" t="n">
-        <v>78263</v>
+        <v>56522</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16411,25 +16411,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16439,10 +16439,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>811120</v>
+        <v>811215</v>
       </c>
       <c r="R156" t="n">
-        <v>7391955</v>
+        <v>7391820</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16909,10 +16909,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>119541180</v>
+        <v>119541035</v>
       </c>
       <c r="B161" t="n">
-        <v>91834</v>
+        <v>56522</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -16921,25 +16921,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>4362</v>
+        <v>100138</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16949,10 +16949,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>811501</v>
+        <v>811805</v>
       </c>
       <c r="R161" t="n">
-        <v>7391868</v>
+        <v>7391923</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17011,10 +17011,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>119541156</v>
+        <v>119541090</v>
       </c>
       <c r="B162" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17023,25 +17023,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17051,10 +17051,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>811039</v>
+        <v>811788</v>
       </c>
       <c r="R162" t="n">
-        <v>7391919</v>
+        <v>7391959</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17113,10 +17113,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>119541035</v>
+        <v>119541180</v>
       </c>
       <c r="B163" t="n">
-        <v>56522</v>
+        <v>91834</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17125,25 +17125,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100138</v>
+        <v>4362</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17153,10 +17153,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>811805</v>
+        <v>811501</v>
       </c>
       <c r="R163" t="n">
-        <v>7391923</v>
+        <v>7391868</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17215,10 +17215,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119541090</v>
+        <v>119541156</v>
       </c>
       <c r="B164" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17227,25 +17227,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17255,10 +17255,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>811788</v>
+        <v>811039</v>
       </c>
       <c r="R164" t="n">
-        <v>7391959</v>
+        <v>7391919</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17317,10 +17317,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119541116</v>
+        <v>119541079</v>
       </c>
       <c r="B165" t="n">
-        <v>91840</v>
+        <v>96868</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17333,21 +17333,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17357,10 +17357,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>811589</v>
+        <v>811182</v>
       </c>
       <c r="R165" t="n">
-        <v>7391777</v>
+        <v>7391854</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17419,7 +17419,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119541141</v>
+        <v>119541116</v>
       </c>
       <c r="B166" t="n">
         <v>91840</v>
@@ -17459,10 +17459,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>811243</v>
+        <v>811589</v>
       </c>
       <c r="R166" t="n">
-        <v>7391854</v>
+        <v>7391777</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17521,7 +17521,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119541137</v>
+        <v>119541141</v>
       </c>
       <c r="B167" t="n">
         <v>91840</v>
@@ -17561,10 +17561,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>811175</v>
+        <v>811243</v>
       </c>
       <c r="R167" t="n">
-        <v>7391841</v>
+        <v>7391854</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17623,10 +17623,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119541079</v>
+        <v>119541137</v>
       </c>
       <c r="B168" t="n">
-        <v>96868</v>
+        <v>91840</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17639,21 +17639,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17663,10 +17663,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>811182</v>
+        <v>811175</v>
       </c>
       <c r="R168" t="n">
-        <v>7391854</v>
+        <v>7391841</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -18439,10 +18439,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>119541065</v>
+        <v>119541168</v>
       </c>
       <c r="B176" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -18451,25 +18451,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18479,10 +18479,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>810977</v>
+        <v>811228</v>
       </c>
       <c r="R176" t="n">
-        <v>7392031</v>
+        <v>7391926</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18541,10 +18541,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>119541041</v>
+        <v>119541184</v>
       </c>
       <c r="B177" t="n">
-        <v>91826</v>
+        <v>91834</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -18557,21 +18557,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18581,10 +18581,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>810994</v>
+        <v>811258</v>
       </c>
       <c r="R177" t="n">
-        <v>7391976</v>
+        <v>7391832</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18643,10 +18643,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>119541029</v>
+        <v>119541041</v>
       </c>
       <c r="B178" t="n">
-        <v>79144</v>
+        <v>91826</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -18659,21 +18659,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>6453</v>
+        <v>3100</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18683,10 +18683,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>811120</v>
+        <v>810994</v>
       </c>
       <c r="R178" t="n">
-        <v>7391955</v>
+        <v>7391976</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18745,10 +18745,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>119541031</v>
+        <v>119541029</v>
       </c>
       <c r="B179" t="n">
-        <v>56522</v>
+        <v>79144</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -18757,25 +18757,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18785,10 +18785,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>811012</v>
+        <v>811120</v>
       </c>
       <c r="R179" t="n">
-        <v>7392154</v>
+        <v>7391955</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18815,12 +18815,12 @@
       </c>
       <c r="Y179" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA179" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD179" t="b">
@@ -18847,10 +18847,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>119541168</v>
+        <v>119541065</v>
       </c>
       <c r="B180" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -18859,25 +18859,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18887,10 +18887,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>811228</v>
+        <v>810977</v>
       </c>
       <c r="R180" t="n">
-        <v>7391926</v>
+        <v>7392031</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18949,10 +18949,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>119541184</v>
+        <v>119541031</v>
       </c>
       <c r="B181" t="n">
-        <v>91834</v>
+        <v>56522</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -18961,25 +18961,25 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>4362</v>
+        <v>100138</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18989,10 +18989,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>811258</v>
+        <v>811012</v>
       </c>
       <c r="R181" t="n">
-        <v>7391832</v>
+        <v>7392154</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19019,12 +19019,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19459,10 +19459,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>119541034</v>
+        <v>119541068</v>
       </c>
       <c r="B186" t="n">
-        <v>56522</v>
+        <v>91852</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -19475,21 +19475,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100138</v>
+        <v>4366</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19499,10 +19499,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>811472</v>
+        <v>811247</v>
       </c>
       <c r="R186" t="n">
-        <v>7391805</v>
+        <v>7391907</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19561,10 +19561,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>119541068</v>
+        <v>119541034</v>
       </c>
       <c r="B187" t="n">
-        <v>91852</v>
+        <v>56522</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -19577,21 +19577,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>4366</v>
+        <v>100138</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19601,10 +19601,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>811247</v>
+        <v>811472</v>
       </c>
       <c r="R187" t="n">
-        <v>7391907</v>
+        <v>7391805</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -22927,10 +22927,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>119541175</v>
+        <v>119541100</v>
       </c>
       <c r="B220" t="n">
-        <v>91834</v>
+        <v>78262</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -22943,21 +22943,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -22967,10 +22967,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>811484</v>
+        <v>811290</v>
       </c>
       <c r="R220" t="n">
-        <v>7391790</v>
+        <v>7391801</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23029,7 +23029,7 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>119541152</v>
+        <v>119541161</v>
       </c>
       <c r="B221" t="n">
         <v>91840</v>
@@ -23069,10 +23069,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>811128</v>
+        <v>811032</v>
       </c>
       <c r="R221" t="n">
-        <v>7391921</v>
+        <v>7392031</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23131,10 +23131,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119541100</v>
+        <v>119541175</v>
       </c>
       <c r="B222" t="n">
-        <v>78262</v>
+        <v>91834</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -23147,21 +23147,21 @@
         </is>
       </c>
       <c r="E222" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -23171,10 +23171,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>811290</v>
+        <v>811484</v>
       </c>
       <c r="R222" t="n">
-        <v>7391801</v>
+        <v>7391790</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23233,7 +23233,7 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>119541161</v>
+        <v>119541152</v>
       </c>
       <c r="B223" t="n">
         <v>91840</v>
@@ -23273,10 +23273,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>811032</v>
+        <v>811128</v>
       </c>
       <c r="R223" t="n">
-        <v>7392031</v>
+        <v>7391921</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23335,10 +23335,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>119541126</v>
+        <v>119541064</v>
       </c>
       <c r="B224" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -23347,25 +23347,25 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -23375,10 +23375,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>811473</v>
+        <v>811042</v>
       </c>
       <c r="R224" t="n">
-        <v>7391962</v>
+        <v>7391966</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23437,10 +23437,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>119541078</v>
+        <v>119541054</v>
       </c>
       <c r="B225" t="n">
-        <v>96868</v>
+        <v>91884</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -23449,25 +23449,25 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>221941</v>
+        <v>5449</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -23477,10 +23477,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>811192</v>
+        <v>811358</v>
       </c>
       <c r="R225" t="n">
-        <v>7391862</v>
+        <v>7391815</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23646,10 +23646,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>119541087</v>
+        <v>119541126</v>
       </c>
       <c r="B227" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -23658,25 +23658,25 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -23686,10 +23686,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>811167</v>
+        <v>811473</v>
       </c>
       <c r="R227" t="n">
-        <v>7391874</v>
+        <v>7391962</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23730,7 +23730,6 @@
       <c r="AE227" t="b">
         <v>0</v>
       </c>
-      <c r="AF227" t="inlineStr"/>
       <c r="AG227" t="b">
         <v>0</v>
       </c>
@@ -23749,10 +23748,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>119541095</v>
+        <v>119541078</v>
       </c>
       <c r="B228" t="n">
-        <v>78263</v>
+        <v>96868</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -23761,25 +23760,25 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E228" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -23789,10 +23788,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>811019</v>
+        <v>811192</v>
       </c>
       <c r="R228" t="n">
-        <v>7392058</v>
+        <v>7391862</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23851,10 +23850,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>119541051</v>
+        <v>119541087</v>
       </c>
       <c r="B229" t="n">
-        <v>90953</v>
+        <v>78263</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -23867,16 +23866,21 @@
         </is>
       </c>
       <c r="E229" t="n">
-        <v>6040162</v>
+        <v>228912</v>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -23886,10 +23890,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>811305</v>
+        <v>811167</v>
       </c>
       <c r="R229" t="n">
-        <v>7391791</v>
+        <v>7391874</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -23949,10 +23953,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>119541064</v>
+        <v>119541095</v>
       </c>
       <c r="B230" t="n">
-        <v>91856</v>
+        <v>78263</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -23965,21 +23969,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -23989,10 +23993,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>811042</v>
+        <v>811019</v>
       </c>
       <c r="R230" t="n">
-        <v>7391966</v>
+        <v>7392058</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24051,10 +24055,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>119541054</v>
+        <v>119541051</v>
       </c>
       <c r="B231" t="n">
-        <v>91884</v>
+        <v>90953</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -24067,21 +24071,16 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>5449</v>
-      </c>
-      <c r="F231" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -24091,10 +24090,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>811358</v>
+        <v>811305</v>
       </c>
       <c r="R231" t="n">
-        <v>7391815</v>
+        <v>7391791</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24135,6 +24134,7 @@
       <c r="AE231" t="b">
         <v>0</v>
       </c>
+      <c r="AF231" t="inlineStr"/>
       <c r="AG231" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 10151-2023 artfynd.xlsx
+++ b/artfynd/A 10151-2023 artfynd.xlsx
@@ -15787,10 +15787,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119541093</v>
+        <v>119541039</v>
       </c>
       <c r="B150" t="n">
-        <v>78263</v>
+        <v>56522</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15799,25 +15799,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15827,10 +15827,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>811120</v>
+        <v>811215</v>
       </c>
       <c r="R150" t="n">
-        <v>7391955</v>
+        <v>7391820</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -16399,10 +16399,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119541039</v>
+        <v>119541093</v>
       </c>
       <c r="B156" t="n">
-        <v>56522</v>
+        <v>78263</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16411,25 +16411,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16439,10 +16439,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>811215</v>
+        <v>811120</v>
       </c>
       <c r="R156" t="n">
-        <v>7391820</v>
+        <v>7391955</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16705,10 +16705,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>119541080</v>
+        <v>119541055</v>
       </c>
       <c r="B159" t="n">
-        <v>56525</v>
+        <v>91884</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16717,25 +16717,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>102613</v>
+        <v>5449</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16745,10 +16745,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>811181</v>
+        <v>811375</v>
       </c>
       <c r="R159" t="n">
-        <v>7391940</v>
+        <v>7391770</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16807,10 +16807,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>119541055</v>
+        <v>119541080</v>
       </c>
       <c r="B160" t="n">
-        <v>91884</v>
+        <v>56525</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16819,25 +16819,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>5449</v>
+        <v>102613</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16847,10 +16847,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>811375</v>
+        <v>811181</v>
       </c>
       <c r="R160" t="n">
-        <v>7391770</v>
+        <v>7391940</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16909,10 +16909,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>119541035</v>
+        <v>119541180</v>
       </c>
       <c r="B161" t="n">
-        <v>56522</v>
+        <v>91834</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -16921,25 +16921,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>100138</v>
+        <v>4362</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16949,10 +16949,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>811805</v>
+        <v>811501</v>
       </c>
       <c r="R161" t="n">
-        <v>7391923</v>
+        <v>7391868</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17011,10 +17011,10 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>119541090</v>
+        <v>119541156</v>
       </c>
       <c r="B162" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
@@ -17023,25 +17023,25 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
@@ -17051,10 +17051,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>811788</v>
+        <v>811039</v>
       </c>
       <c r="R162" t="n">
-        <v>7391959</v>
+        <v>7391919</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17113,10 +17113,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>119541180</v>
+        <v>119541035</v>
       </c>
       <c r="B163" t="n">
-        <v>91834</v>
+        <v>56522</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17125,25 +17125,25 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>4362</v>
+        <v>100138</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17153,10 +17153,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>811501</v>
+        <v>811805</v>
       </c>
       <c r="R163" t="n">
-        <v>7391868</v>
+        <v>7391923</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17215,10 +17215,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119541156</v>
+        <v>119541090</v>
       </c>
       <c r="B164" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17227,25 +17227,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17255,10 +17255,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>811039</v>
+        <v>811788</v>
       </c>
       <c r="R164" t="n">
-        <v>7391919</v>
+        <v>7391959</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17317,10 +17317,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119541079</v>
+        <v>119541116</v>
       </c>
       <c r="B165" t="n">
-        <v>96868</v>
+        <v>91840</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17333,21 +17333,21 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17357,10 +17357,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>811182</v>
+        <v>811589</v>
       </c>
       <c r="R165" t="n">
-        <v>7391854</v>
+        <v>7391777</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17419,7 +17419,7 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119541116</v>
+        <v>119541141</v>
       </c>
       <c r="B166" t="n">
         <v>91840</v>
@@ -17459,10 +17459,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>811589</v>
+        <v>811243</v>
       </c>
       <c r="R166" t="n">
-        <v>7391777</v>
+        <v>7391854</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17521,7 +17521,7 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119541141</v>
+        <v>119541137</v>
       </c>
       <c r="B167" t="n">
         <v>91840</v>
@@ -17561,10 +17561,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>811243</v>
+        <v>811175</v>
       </c>
       <c r="R167" t="n">
-        <v>7391854</v>
+        <v>7391841</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17623,10 +17623,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119541137</v>
+        <v>119541079</v>
       </c>
       <c r="B168" t="n">
-        <v>91840</v>
+        <v>96868</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17639,21 +17639,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17663,10 +17663,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>811175</v>
+        <v>811182</v>
       </c>
       <c r="R168" t="n">
-        <v>7391841</v>
+        <v>7391854</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19459,10 +19459,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>119541068</v>
+        <v>119541034</v>
       </c>
       <c r="B186" t="n">
-        <v>91852</v>
+        <v>56522</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -19475,21 +19475,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>4366</v>
+        <v>100138</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19499,10 +19499,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>811247</v>
+        <v>811472</v>
       </c>
       <c r="R186" t="n">
-        <v>7391907</v>
+        <v>7391805</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19561,10 +19561,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>119541034</v>
+        <v>119541068</v>
       </c>
       <c r="B187" t="n">
-        <v>56522</v>
+        <v>91852</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -19577,21 +19577,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>100138</v>
+        <v>4366</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19601,10 +19601,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>811472</v>
+        <v>811247</v>
       </c>
       <c r="R187" t="n">
-        <v>7391805</v>
+        <v>7391907</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -20173,10 +20173,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119541179</v>
+        <v>119541084</v>
       </c>
       <c r="B193" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -20189,21 +20189,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20213,10 +20213,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>811496</v>
+        <v>811768</v>
       </c>
       <c r="R193" t="n">
-        <v>7391933</v>
+        <v>7391938</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20275,10 +20275,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119541188</v>
+        <v>119541082</v>
       </c>
       <c r="B194" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -20291,21 +20291,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20315,10 +20315,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>811059</v>
+        <v>811354</v>
       </c>
       <c r="R194" t="n">
-        <v>7391942</v>
+        <v>7391857</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20377,10 +20377,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119541142</v>
+        <v>119541179</v>
       </c>
       <c r="B195" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -20389,25 +20389,25 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20417,10 +20417,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>811226</v>
+        <v>811496</v>
       </c>
       <c r="R195" t="n">
-        <v>7391836</v>
+        <v>7391933</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20479,7 +20479,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119541176</v>
+        <v>119541188</v>
       </c>
       <c r="B196" t="n">
         <v>91834</v>
@@ -20519,10 +20519,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>811608</v>
+        <v>811059</v>
       </c>
       <c r="R196" t="n">
-        <v>7391803</v>
+        <v>7391942</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20581,7 +20581,7 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119541138</v>
+        <v>119541142</v>
       </c>
       <c r="B197" t="n">
         <v>91840</v>
@@ -20621,10 +20621,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>811172</v>
+        <v>811226</v>
       </c>
       <c r="R197" t="n">
-        <v>7391843</v>
+        <v>7391836</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20683,10 +20683,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119541134</v>
+        <v>119541176</v>
       </c>
       <c r="B198" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -20695,25 +20695,25 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -20723,10 +20723,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>811445</v>
+        <v>811608</v>
       </c>
       <c r="R198" t="n">
-        <v>7391835</v>
+        <v>7391803</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20785,7 +20785,7 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119541112</v>
+        <v>119541138</v>
       </c>
       <c r="B199" t="n">
         <v>91840</v>
@@ -20825,10 +20825,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>811371</v>
+        <v>811172</v>
       </c>
       <c r="R199" t="n">
-        <v>7391863</v>
+        <v>7391843</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20887,10 +20887,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119541058</v>
+        <v>119541134</v>
       </c>
       <c r="B200" t="n">
-        <v>57326</v>
+        <v>91840</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -20899,25 +20899,25 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20927,10 +20927,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>811109</v>
+        <v>811445</v>
       </c>
       <c r="R200" t="n">
-        <v>7391871</v>
+        <v>7391835</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20989,10 +20989,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119541084</v>
+        <v>119541112</v>
       </c>
       <c r="B201" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21001,25 +21001,25 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21029,10 +21029,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>811768</v>
+        <v>811371</v>
       </c>
       <c r="R201" t="n">
-        <v>7391938</v>
+        <v>7391863</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21091,10 +21091,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119541082</v>
+        <v>119541058</v>
       </c>
       <c r="B202" t="n">
-        <v>91832</v>
+        <v>57326</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -21107,21 +21107,21 @@
         </is>
       </c>
       <c r="E202" t="n">
-        <v>4361</v>
+        <v>100049</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -21131,10 +21131,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>811354</v>
+        <v>811109</v>
       </c>
       <c r="R202" t="n">
-        <v>7391857</v>
+        <v>7391871</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>

--- a/artfynd/A 10151-2023 artfynd.xlsx
+++ b/artfynd/A 10151-2023 artfynd.xlsx
@@ -10273,10 +10273,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119541083</v>
+        <v>119541165</v>
       </c>
       <c r="B96" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10285,25 +10285,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10313,10 +10313,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>811752</v>
+        <v>810902</v>
       </c>
       <c r="R96" t="n">
-        <v>7391915</v>
+        <v>7392035</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10375,10 +10375,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119541104</v>
+        <v>119541137</v>
       </c>
       <c r="B97" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10387,25 +10387,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10415,10 +10415,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>811313</v>
+        <v>811175</v>
       </c>
       <c r="R97" t="n">
-        <v>7391795</v>
+        <v>7391841</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10477,7 +10477,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119541125</v>
+        <v>119541136</v>
       </c>
       <c r="B98" t="n">
         <v>91840</v>
@@ -10517,10 +10517,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>811502</v>
+        <v>811196</v>
       </c>
       <c r="R98" t="n">
-        <v>7391976</v>
+        <v>7391817</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10579,10 +10579,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119541183</v>
+        <v>119541152</v>
       </c>
       <c r="B99" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10591,25 +10591,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10619,10 +10619,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>811180</v>
+        <v>811128</v>
       </c>
       <c r="R99" t="n">
-        <v>7391829</v>
+        <v>7391921</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10681,10 +10681,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119541177</v>
+        <v>119541073</v>
       </c>
       <c r="B100" t="n">
-        <v>91834</v>
+        <v>96868</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10693,25 +10693,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10721,10 +10721,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>811607</v>
+        <v>811602</v>
       </c>
       <c r="R100" t="n">
-        <v>7391859</v>
+        <v>7391853</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10783,7 +10783,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119541045</v>
+        <v>119541049</v>
       </c>
       <c r="B101" t="n">
         <v>91463</v>
@@ -10823,10 +10823,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>811207</v>
+        <v>811251</v>
       </c>
       <c r="R101" t="n">
-        <v>7391947</v>
+        <v>7391796</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10885,10 +10885,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119541056</v>
+        <v>119541099</v>
       </c>
       <c r="B102" t="n">
-        <v>91884</v>
+        <v>78262</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10901,21 +10901,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5449</v>
+        <v>6446</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10925,10 +10925,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>811402</v>
+        <v>811540</v>
       </c>
       <c r="R102" t="n">
-        <v>7391791</v>
+        <v>7391755</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10987,10 +10987,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119541075</v>
+        <v>119541063</v>
       </c>
       <c r="B103" t="n">
-        <v>96868</v>
+        <v>91856</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -10999,25 +10999,25 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>221941</v>
+        <v>2059</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11027,10 +11027,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>811178</v>
+        <v>811474</v>
       </c>
       <c r="R103" t="n">
-        <v>7391829</v>
+        <v>7391808</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11089,10 +11089,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119541118</v>
+        <v>119541190</v>
       </c>
       <c r="B104" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11101,25 +11101,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11129,10 +11129,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>811600</v>
+        <v>811005</v>
       </c>
       <c r="R104" t="n">
-        <v>7391842</v>
+        <v>7391977</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11191,10 +11191,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119541071</v>
+        <v>119541173</v>
       </c>
       <c r="B105" t="n">
-        <v>96868</v>
+        <v>91834</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11203,25 +11203,25 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11231,10 +11231,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>811599</v>
+        <v>811366</v>
       </c>
       <c r="R105" t="n">
-        <v>7391829</v>
+        <v>7391825</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11293,10 +11293,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119541129</v>
+        <v>119541182</v>
       </c>
       <c r="B106" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11305,25 +11305,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11333,10 +11333,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>811545</v>
+        <v>811269</v>
       </c>
       <c r="R106" t="n">
-        <v>7391850</v>
+        <v>7391786</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11395,10 +11395,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119541089</v>
+        <v>119541047</v>
       </c>
       <c r="B107" t="n">
-        <v>78263</v>
+        <v>91463</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11411,21 +11411,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>228912</v>
+        <v>4745</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11435,10 +11435,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>811635</v>
+        <v>811768</v>
       </c>
       <c r="R107" t="n">
-        <v>7391860</v>
+        <v>7391938</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11497,10 +11497,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119541092</v>
+        <v>119541048</v>
       </c>
       <c r="B108" t="n">
-        <v>78263</v>
+        <v>91463</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11513,21 +11513,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>228912</v>
+        <v>4745</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11537,10 +11537,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>811155</v>
+        <v>811437</v>
       </c>
       <c r="R108" t="n">
-        <v>7391931</v>
+        <v>7391823</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11599,10 +11599,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119541165</v>
+        <v>119541100</v>
       </c>
       <c r="B109" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11611,25 +11611,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11639,10 +11639,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>810902</v>
+        <v>811290</v>
       </c>
       <c r="R109" t="n">
-        <v>7392035</v>
+        <v>7391801</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11701,10 +11701,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119541150</v>
+        <v>119541087</v>
       </c>
       <c r="B110" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11713,25 +11713,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11741,10 +11741,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>811181</v>
+        <v>811167</v>
       </c>
       <c r="R110" t="n">
-        <v>7391849</v>
+        <v>7391874</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11785,6 +11785,7 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11803,10 +11804,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119541163</v>
+        <v>119541093</v>
       </c>
       <c r="B111" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11815,25 +11816,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11843,10 +11844,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>810984</v>
+        <v>811120</v>
       </c>
       <c r="R111" t="n">
-        <v>7392025</v>
+        <v>7391955</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11905,10 +11906,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119541144</v>
+        <v>119541061</v>
       </c>
       <c r="B112" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -11917,25 +11918,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11945,10 +11946,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>811266</v>
+        <v>811158</v>
       </c>
       <c r="R112" t="n">
-        <v>7391829</v>
+        <v>7391914</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12007,10 +12008,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119541187</v>
+        <v>119541025</v>
       </c>
       <c r="B113" t="n">
-        <v>91834</v>
+        <v>91836</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12019,25 +12020,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4362</v>
+        <v>4363</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12047,10 +12048,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>811107</v>
+        <v>811673</v>
       </c>
       <c r="R113" t="n">
-        <v>7391952</v>
+        <v>7391865</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12109,10 +12110,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119541123</v>
+        <v>119541189</v>
       </c>
       <c r="B114" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12121,25 +12122,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12149,7 +12150,7 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>811693</v>
+        <v>811022</v>
       </c>
       <c r="R114" t="n">
         <v>7391895</v>
@@ -12211,10 +12212,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119541030</v>
+        <v>119541106</v>
       </c>
       <c r="B115" t="n">
-        <v>79115</v>
+        <v>78526</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12227,21 +12228,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12251,10 +12252,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>811122</v>
+        <v>810962</v>
       </c>
       <c r="R115" t="n">
-        <v>7391953</v>
+        <v>7392039</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12295,7 +12296,6 @@
       <c r="AE115" t="b">
         <v>0</v>
       </c>
-      <c r="AF115" t="inlineStr"/>
       <c r="AG115" t="b">
         <v>0</v>
       </c>
@@ -12314,10 +12314,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119541032</v>
+        <v>119541126</v>
       </c>
       <c r="B116" t="n">
-        <v>56522</v>
+        <v>91840</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12330,21 +12330,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12354,10 +12354,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>811213</v>
+        <v>811473</v>
       </c>
       <c r="R116" t="n">
-        <v>7391942</v>
+        <v>7391962</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12390,11 +12390,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12421,10 +12416,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119541048</v>
+        <v>119541141</v>
       </c>
       <c r="B117" t="n">
-        <v>91463</v>
+        <v>91840</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12433,25 +12428,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12461,10 +12456,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>811437</v>
+        <v>811243</v>
       </c>
       <c r="R117" t="n">
-        <v>7391823</v>
+        <v>7391854</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12523,10 +12518,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119541044</v>
+        <v>119541130</v>
       </c>
       <c r="B118" t="n">
-        <v>91463</v>
+        <v>91840</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12535,25 +12530,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12563,10 +12558,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>811162</v>
+        <v>811571</v>
       </c>
       <c r="R118" t="n">
-        <v>7391926</v>
+        <v>7391809</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12625,7 +12620,7 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119541139</v>
+        <v>119541155</v>
       </c>
       <c r="B119" t="n">
         <v>91840</v>
@@ -12665,10 +12660,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>811223</v>
+        <v>811049</v>
       </c>
       <c r="R119" t="n">
-        <v>7391823</v>
+        <v>7391928</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12727,7 +12722,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119541157</v>
+        <v>119541117</v>
       </c>
       <c r="B120" t="n">
         <v>91840</v>
@@ -12767,10 +12762,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>811006</v>
+        <v>811616</v>
       </c>
       <c r="R120" t="n">
-        <v>7391996</v>
+        <v>7391803</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12829,10 +12824,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119541091</v>
+        <v>119541159</v>
       </c>
       <c r="B121" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12841,25 +12836,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12869,10 +12864,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>811814</v>
+        <v>811018</v>
       </c>
       <c r="R121" t="n">
-        <v>7391907</v>
+        <v>7392016</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12931,10 +12926,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119541066</v>
+        <v>119541091</v>
       </c>
       <c r="B122" t="n">
-        <v>91852</v>
+        <v>78263</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -12943,25 +12938,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4366</v>
+        <v>228912</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12971,10 +12966,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>811361</v>
+        <v>811814</v>
       </c>
       <c r="R122" t="n">
-        <v>7391844</v>
+        <v>7391907</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13033,10 +13028,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119541148</v>
+        <v>119541029</v>
       </c>
       <c r="B123" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13045,25 +13040,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13073,10 +13068,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>811222</v>
+        <v>811120</v>
       </c>
       <c r="R123" t="n">
-        <v>7391892</v>
+        <v>7391955</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13135,7 +13130,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119541135</v>
+        <v>119541161</v>
       </c>
       <c r="B124" t="n">
         <v>91840</v>
@@ -13175,10 +13170,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>811304</v>
+        <v>811032</v>
       </c>
       <c r="R124" t="n">
-        <v>7391760</v>
+        <v>7392031</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13237,10 +13232,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119541143</v>
+        <v>119541068</v>
       </c>
       <c r="B125" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13253,21 +13248,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13277,10 +13272,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>811263</v>
+        <v>811247</v>
       </c>
       <c r="R125" t="n">
-        <v>7391814</v>
+        <v>7391907</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13339,10 +13334,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119541172</v>
+        <v>119541150</v>
       </c>
       <c r="B126" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13351,25 +13346,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13379,10 +13374,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>811367</v>
+        <v>811181</v>
       </c>
       <c r="R126" t="n">
-        <v>7391855</v>
+        <v>7391849</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13441,10 +13436,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119541061</v>
+        <v>119541147</v>
       </c>
       <c r="B127" t="n">
-        <v>91856</v>
+        <v>91840</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13453,25 +13448,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13481,10 +13476,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>811158</v>
+        <v>811248</v>
       </c>
       <c r="R127" t="n">
-        <v>7391914</v>
+        <v>7391873</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13543,10 +13538,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>119541040</v>
+        <v>119541054</v>
       </c>
       <c r="B128" t="n">
-        <v>56522</v>
+        <v>91884</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13555,25 +13550,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>100138</v>
+        <v>5449</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13583,10 +13578,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>811186</v>
+        <v>811358</v>
       </c>
       <c r="R128" t="n">
-        <v>7391822</v>
+        <v>7391815</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13645,7 +13640,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>119541158</v>
+        <v>119541118</v>
       </c>
       <c r="B129" t="n">
         <v>91840</v>
@@ -13685,10 +13680,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>811003</v>
+        <v>811600</v>
       </c>
       <c r="R129" t="n">
-        <v>7392012</v>
+        <v>7391842</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13747,7 +13742,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119541110</v>
+        <v>119541124</v>
       </c>
       <c r="B130" t="n">
         <v>91840</v>
@@ -13787,10 +13782,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>811189</v>
+        <v>811523</v>
       </c>
       <c r="R130" t="n">
-        <v>7391809</v>
+        <v>7391986</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13849,7 +13844,7 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>119541113</v>
+        <v>119541164</v>
       </c>
       <c r="B131" t="n">
         <v>91840</v>
@@ -13889,10 +13884,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>811489</v>
+        <v>810929</v>
       </c>
       <c r="R131" t="n">
-        <v>7391792</v>
+        <v>7392042</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13951,10 +13946,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119541117</v>
+        <v>119541066</v>
       </c>
       <c r="B132" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -13967,21 +13962,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13991,10 +13986,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>811616</v>
+        <v>811361</v>
       </c>
       <c r="R132" t="n">
-        <v>7391803</v>
+        <v>7391844</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14053,10 +14048,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>119541159</v>
+        <v>119541083</v>
       </c>
       <c r="B133" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14065,25 +14060,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14093,10 +14088,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>811018</v>
+        <v>811752</v>
       </c>
       <c r="R133" t="n">
-        <v>7392016</v>
+        <v>7391915</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14155,10 +14150,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>119541181</v>
+        <v>119541084</v>
       </c>
       <c r="B134" t="n">
-        <v>91834</v>
+        <v>91832</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14171,21 +14166,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4362</v>
+        <v>4361</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14195,10 +14190,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>811465</v>
+        <v>811768</v>
       </c>
       <c r="R134" t="n">
-        <v>7391838</v>
+        <v>7391938</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14257,10 +14252,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>119541178</v>
+        <v>119541112</v>
       </c>
       <c r="B135" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14269,25 +14264,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14297,10 +14292,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>811475</v>
+        <v>811371</v>
       </c>
       <c r="R135" t="n">
-        <v>7391925</v>
+        <v>7391863</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14359,10 +14354,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119541151</v>
+        <v>119541040</v>
       </c>
       <c r="B136" t="n">
-        <v>91840</v>
+        <v>56522</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14375,21 +14370,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14399,10 +14394,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>811142</v>
+        <v>811186</v>
       </c>
       <c r="R136" t="n">
-        <v>7391892</v>
+        <v>7391822</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14461,10 +14456,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119541122</v>
+        <v>119541102</v>
       </c>
       <c r="B137" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14473,25 +14468,25 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14501,7 +14496,7 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>811803</v>
+        <v>811751</v>
       </c>
       <c r="R137" t="n">
         <v>7391929</v>
@@ -14563,7 +14558,7 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119541147</v>
+        <v>119541115</v>
       </c>
       <c r="B138" t="n">
         <v>91840</v>
@@ -14603,10 +14598,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>811248</v>
+        <v>811544</v>
       </c>
       <c r="R138" t="n">
-        <v>7391873</v>
+        <v>7391770</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14665,10 +14660,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119541060</v>
+        <v>119541129</v>
       </c>
       <c r="B139" t="n">
-        <v>57326</v>
+        <v>91840</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14677,25 +14672,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14705,10 +14700,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>811547</v>
+        <v>811545</v>
       </c>
       <c r="R139" t="n">
-        <v>7391873</v>
+        <v>7391850</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14767,10 +14762,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119541096</v>
+        <v>119541075</v>
       </c>
       <c r="B140" t="n">
-        <v>78263</v>
+        <v>96868</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
@@ -14779,25 +14774,25 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -14807,10 +14802,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>810955</v>
+        <v>811178</v>
       </c>
       <c r="R140" t="n">
-        <v>7392033</v>
+        <v>7391829</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14869,10 +14864,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119541086</v>
+        <v>119541030</v>
       </c>
       <c r="B141" t="n">
-        <v>91832</v>
+        <v>79115</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -14885,21 +14880,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>4361</v>
+        <v>229821</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14909,10 +14904,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>811036</v>
+        <v>811122</v>
       </c>
       <c r="R141" t="n">
-        <v>7391909</v>
+        <v>7391953</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14953,6 +14948,7 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -14971,10 +14967,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119541106</v>
+        <v>119541078</v>
       </c>
       <c r="B142" t="n">
-        <v>78526</v>
+        <v>96868</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -14983,25 +14979,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15011,10 +15007,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>810962</v>
+        <v>811192</v>
       </c>
       <c r="R142" t="n">
-        <v>7392039</v>
+        <v>7391862</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15073,10 +15069,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119541057</v>
+        <v>119541172</v>
       </c>
       <c r="B143" t="n">
-        <v>91884</v>
+        <v>91834</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15089,21 +15085,21 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5449</v>
+        <v>4362</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15113,10 +15109,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>811123</v>
+        <v>811367</v>
       </c>
       <c r="R143" t="n">
-        <v>7391919</v>
+        <v>7391855</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15175,10 +15171,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119541098</v>
+        <v>119541104</v>
       </c>
       <c r="B144" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15191,21 +15187,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15215,10 +15211,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>811353</v>
+        <v>811313</v>
       </c>
       <c r="R144" t="n">
-        <v>7391859</v>
+        <v>7391795</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15277,10 +15273,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119541102</v>
+        <v>119541138</v>
       </c>
       <c r="B145" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15289,25 +15285,25 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15317,10 +15313,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>811751</v>
+        <v>811172</v>
       </c>
       <c r="R145" t="n">
-        <v>7391929</v>
+        <v>7391843</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15379,7 +15375,7 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119541146</v>
+        <v>119541119</v>
       </c>
       <c r="B146" t="n">
         <v>91840</v>
@@ -15419,10 +15415,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>811255</v>
+        <v>811661</v>
       </c>
       <c r="R146" t="n">
-        <v>7391871</v>
+        <v>7391873</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15481,10 +15477,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119541130</v>
+        <v>119541080</v>
       </c>
       <c r="B147" t="n">
-        <v>91840</v>
+        <v>56525</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15497,21 +15493,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4364</v>
+        <v>102613</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15521,10 +15517,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>811571</v>
+        <v>811181</v>
       </c>
       <c r="R147" t="n">
-        <v>7391809</v>
+        <v>7391940</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15583,10 +15579,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119541164</v>
+        <v>119541038</v>
       </c>
       <c r="B148" t="n">
-        <v>91840</v>
+        <v>56522</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15599,21 +15595,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15623,10 +15619,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>810929</v>
+        <v>811354</v>
       </c>
       <c r="R148" t="n">
-        <v>7392042</v>
+        <v>7391760</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15685,10 +15681,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119541186</v>
+        <v>119541076</v>
       </c>
       <c r="B149" t="n">
-        <v>91834</v>
+        <v>96868</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15697,25 +15693,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15725,10 +15721,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>811144</v>
+        <v>811175</v>
       </c>
       <c r="R149" t="n">
-        <v>7391927</v>
+        <v>7391844</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15787,10 +15783,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119541039</v>
+        <v>119541046</v>
       </c>
       <c r="B150" t="n">
-        <v>56522</v>
+        <v>91463</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15799,25 +15795,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>100138</v>
+        <v>4745</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15827,10 +15823,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>811215</v>
+        <v>811712</v>
       </c>
       <c r="R150" t="n">
-        <v>7391820</v>
+        <v>7391868</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15889,10 +15885,10 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119541103</v>
+        <v>119541142</v>
       </c>
       <c r="B151" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
@@ -15901,25 +15897,25 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
@@ -15929,10 +15925,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>811689</v>
+        <v>811226</v>
       </c>
       <c r="R151" t="n">
-        <v>7391899</v>
+        <v>7391836</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15991,7 +15987,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119541149</v>
+        <v>119541148</v>
       </c>
       <c r="B152" t="n">
         <v>91840</v>
@@ -16031,10 +16027,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>811213</v>
+        <v>811222</v>
       </c>
       <c r="R152" t="n">
-        <v>7391876</v>
+        <v>7391892</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16093,7 +16089,7 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119541127</v>
+        <v>119541134</v>
       </c>
       <c r="B153" t="n">
         <v>91840</v>
@@ -16133,10 +16129,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>811557</v>
+        <v>811445</v>
       </c>
       <c r="R153" t="n">
-        <v>7391884</v>
+        <v>7391835</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16195,10 +16191,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119541107</v>
+        <v>119541058</v>
       </c>
       <c r="B154" t="n">
-        <v>91840</v>
+        <v>57326</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16207,25 +16203,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16235,10 +16231,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>811147</v>
+        <v>811109</v>
       </c>
       <c r="R154" t="n">
-        <v>7391914</v>
+        <v>7391871</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16297,7 +16293,7 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119541132</v>
+        <v>119541149</v>
       </c>
       <c r="B155" t="n">
         <v>91840</v>
@@ -16337,10 +16333,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>811532</v>
+        <v>811213</v>
       </c>
       <c r="R155" t="n">
-        <v>7391774</v>
+        <v>7391876</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16399,10 +16395,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119541093</v>
+        <v>119541146</v>
       </c>
       <c r="B156" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16411,25 +16407,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16439,10 +16435,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>811120</v>
+        <v>811255</v>
       </c>
       <c r="R156" t="n">
-        <v>7391955</v>
+        <v>7391871</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16501,10 +16497,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>119541190</v>
+        <v>119541060</v>
       </c>
       <c r="B157" t="n">
-        <v>91834</v>
+        <v>57326</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16517,21 +16513,21 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>4362</v>
+        <v>100049</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16541,10 +16537,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>811005</v>
+        <v>811547</v>
       </c>
       <c r="R157" t="n">
-        <v>7391977</v>
+        <v>7391873</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16603,10 +16599,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>119541136</v>
+        <v>119541077</v>
       </c>
       <c r="B158" t="n">
-        <v>91840</v>
+        <v>96868</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16619,21 +16615,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16646,7 +16642,7 @@
         <v>811196</v>
       </c>
       <c r="R158" t="n">
-        <v>7391817</v>
+        <v>7391824</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16705,10 +16701,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>119541055</v>
+        <v>119541081</v>
       </c>
       <c r="B159" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16721,21 +16717,21 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16745,10 +16741,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>811375</v>
+        <v>811187</v>
       </c>
       <c r="R159" t="n">
-        <v>7391770</v>
+        <v>7391879</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16807,10 +16803,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>119541080</v>
+        <v>119541187</v>
       </c>
       <c r="B160" t="n">
-        <v>56525</v>
+        <v>91834</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16819,25 +16815,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>102613</v>
+        <v>4362</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16847,10 +16843,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>811181</v>
+        <v>811107</v>
       </c>
       <c r="R160" t="n">
-        <v>7391940</v>
+        <v>7391952</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16909,10 +16905,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>119541180</v>
+        <v>119541055</v>
       </c>
       <c r="B161" t="n">
-        <v>91834</v>
+        <v>91884</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -16925,21 +16921,21 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>4362</v>
+        <v>5449</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16949,10 +16945,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>811501</v>
+        <v>811375</v>
       </c>
       <c r="R161" t="n">
-        <v>7391868</v>
+        <v>7391770</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17011,7 +17007,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>119541156</v>
+        <v>119541116</v>
       </c>
       <c r="B162" t="n">
         <v>91840</v>
@@ -17051,10 +17047,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>811039</v>
+        <v>811589</v>
       </c>
       <c r="R162" t="n">
-        <v>7391919</v>
+        <v>7391777</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17113,10 +17109,10 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>119541035</v>
+        <v>119541151</v>
       </c>
       <c r="B163" t="n">
-        <v>56522</v>
+        <v>91840</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
@@ -17129,21 +17125,21 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
@@ -17153,10 +17149,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>811805</v>
+        <v>811142</v>
       </c>
       <c r="R163" t="n">
-        <v>7391923</v>
+        <v>7391892</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17215,10 +17211,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119541090</v>
+        <v>119541122</v>
       </c>
       <c r="B164" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17227,25 +17223,25 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17255,10 +17251,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>811788</v>
+        <v>811803</v>
       </c>
       <c r="R164" t="n">
-        <v>7391959</v>
+        <v>7391929</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17317,7 +17313,7 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119541116</v>
+        <v>119541131</v>
       </c>
       <c r="B165" t="n">
         <v>91840</v>
@@ -17357,10 +17353,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>811589</v>
+        <v>811559</v>
       </c>
       <c r="R165" t="n">
-        <v>7391777</v>
+        <v>7391807</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17419,10 +17415,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119541141</v>
+        <v>119541176</v>
       </c>
       <c r="B166" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17431,25 +17427,25 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17459,10 +17455,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>811243</v>
+        <v>811608</v>
       </c>
       <c r="R166" t="n">
-        <v>7391854</v>
+        <v>7391803</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17521,10 +17517,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119541137</v>
+        <v>119541085</v>
       </c>
       <c r="B167" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17533,25 +17529,25 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17561,10 +17557,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>811175</v>
+        <v>811445</v>
       </c>
       <c r="R167" t="n">
-        <v>7391841</v>
+        <v>7391835</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17623,10 +17619,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119541079</v>
+        <v>119541086</v>
       </c>
       <c r="B168" t="n">
-        <v>96868</v>
+        <v>91832</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17635,25 +17631,25 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>221941</v>
+        <v>4361</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17663,10 +17659,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>811182</v>
+        <v>811036</v>
       </c>
       <c r="R168" t="n">
-        <v>7391854</v>
+        <v>7391909</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17725,10 +17721,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119541049</v>
+        <v>119541057</v>
       </c>
       <c r="B169" t="n">
-        <v>91463</v>
+        <v>91884</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17741,21 +17737,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>4745</v>
+        <v>5449</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17765,10 +17761,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>811251</v>
+        <v>811123</v>
       </c>
       <c r="R169" t="n">
-        <v>7391796</v>
+        <v>7391919</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17827,10 +17823,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>119541120</v>
+        <v>119541101</v>
       </c>
       <c r="B170" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -17839,25 +17835,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17867,10 +17863,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>811720</v>
+        <v>811120</v>
       </c>
       <c r="R170" t="n">
-        <v>7391872</v>
+        <v>7391955</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17929,7 +17925,7 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>119541124</v>
+        <v>119541158</v>
       </c>
       <c r="B171" t="n">
         <v>91840</v>
@@ -17969,10 +17965,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>811523</v>
+        <v>811003</v>
       </c>
       <c r="R171" t="n">
-        <v>7391986</v>
+        <v>7392012</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18031,10 +18027,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>119541173</v>
+        <v>119541074</v>
       </c>
       <c r="B172" t="n">
-        <v>91834</v>
+        <v>96868</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18043,25 +18039,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18071,10 +18067,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>811366</v>
+        <v>811554</v>
       </c>
       <c r="R172" t="n">
-        <v>7391825</v>
+        <v>7391879</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18133,10 +18129,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>119541119</v>
+        <v>119541064</v>
       </c>
       <c r="B173" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18145,25 +18141,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18173,10 +18169,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>811661</v>
+        <v>811042</v>
       </c>
       <c r="R173" t="n">
-        <v>7391873</v>
+        <v>7391966</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18235,10 +18231,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>119541162</v>
+        <v>119541181</v>
       </c>
       <c r="B174" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18247,25 +18243,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18275,10 +18271,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>811007</v>
+        <v>811465</v>
       </c>
       <c r="R174" t="n">
-        <v>7392021</v>
+        <v>7391838</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18337,10 +18333,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>119541063</v>
+        <v>119541039</v>
       </c>
       <c r="B175" t="n">
-        <v>91856</v>
+        <v>56522</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18349,25 +18345,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>2059</v>
+        <v>100138</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18377,10 +18373,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>811474</v>
+        <v>811215</v>
       </c>
       <c r="R175" t="n">
-        <v>7391808</v>
+        <v>7391820</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18439,10 +18435,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>119541168</v>
+        <v>119541034</v>
       </c>
       <c r="B176" t="n">
-        <v>91834</v>
+        <v>56522</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -18451,25 +18447,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>4362</v>
+        <v>100138</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18479,10 +18475,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>811228</v>
+        <v>811472</v>
       </c>
       <c r="R176" t="n">
-        <v>7391926</v>
+        <v>7391805</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18541,10 +18537,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>119541184</v>
+        <v>119541069</v>
       </c>
       <c r="B177" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -18553,25 +18549,25 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E177" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18581,10 +18577,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>811258</v>
+        <v>811140</v>
       </c>
       <c r="R177" t="n">
-        <v>7391832</v>
+        <v>7391897</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18643,10 +18639,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>119541041</v>
+        <v>119541184</v>
       </c>
       <c r="B178" t="n">
-        <v>91826</v>
+        <v>91834</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -18659,21 +18655,21 @@
         </is>
       </c>
       <c r="E178" t="n">
-        <v>3100</v>
+        <v>4362</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18683,10 +18679,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>810994</v>
+        <v>811258</v>
       </c>
       <c r="R178" t="n">
-        <v>7391976</v>
+        <v>7391832</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18745,10 +18741,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>119541029</v>
+        <v>119541056</v>
       </c>
       <c r="B179" t="n">
-        <v>79144</v>
+        <v>91884</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -18761,21 +18757,21 @@
         </is>
       </c>
       <c r="E179" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18785,10 +18781,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>811120</v>
+        <v>811402</v>
       </c>
       <c r="R179" t="n">
-        <v>7391955</v>
+        <v>7391791</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18847,10 +18843,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>119541065</v>
+        <v>119541105</v>
       </c>
       <c r="B180" t="n">
-        <v>91852</v>
+        <v>78526</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -18859,25 +18855,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18887,10 +18883,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>810977</v>
+        <v>811251</v>
       </c>
       <c r="R180" t="n">
-        <v>7392031</v>
+        <v>7391852</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18949,10 +18945,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>119541031</v>
+        <v>119541139</v>
       </c>
       <c r="B181" t="n">
-        <v>56522</v>
+        <v>91840</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -18965,21 +18961,21 @@
         </is>
       </c>
       <c r="E181" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18989,10 +18985,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>811012</v>
+        <v>811223</v>
       </c>
       <c r="R181" t="n">
-        <v>7392154</v>
+        <v>7391823</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19019,12 +19015,12 @@
       </c>
       <c r="Y181" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA181" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD181" t="b">
@@ -19051,10 +19047,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119541069</v>
+        <v>119541033</v>
       </c>
       <c r="B182" t="n">
-        <v>91852</v>
+        <v>56522</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19067,21 +19063,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>4366</v>
+        <v>100138</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19091,10 +19087,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>811140</v>
+        <v>811505</v>
       </c>
       <c r="R182" t="n">
-        <v>7391897</v>
+        <v>7391980</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19127,6 +19123,11 @@
       <c r="AA182" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC182" t="inlineStr">
+        <is>
+          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19153,10 +19154,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>119541099</v>
+        <v>119541114</v>
       </c>
       <c r="B183" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19165,25 +19166,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19193,10 +19194,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>811540</v>
+        <v>811522</v>
       </c>
       <c r="R183" t="n">
-        <v>7391755</v>
+        <v>7391777</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19255,10 +19256,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>119541174</v>
+        <v>119541127</v>
       </c>
       <c r="B184" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -19267,25 +19268,25 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19295,10 +19296,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>811427</v>
+        <v>811557</v>
       </c>
       <c r="R184" t="n">
-        <v>7391805</v>
+        <v>7391884</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19357,10 +19358,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>119541073</v>
+        <v>119541157</v>
       </c>
       <c r="B185" t="n">
-        <v>96868</v>
+        <v>91840</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -19373,21 +19374,21 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19397,10 +19398,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>811602</v>
+        <v>811006</v>
       </c>
       <c r="R185" t="n">
-        <v>7391853</v>
+        <v>7391996</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19459,10 +19460,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>119541034</v>
+        <v>119541156</v>
       </c>
       <c r="B186" t="n">
-        <v>56522</v>
+        <v>91840</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -19475,21 +19476,21 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19499,10 +19500,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>811472</v>
+        <v>811039</v>
       </c>
       <c r="R186" t="n">
-        <v>7391805</v>
+        <v>7391919</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19561,10 +19562,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>119541068</v>
+        <v>119541079</v>
       </c>
       <c r="B187" t="n">
-        <v>91852</v>
+        <v>96868</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -19577,21 +19578,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>4366</v>
+        <v>221941</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19601,10 +19602,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>811247</v>
+        <v>811182</v>
       </c>
       <c r="R187" t="n">
-        <v>7391907</v>
+        <v>7391854</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19663,10 +19664,10 @@
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>119541115</v>
+        <v>119541168</v>
       </c>
       <c r="B188" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
@@ -19675,25 +19676,25 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I188" t="inlineStr"/>
@@ -19703,10 +19704,10 @@
         </is>
       </c>
       <c r="Q188" t="n">
-        <v>811544</v>
+        <v>811228</v>
       </c>
       <c r="R188" t="n">
-        <v>7391770</v>
+        <v>7391926</v>
       </c>
       <c r="S188" t="n">
         <v>10</v>
@@ -19765,10 +19766,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119541155</v>
+        <v>119541174</v>
       </c>
       <c r="B189" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -19777,25 +19778,25 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19805,10 +19806,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>811049</v>
+        <v>811427</v>
       </c>
       <c r="R189" t="n">
-        <v>7391928</v>
+        <v>7391805</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19867,10 +19868,10 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119541025</v>
+        <v>119541163</v>
       </c>
       <c r="B190" t="n">
-        <v>91836</v>
+        <v>91840</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
@@ -19883,21 +19884,21 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>4363</v>
+        <v>4364</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I190" t="inlineStr"/>
@@ -19907,10 +19908,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>811673</v>
+        <v>810984</v>
       </c>
       <c r="R190" t="n">
-        <v>7391865</v>
+        <v>7392025</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19969,10 +19970,10 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119541182</v>
+        <v>119541143</v>
       </c>
       <c r="B191" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -19981,25 +19982,25 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E191" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I191" t="inlineStr"/>
@@ -20009,10 +20010,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>811269</v>
+        <v>811263</v>
       </c>
       <c r="R191" t="n">
-        <v>7391786</v>
+        <v>7391814</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20071,7 +20072,7 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119541153</v>
+        <v>119541107</v>
       </c>
       <c r="B192" t="n">
         <v>91840</v>
@@ -20114,7 +20115,7 @@
         <v>811147</v>
       </c>
       <c r="R192" t="n">
-        <v>7391936</v>
+        <v>7391914</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20173,10 +20174,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119541084</v>
+        <v>119541162</v>
       </c>
       <c r="B193" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -20185,25 +20186,25 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20213,10 +20214,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>811768</v>
+        <v>811007</v>
       </c>
       <c r="R193" t="n">
-        <v>7391938</v>
+        <v>7392021</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20275,10 +20276,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119541082</v>
+        <v>119541179</v>
       </c>
       <c r="B194" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -20291,21 +20292,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20315,10 +20316,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>811354</v>
+        <v>811496</v>
       </c>
       <c r="R194" t="n">
-        <v>7391857</v>
+        <v>7391933</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20377,7 +20378,7 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119541179</v>
+        <v>119541188</v>
       </c>
       <c r="B195" t="n">
         <v>91834</v>
@@ -20417,10 +20418,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>811496</v>
+        <v>811059</v>
       </c>
       <c r="R195" t="n">
-        <v>7391933</v>
+        <v>7391942</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20479,7 +20480,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119541188</v>
+        <v>119541178</v>
       </c>
       <c r="B196" t="n">
         <v>91834</v>
@@ -20519,10 +20520,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>811059</v>
+        <v>811475</v>
       </c>
       <c r="R196" t="n">
-        <v>7391942</v>
+        <v>7391925</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20581,10 +20582,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119541142</v>
+        <v>119541035</v>
       </c>
       <c r="B197" t="n">
-        <v>91840</v>
+        <v>56522</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -20597,21 +20598,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20621,10 +20622,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>811226</v>
+        <v>811805</v>
       </c>
       <c r="R197" t="n">
-        <v>7391836</v>
+        <v>7391923</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20683,10 +20684,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119541176</v>
+        <v>119541095</v>
       </c>
       <c r="B198" t="n">
-        <v>91834</v>
+        <v>78263</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -20699,21 +20700,21 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>4362</v>
+        <v>228912</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -20723,10 +20724,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>811608</v>
+        <v>811019</v>
       </c>
       <c r="R198" t="n">
-        <v>7391803</v>
+        <v>7392058</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20785,10 +20786,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119541138</v>
+        <v>119541092</v>
       </c>
       <c r="B199" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -20797,25 +20798,25 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -20825,10 +20826,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>811172</v>
+        <v>811155</v>
       </c>
       <c r="R199" t="n">
-        <v>7391843</v>
+        <v>7391931</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20887,10 +20888,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119541134</v>
+        <v>119541070</v>
       </c>
       <c r="B200" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -20903,21 +20904,21 @@
         </is>
       </c>
       <c r="E200" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20927,10 +20928,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>811445</v>
+        <v>810940</v>
       </c>
       <c r="R200" t="n">
-        <v>7391835</v>
+        <v>7392041</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20989,7 +20990,7 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119541112</v>
+        <v>119541154</v>
       </c>
       <c r="B201" t="n">
         <v>91840</v>
@@ -21029,10 +21030,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>811371</v>
+        <v>811034</v>
       </c>
       <c r="R201" t="n">
-        <v>7391863</v>
+        <v>7391905</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21091,10 +21092,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119541058</v>
+        <v>119541113</v>
       </c>
       <c r="B202" t="n">
-        <v>57326</v>
+        <v>91840</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -21103,25 +21104,25 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -21131,10 +21132,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>811109</v>
+        <v>811489</v>
       </c>
       <c r="R202" t="n">
-        <v>7391871</v>
+        <v>7391792</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21193,10 +21194,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119541046</v>
+        <v>119541183</v>
       </c>
       <c r="B203" t="n">
-        <v>91463</v>
+        <v>91834</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -21209,21 +21210,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -21233,10 +21234,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>811712</v>
+        <v>811180</v>
       </c>
       <c r="R203" t="n">
-        <v>7391868</v>
+        <v>7391829</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21295,10 +21296,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>119541043</v>
+        <v>119541177</v>
       </c>
       <c r="B204" t="n">
-        <v>91463</v>
+        <v>91834</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -21311,21 +21312,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -21335,10 +21336,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>811147</v>
+        <v>811607</v>
       </c>
       <c r="R204" t="n">
-        <v>7391872</v>
+        <v>7391859</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21397,7 +21398,7 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>119541047</v>
+        <v>119541043</v>
       </c>
       <c r="B205" t="n">
         <v>91463</v>
@@ -21437,10 +21438,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>811768</v>
+        <v>811147</v>
       </c>
       <c r="R205" t="n">
-        <v>7391938</v>
+        <v>7391872</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21499,10 +21500,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>119541101</v>
+        <v>119541045</v>
       </c>
       <c r="B206" t="n">
-        <v>78262</v>
+        <v>91463</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -21515,21 +21516,21 @@
         </is>
       </c>
       <c r="E206" t="n">
-        <v>6446</v>
+        <v>4745</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -21539,10 +21540,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>811120</v>
+        <v>811207</v>
       </c>
       <c r="R206" t="n">
-        <v>7391955</v>
+        <v>7391947</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21601,10 +21602,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>119541105</v>
+        <v>119541044</v>
       </c>
       <c r="B207" t="n">
-        <v>78526</v>
+        <v>91463</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -21617,21 +21618,21 @@
         </is>
       </c>
       <c r="E207" t="n">
-        <v>6425</v>
+        <v>4745</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -21641,10 +21642,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>811251</v>
+        <v>811162</v>
       </c>
       <c r="R207" t="n">
-        <v>7391852</v>
+        <v>7391926</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21703,10 +21704,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119541154</v>
+        <v>119541103</v>
       </c>
       <c r="B208" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -21715,25 +21716,25 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -21743,10 +21744,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>811034</v>
+        <v>811689</v>
       </c>
       <c r="R208" t="n">
-        <v>7391905</v>
+        <v>7391899</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21805,10 +21806,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119541114</v>
+        <v>119541090</v>
       </c>
       <c r="B209" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -21817,25 +21818,25 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E209" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -21845,10 +21846,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>811522</v>
+        <v>811788</v>
       </c>
       <c r="R209" t="n">
-        <v>7391777</v>
+        <v>7391959</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21907,10 +21908,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>119541189</v>
+        <v>119541071</v>
       </c>
       <c r="B210" t="n">
-        <v>91834</v>
+        <v>96868</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -21919,25 +21920,25 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>4362</v>
+        <v>221941</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -21947,10 +21948,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>811022</v>
+        <v>811599</v>
       </c>
       <c r="R210" t="n">
-        <v>7391895</v>
+        <v>7391829</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22009,10 +22010,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>119541131</v>
+        <v>119541098</v>
       </c>
       <c r="B211" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22021,25 +22022,25 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -22049,10 +22050,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>811559</v>
+        <v>811353</v>
       </c>
       <c r="R211" t="n">
-        <v>7391807</v>
+        <v>7391859</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22111,10 +22112,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>119541076</v>
+        <v>119541120</v>
       </c>
       <c r="B212" t="n">
-        <v>96868</v>
+        <v>91840</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -22127,21 +22128,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -22151,10 +22152,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>811175</v>
+        <v>811720</v>
       </c>
       <c r="R212" t="n">
-        <v>7391844</v>
+        <v>7391872</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22213,10 +22214,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>119541077</v>
+        <v>119541065</v>
       </c>
       <c r="B213" t="n">
-        <v>96868</v>
+        <v>91852</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -22229,21 +22230,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>221941</v>
+        <v>4366</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -22253,10 +22254,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>811196</v>
+        <v>810977</v>
       </c>
       <c r="R213" t="n">
-        <v>7391824</v>
+        <v>7392031</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22315,10 +22316,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>119541074</v>
+        <v>119541132</v>
       </c>
       <c r="B214" t="n">
-        <v>96868</v>
+        <v>91840</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -22331,21 +22332,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -22355,10 +22356,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>811554</v>
+        <v>811532</v>
       </c>
       <c r="R214" t="n">
-        <v>7391879</v>
+        <v>7391774</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22417,10 +22418,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>119541070</v>
+        <v>119541180</v>
       </c>
       <c r="B215" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -22429,25 +22430,25 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -22457,10 +22458,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>810940</v>
+        <v>811501</v>
       </c>
       <c r="R215" t="n">
-        <v>7392041</v>
+        <v>7391868</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22519,10 +22520,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>119541059</v>
+        <v>119541051</v>
       </c>
       <c r="B216" t="n">
-        <v>57326</v>
+        <v>90953</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -22535,21 +22536,16 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -22559,10 +22555,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>811490</v>
+        <v>811305</v>
       </c>
       <c r="R216" t="n">
-        <v>7391874</v>
+        <v>7391791</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22603,6 +22599,7 @@
       <c r="AE216" t="b">
         <v>0</v>
       </c>
+      <c r="AF216" t="inlineStr"/>
       <c r="AG216" t="b">
         <v>0</v>
       </c>
@@ -22621,10 +22618,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>119541038</v>
+        <v>119541125</v>
       </c>
       <c r="B217" t="n">
-        <v>56522</v>
+        <v>91840</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -22637,21 +22634,21 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -22661,10 +22658,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>811354</v>
+        <v>811502</v>
       </c>
       <c r="R217" t="n">
-        <v>7391760</v>
+        <v>7391976</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22723,10 +22720,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>119541081</v>
+        <v>119541144</v>
       </c>
       <c r="B218" t="n">
-        <v>91832</v>
+        <v>91840</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -22735,25 +22732,25 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -22763,10 +22760,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>811187</v>
+        <v>811266</v>
       </c>
       <c r="R218" t="n">
-        <v>7391879</v>
+        <v>7391829</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -22825,10 +22822,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>119541085</v>
+        <v>119541175</v>
       </c>
       <c r="B219" t="n">
-        <v>91832</v>
+        <v>91834</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -22841,21 +22838,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -22865,10 +22862,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>811445</v>
+        <v>811484</v>
       </c>
       <c r="R219" t="n">
-        <v>7391835</v>
+        <v>7391790</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22927,10 +22924,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>119541100</v>
+        <v>119541082</v>
       </c>
       <c r="B220" t="n">
-        <v>78262</v>
+        <v>91832</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -22943,21 +22940,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>6446</v>
+        <v>4361</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -22967,10 +22964,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>811290</v>
+        <v>811354</v>
       </c>
       <c r="R220" t="n">
-        <v>7391801</v>
+        <v>7391857</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23029,10 +23026,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>119541161</v>
+        <v>119541059</v>
       </c>
       <c r="B221" t="n">
-        <v>91840</v>
+        <v>57326</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -23041,25 +23038,25 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -23069,10 +23066,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>811032</v>
+        <v>811490</v>
       </c>
       <c r="R221" t="n">
-        <v>7392031</v>
+        <v>7391874</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23131,10 +23128,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119541175</v>
+        <v>119541032</v>
       </c>
       <c r="B222" t="n">
-        <v>91834</v>
+        <v>56522</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -23143,25 +23140,25 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>4362</v>
+        <v>100138</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -23171,10 +23168,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>811484</v>
+        <v>811213</v>
       </c>
       <c r="R222" t="n">
-        <v>7391790</v>
+        <v>7391942</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23207,6 +23204,11 @@
       <c r="AA222" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC222" t="inlineStr">
+        <is>
+          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -23233,10 +23235,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>119541152</v>
+        <v>119541031</v>
       </c>
       <c r="B223" t="n">
-        <v>91840</v>
+        <v>56522</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -23249,21 +23251,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -23273,10 +23275,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>811128</v>
+        <v>811012</v>
       </c>
       <c r="R223" t="n">
-        <v>7391921</v>
+        <v>7392154</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23303,12 +23305,12 @@
       </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -23335,10 +23337,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>119541064</v>
+        <v>119541089</v>
       </c>
       <c r="B224" t="n">
-        <v>91856</v>
+        <v>78263</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -23351,21 +23353,21 @@
         </is>
       </c>
       <c r="E224" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -23375,10 +23377,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>811042</v>
+        <v>811635</v>
       </c>
       <c r="R224" t="n">
-        <v>7391966</v>
+        <v>7391860</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23437,10 +23439,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>119541054</v>
+        <v>119541096</v>
       </c>
       <c r="B225" t="n">
-        <v>91884</v>
+        <v>78263</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -23453,21 +23455,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>5449</v>
+        <v>228912</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -23477,10 +23479,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>811358</v>
+        <v>810955</v>
       </c>
       <c r="R225" t="n">
-        <v>7391815</v>
+        <v>7392033</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23539,10 +23541,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>119541033</v>
+        <v>119541186</v>
       </c>
       <c r="B226" t="n">
-        <v>56522</v>
+        <v>91834</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -23551,25 +23553,25 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>100138</v>
+        <v>4362</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23579,10 +23581,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>811505</v>
+        <v>811144</v>
       </c>
       <c r="R226" t="n">
-        <v>7391980</v>
+        <v>7391927</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23615,11 +23617,6 @@
       <c r="AA226" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC226" t="inlineStr">
-        <is>
-          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD226" t="b">
@@ -23646,10 +23643,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>119541126</v>
+        <v>119541041</v>
       </c>
       <c r="B227" t="n">
-        <v>91840</v>
+        <v>91826</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -23658,25 +23655,25 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -23686,10 +23683,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>811473</v>
+        <v>810994</v>
       </c>
       <c r="R227" t="n">
-        <v>7391962</v>
+        <v>7391976</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23748,10 +23745,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>119541078</v>
+        <v>119541135</v>
       </c>
       <c r="B228" t="n">
-        <v>96868</v>
+        <v>91840</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -23764,21 +23761,21 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -23788,10 +23785,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>811192</v>
+        <v>811304</v>
       </c>
       <c r="R228" t="n">
-        <v>7391862</v>
+        <v>7391760</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23850,10 +23847,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>119541087</v>
+        <v>119541110</v>
       </c>
       <c r="B229" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -23862,25 +23859,25 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -23890,10 +23887,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>811167</v>
+        <v>811189</v>
       </c>
       <c r="R229" t="n">
-        <v>7391874</v>
+        <v>7391809</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -23934,7 +23931,6 @@
       <c r="AE229" t="b">
         <v>0</v>
       </c>
-      <c r="AF229" t="inlineStr"/>
       <c r="AG229" t="b">
         <v>0</v>
       </c>
@@ -23953,10 +23949,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>119541095</v>
+        <v>119541123</v>
       </c>
       <c r="B230" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -23965,25 +23961,25 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -23993,10 +23989,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>811019</v>
+        <v>811693</v>
       </c>
       <c r="R230" t="n">
-        <v>7392058</v>
+        <v>7391895</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24055,10 +24051,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>119541051</v>
+        <v>119541153</v>
       </c>
       <c r="B231" t="n">
-        <v>90953</v>
+        <v>91840</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -24067,20 +24063,25 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>6040162</v>
+        <v>4364</v>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -24090,10 +24091,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>811305</v>
+        <v>811147</v>
       </c>
       <c r="R231" t="n">
-        <v>7391791</v>
+        <v>7391936</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>
@@ -24134,7 +24135,6 @@
       <c r="AE231" t="b">
         <v>0</v>
       </c>
-      <c r="AF231" t="inlineStr"/>
       <c r="AG231" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 10151-2023 artfynd.xlsx
+++ b/artfynd/A 10151-2023 artfynd.xlsx
@@ -11701,10 +11701,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119541087</v>
+        <v>119541189</v>
       </c>
       <c r="B110" t="n">
-        <v>78263</v>
+        <v>91834</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -11717,21 +11717,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>228912</v>
+        <v>4362</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -11741,10 +11741,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>811167</v>
+        <v>811022</v>
       </c>
       <c r="R110" t="n">
-        <v>7391874</v>
+        <v>7391895</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -11785,7 +11785,6 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
-      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
@@ -11804,10 +11803,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119541093</v>
+        <v>119541025</v>
       </c>
       <c r="B111" t="n">
-        <v>78263</v>
+        <v>91836</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11816,25 +11815,25 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>228912</v>
+        <v>4363</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11844,10 +11843,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>811120</v>
+        <v>811673</v>
       </c>
       <c r="R111" t="n">
-        <v>7391955</v>
+        <v>7391865</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11906,10 +11905,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119541061</v>
+        <v>119541106</v>
       </c>
       <c r="B112" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -11922,21 +11921,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11946,10 +11945,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>811158</v>
+        <v>810962</v>
       </c>
       <c r="R112" t="n">
-        <v>7391914</v>
+        <v>7392039</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12008,10 +12007,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119541025</v>
+        <v>119541126</v>
       </c>
       <c r="B113" t="n">
-        <v>91836</v>
+        <v>91840</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12024,21 +12023,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4363</v>
+        <v>4364</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12048,10 +12047,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>811673</v>
+        <v>811473</v>
       </c>
       <c r="R113" t="n">
-        <v>7391865</v>
+        <v>7391962</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12110,10 +12109,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119541189</v>
+        <v>119541141</v>
       </c>
       <c r="B114" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12122,25 +12121,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12150,10 +12149,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>811022</v>
+        <v>811243</v>
       </c>
       <c r="R114" t="n">
-        <v>7391895</v>
+        <v>7391854</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12212,10 +12211,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119541106</v>
+        <v>119541130</v>
       </c>
       <c r="B115" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12224,25 +12223,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12252,10 +12251,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>810962</v>
+        <v>811571</v>
       </c>
       <c r="R115" t="n">
-        <v>7392039</v>
+        <v>7391809</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12314,7 +12313,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119541126</v>
+        <v>119541155</v>
       </c>
       <c r="B116" t="n">
         <v>91840</v>
@@ -12354,10 +12353,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>811473</v>
+        <v>811049</v>
       </c>
       <c r="R116" t="n">
-        <v>7391962</v>
+        <v>7391928</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12416,7 +12415,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119541141</v>
+        <v>119541117</v>
       </c>
       <c r="B117" t="n">
         <v>91840</v>
@@ -12456,10 +12455,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>811243</v>
+        <v>811616</v>
       </c>
       <c r="R117" t="n">
-        <v>7391854</v>
+        <v>7391803</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12518,7 +12517,7 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119541130</v>
+        <v>119541159</v>
       </c>
       <c r="B118" t="n">
         <v>91840</v>
@@ -12558,10 +12557,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>811571</v>
+        <v>811018</v>
       </c>
       <c r="R118" t="n">
-        <v>7391809</v>
+        <v>7392016</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12620,10 +12619,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119541155</v>
+        <v>119541061</v>
       </c>
       <c r="B119" t="n">
-        <v>91840</v>
+        <v>91856</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12632,25 +12631,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12660,10 +12659,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>811049</v>
+        <v>811158</v>
       </c>
       <c r="R119" t="n">
-        <v>7391928</v>
+        <v>7391914</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12722,10 +12721,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119541117</v>
+        <v>119541087</v>
       </c>
       <c r="B120" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12734,25 +12733,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12762,10 +12761,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>811616</v>
+        <v>811167</v>
       </c>
       <c r="R120" t="n">
-        <v>7391803</v>
+        <v>7391874</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12806,6 +12805,7 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
+      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12824,10 +12824,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119541159</v>
+        <v>119541093</v>
       </c>
       <c r="B121" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12836,25 +12836,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12864,10 +12864,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>811018</v>
+        <v>811120</v>
       </c>
       <c r="R121" t="n">
-        <v>7392016</v>
+        <v>7391955</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12926,10 +12926,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119541091</v>
+        <v>119541161</v>
       </c>
       <c r="B122" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -12938,25 +12938,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12966,10 +12966,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>811814</v>
+        <v>811032</v>
       </c>
       <c r="R122" t="n">
-        <v>7391907</v>
+        <v>7392031</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13028,10 +13028,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119541029</v>
+        <v>119541068</v>
       </c>
       <c r="B123" t="n">
-        <v>79144</v>
+        <v>91852</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13040,25 +13040,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6453</v>
+        <v>4366</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13068,10 +13068,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>811120</v>
+        <v>811247</v>
       </c>
       <c r="R123" t="n">
-        <v>7391955</v>
+        <v>7391907</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13130,7 +13130,7 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119541161</v>
+        <v>119541150</v>
       </c>
       <c r="B124" t="n">
         <v>91840</v>
@@ -13170,10 +13170,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>811032</v>
+        <v>811181</v>
       </c>
       <c r="R124" t="n">
-        <v>7392031</v>
+        <v>7391849</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13232,10 +13232,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119541068</v>
+        <v>119541147</v>
       </c>
       <c r="B125" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13248,21 +13248,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13272,10 +13272,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>811247</v>
+        <v>811248</v>
       </c>
       <c r="R125" t="n">
-        <v>7391907</v>
+        <v>7391873</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13334,10 +13334,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119541150</v>
+        <v>119541029</v>
       </c>
       <c r="B126" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13346,25 +13346,25 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13374,10 +13374,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>811181</v>
+        <v>811120</v>
       </c>
       <c r="R126" t="n">
-        <v>7391849</v>
+        <v>7391955</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13436,10 +13436,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119541147</v>
+        <v>119541091</v>
       </c>
       <c r="B127" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13448,25 +13448,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13476,10 +13476,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>811248</v>
+        <v>811814</v>
       </c>
       <c r="R127" t="n">
-        <v>7391873</v>
+        <v>7391907</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13538,10 +13538,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>119541054</v>
+        <v>119541118</v>
       </c>
       <c r="B128" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13550,25 +13550,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13578,10 +13578,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>811358</v>
+        <v>811600</v>
       </c>
       <c r="R128" t="n">
-        <v>7391815</v>
+        <v>7391842</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13640,7 +13640,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>119541118</v>
+        <v>119541124</v>
       </c>
       <c r="B129" t="n">
         <v>91840</v>
@@ -13680,10 +13680,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>811600</v>
+        <v>811523</v>
       </c>
       <c r="R129" t="n">
-        <v>7391842</v>
+        <v>7391986</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13742,7 +13742,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119541124</v>
+        <v>119541164</v>
       </c>
       <c r="B130" t="n">
         <v>91840</v>
@@ -13782,10 +13782,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>811523</v>
+        <v>810929</v>
       </c>
       <c r="R130" t="n">
-        <v>7391986</v>
+        <v>7392042</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13844,10 +13844,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>119541164</v>
+        <v>119541054</v>
       </c>
       <c r="B131" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13856,25 +13856,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13884,10 +13884,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>810929</v>
+        <v>811358</v>
       </c>
       <c r="R131" t="n">
-        <v>7392042</v>
+        <v>7391815</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15273,10 +15273,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119541138</v>
+        <v>119541080</v>
       </c>
       <c r="B145" t="n">
-        <v>91840</v>
+        <v>56525</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15289,21 +15289,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>4364</v>
+        <v>102613</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15313,10 +15313,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>811172</v>
+        <v>811181</v>
       </c>
       <c r="R145" t="n">
-        <v>7391843</v>
+        <v>7391940</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15375,10 +15375,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119541119</v>
+        <v>119541038</v>
       </c>
       <c r="B146" t="n">
-        <v>91840</v>
+        <v>56522</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15391,21 +15391,21 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15415,10 +15415,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>811661</v>
+        <v>811354</v>
       </c>
       <c r="R146" t="n">
-        <v>7391873</v>
+        <v>7391760</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15477,10 +15477,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119541080</v>
+        <v>119541138</v>
       </c>
       <c r="B147" t="n">
-        <v>56525</v>
+        <v>91840</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15493,21 +15493,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>102613</v>
+        <v>4364</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15517,10 +15517,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>811181</v>
+        <v>811172</v>
       </c>
       <c r="R147" t="n">
-        <v>7391940</v>
+        <v>7391843</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15579,10 +15579,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119541038</v>
+        <v>119541119</v>
       </c>
       <c r="B148" t="n">
-        <v>56522</v>
+        <v>91840</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15595,21 +15595,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15619,10 +15619,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>811354</v>
+        <v>811661</v>
       </c>
       <c r="R148" t="n">
-        <v>7391760</v>
+        <v>7391873</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15681,10 +15681,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119541076</v>
+        <v>119541058</v>
       </c>
       <c r="B149" t="n">
-        <v>96868</v>
+        <v>57326</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15693,25 +15693,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15721,10 +15721,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>811175</v>
+        <v>811109</v>
       </c>
       <c r="R149" t="n">
-        <v>7391844</v>
+        <v>7391871</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -15783,10 +15783,10 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119541046</v>
+        <v>119541142</v>
       </c>
       <c r="B150" t="n">
-        <v>91463</v>
+        <v>91840</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
@@ -15795,25 +15795,25 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
@@ -15823,10 +15823,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>811712</v>
+        <v>811226</v>
       </c>
       <c r="R150" t="n">
-        <v>7391868</v>
+        <v>7391836</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15885,7 +15885,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119541142</v>
+        <v>119541148</v>
       </c>
       <c r="B151" t="n">
         <v>91840</v>
@@ -15925,10 +15925,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>811226</v>
+        <v>811222</v>
       </c>
       <c r="R151" t="n">
-        <v>7391836</v>
+        <v>7391892</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15987,7 +15987,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119541148</v>
+        <v>119541134</v>
       </c>
       <c r="B152" t="n">
         <v>91840</v>
@@ -16027,10 +16027,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>811222</v>
+        <v>811445</v>
       </c>
       <c r="R152" t="n">
-        <v>7391892</v>
+        <v>7391835</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16089,10 +16089,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119541134</v>
+        <v>119541046</v>
       </c>
       <c r="B153" t="n">
-        <v>91840</v>
+        <v>91463</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16101,25 +16101,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16129,10 +16129,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>811445</v>
+        <v>811712</v>
       </c>
       <c r="R153" t="n">
-        <v>7391835</v>
+        <v>7391868</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16191,10 +16191,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119541058</v>
+        <v>119541076</v>
       </c>
       <c r="B154" t="n">
-        <v>57326</v>
+        <v>96868</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16203,25 +16203,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>100049</v>
+        <v>221941</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16231,10 +16231,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>811109</v>
+        <v>811175</v>
       </c>
       <c r="R154" t="n">
-        <v>7391871</v>
+        <v>7391844</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -18027,10 +18027,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>119541074</v>
+        <v>119541064</v>
       </c>
       <c r="B172" t="n">
-        <v>96868</v>
+        <v>91856</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18039,25 +18039,25 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>221941</v>
+        <v>2059</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18067,10 +18067,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>811554</v>
+        <v>811042</v>
       </c>
       <c r="R172" t="n">
-        <v>7391879</v>
+        <v>7391966</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18129,10 +18129,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>119541064</v>
+        <v>119541181</v>
       </c>
       <c r="B173" t="n">
-        <v>91856</v>
+        <v>91834</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18145,21 +18145,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18169,10 +18169,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>811042</v>
+        <v>811465</v>
       </c>
       <c r="R173" t="n">
-        <v>7391966</v>
+        <v>7391838</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18231,10 +18231,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>119541181</v>
+        <v>119541069</v>
       </c>
       <c r="B174" t="n">
-        <v>91834</v>
+        <v>91852</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18243,25 +18243,25 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18271,10 +18271,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>811465</v>
+        <v>811140</v>
       </c>
       <c r="R174" t="n">
-        <v>7391838</v>
+        <v>7391897</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18333,10 +18333,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>119541039</v>
+        <v>119541074</v>
       </c>
       <c r="B175" t="n">
-        <v>56522</v>
+        <v>96868</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18349,21 +18349,21 @@
         </is>
       </c>
       <c r="E175" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18373,10 +18373,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>811215</v>
+        <v>811554</v>
       </c>
       <c r="R175" t="n">
-        <v>7391820</v>
+        <v>7391879</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18435,7 +18435,7 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>119541034</v>
+        <v>119541039</v>
       </c>
       <c r="B176" t="n">
         <v>56522</v>
@@ -18475,10 +18475,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>811472</v>
+        <v>811215</v>
       </c>
       <c r="R176" t="n">
-        <v>7391805</v>
+        <v>7391820</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18537,10 +18537,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>119541069</v>
+        <v>119541034</v>
       </c>
       <c r="B177" t="n">
-        <v>91852</v>
+        <v>56522</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -18553,21 +18553,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>4366</v>
+        <v>100138</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18577,10 +18577,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>811140</v>
+        <v>811472</v>
       </c>
       <c r="R177" t="n">
-        <v>7391897</v>
+        <v>7391805</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -20888,10 +20888,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119541070</v>
+        <v>119541183</v>
       </c>
       <c r="B200" t="n">
-        <v>91852</v>
+        <v>91834</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -20900,25 +20900,25 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20928,10 +20928,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>810940</v>
+        <v>811180</v>
       </c>
       <c r="R200" t="n">
-        <v>7392041</v>
+        <v>7391829</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20990,10 +20990,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119541154</v>
+        <v>119541177</v>
       </c>
       <c r="B201" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21002,25 +21002,25 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21030,10 +21030,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>811034</v>
+        <v>811607</v>
       </c>
       <c r="R201" t="n">
-        <v>7391905</v>
+        <v>7391859</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21092,10 +21092,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119541113</v>
+        <v>119541043</v>
       </c>
       <c r="B202" t="n">
-        <v>91840</v>
+        <v>91463</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -21104,25 +21104,25 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -21132,10 +21132,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>811489</v>
+        <v>811147</v>
       </c>
       <c r="R202" t="n">
-        <v>7391792</v>
+        <v>7391872</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21194,10 +21194,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119541183</v>
+        <v>119541045</v>
       </c>
       <c r="B203" t="n">
-        <v>91834</v>
+        <v>91463</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -21210,21 +21210,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -21234,10 +21234,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>811180</v>
+        <v>811207</v>
       </c>
       <c r="R203" t="n">
-        <v>7391829</v>
+        <v>7391947</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21296,10 +21296,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>119541177</v>
+        <v>119541044</v>
       </c>
       <c r="B204" t="n">
-        <v>91834</v>
+        <v>91463</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -21312,21 +21312,21 @@
         </is>
       </c>
       <c r="E204" t="n">
-        <v>4362</v>
+        <v>4745</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -21336,10 +21336,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>811607</v>
+        <v>811162</v>
       </c>
       <c r="R204" t="n">
-        <v>7391859</v>
+        <v>7391926</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21398,10 +21398,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>119541043</v>
+        <v>119541103</v>
       </c>
       <c r="B205" t="n">
-        <v>91463</v>
+        <v>78526</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -21414,21 +21414,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>4745</v>
+        <v>6425</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -21438,10 +21438,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>811147</v>
+        <v>811689</v>
       </c>
       <c r="R205" t="n">
-        <v>7391872</v>
+        <v>7391899</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21500,10 +21500,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>119541045</v>
+        <v>119541070</v>
       </c>
       <c r="B206" t="n">
-        <v>91463</v>
+        <v>91852</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -21512,25 +21512,25 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>4745</v>
+        <v>4366</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -21540,10 +21540,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>811207</v>
+        <v>810940</v>
       </c>
       <c r="R206" t="n">
-        <v>7391947</v>
+        <v>7392041</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21602,10 +21602,10 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>119541044</v>
+        <v>119541154</v>
       </c>
       <c r="B207" t="n">
-        <v>91463</v>
+        <v>91840</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
@@ -21614,25 +21614,25 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E207" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I207" t="inlineStr"/>
@@ -21642,10 +21642,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>811162</v>
+        <v>811034</v>
       </c>
       <c r="R207" t="n">
-        <v>7391926</v>
+        <v>7391905</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21704,10 +21704,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119541103</v>
+        <v>119541113</v>
       </c>
       <c r="B208" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -21716,25 +21716,25 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -21744,10 +21744,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>811689</v>
+        <v>811489</v>
       </c>
       <c r="R208" t="n">
-        <v>7391899</v>
+        <v>7391792</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21908,10 +21908,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>119541071</v>
+        <v>119541120</v>
       </c>
       <c r="B210" t="n">
-        <v>96868</v>
+        <v>91840</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -21924,21 +21924,21 @@
         </is>
       </c>
       <c r="E210" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -21948,10 +21948,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>811599</v>
+        <v>811720</v>
       </c>
       <c r="R210" t="n">
-        <v>7391829</v>
+        <v>7391872</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22010,10 +22010,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>119541098</v>
+        <v>119541065</v>
       </c>
       <c r="B211" t="n">
-        <v>78262</v>
+        <v>91852</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22022,25 +22022,25 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E211" t="n">
-        <v>6446</v>
+        <v>4366</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -22050,10 +22050,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>811353</v>
+        <v>810977</v>
       </c>
       <c r="R211" t="n">
-        <v>7391859</v>
+        <v>7392031</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22112,7 +22112,7 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>119541120</v>
+        <v>119541132</v>
       </c>
       <c r="B212" t="n">
         <v>91840</v>
@@ -22152,10 +22152,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>811720</v>
+        <v>811532</v>
       </c>
       <c r="R212" t="n">
-        <v>7391872</v>
+        <v>7391774</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22214,10 +22214,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>119541065</v>
+        <v>119541098</v>
       </c>
       <c r="B213" t="n">
-        <v>91852</v>
+        <v>78262</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -22226,25 +22226,25 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E213" t="n">
-        <v>4366</v>
+        <v>6446</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -22254,10 +22254,10 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>810977</v>
+        <v>811353</v>
       </c>
       <c r="R213" t="n">
-        <v>7392031</v>
+        <v>7391859</v>
       </c>
       <c r="S213" t="n">
         <v>10</v>
@@ -22316,10 +22316,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>119541132</v>
+        <v>119541071</v>
       </c>
       <c r="B214" t="n">
-        <v>91840</v>
+        <v>96868</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -22332,21 +22332,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -22356,10 +22356,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>811532</v>
+        <v>811599</v>
       </c>
       <c r="R214" t="n">
-        <v>7391774</v>
+        <v>7391829</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -23235,10 +23235,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>119541031</v>
+        <v>119541089</v>
       </c>
       <c r="B223" t="n">
-        <v>56522</v>
+        <v>78263</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -23247,25 +23247,25 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E223" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -23275,10 +23275,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>811012</v>
+        <v>811635</v>
       </c>
       <c r="R223" t="n">
-        <v>7392154</v>
+        <v>7391860</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23305,12 +23305,12 @@
       </c>
       <c r="Y223" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA223" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD223" t="b">
@@ -23337,7 +23337,7 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>119541089</v>
+        <v>119541096</v>
       </c>
       <c r="B224" t="n">
         <v>78263</v>
@@ -23377,10 +23377,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>811635</v>
+        <v>810955</v>
       </c>
       <c r="R224" t="n">
-        <v>7391860</v>
+        <v>7392033</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23439,10 +23439,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>119541096</v>
+        <v>119541041</v>
       </c>
       <c r="B225" t="n">
-        <v>78263</v>
+        <v>91826</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -23455,21 +23455,21 @@
         </is>
       </c>
       <c r="E225" t="n">
-        <v>228912</v>
+        <v>3100</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -23479,10 +23479,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>810955</v>
+        <v>810994</v>
       </c>
       <c r="R225" t="n">
-        <v>7392033</v>
+        <v>7391976</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23541,10 +23541,10 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>119541186</v>
+        <v>119541135</v>
       </c>
       <c r="B226" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
@@ -23553,25 +23553,25 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E226" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
@@ -23581,10 +23581,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>811144</v>
+        <v>811304</v>
       </c>
       <c r="R226" t="n">
-        <v>7391927</v>
+        <v>7391760</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23643,10 +23643,10 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>119541041</v>
+        <v>119541110</v>
       </c>
       <c r="B227" t="n">
-        <v>91826</v>
+        <v>91840</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
@@ -23655,25 +23655,25 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E227" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
@@ -23683,10 +23683,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>810994</v>
+        <v>811189</v>
       </c>
       <c r="R227" t="n">
-        <v>7391976</v>
+        <v>7391809</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23745,7 +23745,7 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>119541135</v>
+        <v>119541123</v>
       </c>
       <c r="B228" t="n">
         <v>91840</v>
@@ -23785,10 +23785,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>811304</v>
+        <v>811693</v>
       </c>
       <c r="R228" t="n">
-        <v>7391760</v>
+        <v>7391895</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23847,7 +23847,7 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>119541110</v>
+        <v>119541153</v>
       </c>
       <c r="B229" t="n">
         <v>91840</v>
@@ -23887,10 +23887,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>811189</v>
+        <v>811147</v>
       </c>
       <c r="R229" t="n">
-        <v>7391809</v>
+        <v>7391936</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -23949,10 +23949,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>119541123</v>
+        <v>119541031</v>
       </c>
       <c r="B230" t="n">
-        <v>91840</v>
+        <v>56522</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -23965,21 +23965,21 @@
         </is>
       </c>
       <c r="E230" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -23989,10 +23989,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>811693</v>
+        <v>811012</v>
       </c>
       <c r="R230" t="n">
-        <v>7391895</v>
+        <v>7392154</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24019,12 +24019,12 @@
       </c>
       <c r="Y230" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -24051,10 +24051,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>119541153</v>
+        <v>119541186</v>
       </c>
       <c r="B231" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -24063,25 +24063,25 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E231" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -24091,10 +24091,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>811147</v>
+        <v>811144</v>
       </c>
       <c r="R231" t="n">
-        <v>7391936</v>
+        <v>7391927</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>

--- a/artfynd/A 10151-2023 artfynd.xlsx
+++ b/artfynd/A 10151-2023 artfynd.xlsx
@@ -10273,7 +10273,7 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119541165</v>
+        <v>119541161</v>
       </c>
       <c r="B96" t="n">
         <v>91840</v>
@@ -10313,10 +10313,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>810902</v>
+        <v>811032</v>
       </c>
       <c r="R96" t="n">
-        <v>7392035</v>
+        <v>7392031</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10375,7 +10375,7 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119541137</v>
+        <v>119541155</v>
       </c>
       <c r="B97" t="n">
         <v>91840</v>
@@ -10415,10 +10415,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>811175</v>
+        <v>811049</v>
       </c>
       <c r="R97" t="n">
-        <v>7391841</v>
+        <v>7391928</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10477,7 +10477,7 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119541136</v>
+        <v>119541152</v>
       </c>
       <c r="B98" t="n">
         <v>91840</v>
@@ -10517,10 +10517,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>811196</v>
+        <v>811128</v>
       </c>
       <c r="R98" t="n">
-        <v>7391817</v>
+        <v>7391921</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10579,10 +10579,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119541152</v>
+        <v>119541035</v>
       </c>
       <c r="B99" t="n">
-        <v>91840</v>
+        <v>56522</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10595,21 +10595,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10619,10 +10619,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>811128</v>
+        <v>811805</v>
       </c>
       <c r="R99" t="n">
-        <v>7391921</v>
+        <v>7391923</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10681,10 +10681,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119541073</v>
+        <v>119541058</v>
       </c>
       <c r="B100" t="n">
-        <v>96868</v>
+        <v>57326</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -10693,25 +10693,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>221941</v>
+        <v>100049</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -10721,10 +10721,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>811602</v>
+        <v>811109</v>
       </c>
       <c r="R100" t="n">
-        <v>7391853</v>
+        <v>7391871</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -10783,7 +10783,7 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119541049</v>
+        <v>119541047</v>
       </c>
       <c r="B101" t="n">
         <v>91463</v>
@@ -10823,10 +10823,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>811251</v>
+        <v>811768</v>
       </c>
       <c r="R101" t="n">
-        <v>7391796</v>
+        <v>7391938</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -10885,10 +10885,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119541099</v>
+        <v>119541057</v>
       </c>
       <c r="B102" t="n">
-        <v>78262</v>
+        <v>91884</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -10901,21 +10901,21 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6446</v>
+        <v>5449</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -10925,10 +10925,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>811540</v>
+        <v>811123</v>
       </c>
       <c r="R102" t="n">
-        <v>7391755</v>
+        <v>7391919</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -10987,10 +10987,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119541063</v>
+        <v>119541103</v>
       </c>
       <c r="B103" t="n">
-        <v>91856</v>
+        <v>78526</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11003,21 +11003,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2059</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11027,10 +11027,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>811474</v>
+        <v>811689</v>
       </c>
       <c r="R103" t="n">
-        <v>7391808</v>
+        <v>7391899</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11089,10 +11089,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119541190</v>
+        <v>119541051</v>
       </c>
       <c r="B104" t="n">
-        <v>91834</v>
+        <v>90953</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11105,21 +11105,16 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4362</v>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Blå taggsvamp</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11129,10 +11124,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>811005</v>
+        <v>811305</v>
       </c>
       <c r="R104" t="n">
-        <v>7391977</v>
+        <v>7391791</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11173,6 +11168,7 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -11191,10 +11187,10 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119541173</v>
+        <v>119541064</v>
       </c>
       <c r="B105" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11207,21 +11203,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11231,10 +11227,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>811366</v>
+        <v>811042</v>
       </c>
       <c r="R105" t="n">
-        <v>7391825</v>
+        <v>7391966</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11293,10 +11289,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119541182</v>
+        <v>119541138</v>
       </c>
       <c r="B106" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11305,25 +11301,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11333,10 +11329,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>811269</v>
+        <v>811172</v>
       </c>
       <c r="R106" t="n">
-        <v>7391786</v>
+        <v>7391843</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11395,10 +11391,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119541047</v>
+        <v>119541182</v>
       </c>
       <c r="B107" t="n">
-        <v>91463</v>
+        <v>91834</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11411,21 +11407,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11435,10 +11431,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>811768</v>
+        <v>811269</v>
       </c>
       <c r="R107" t="n">
-        <v>7391938</v>
+        <v>7391786</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11497,10 +11493,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119541048</v>
+        <v>119541112</v>
       </c>
       <c r="B108" t="n">
-        <v>91463</v>
+        <v>91840</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11509,25 +11505,25 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11537,10 +11533,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>811437</v>
+        <v>811371</v>
       </c>
       <c r="R108" t="n">
-        <v>7391823</v>
+        <v>7391863</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11599,10 +11595,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119541100</v>
+        <v>119541132</v>
       </c>
       <c r="B109" t="n">
-        <v>78262</v>
+        <v>91840</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -11611,25 +11607,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -11639,10 +11635,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>811290</v>
+        <v>811532</v>
       </c>
       <c r="R109" t="n">
-        <v>7391801</v>
+        <v>7391774</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11803,10 +11799,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119541025</v>
+        <v>119541137</v>
       </c>
       <c r="B111" t="n">
-        <v>91836</v>
+        <v>91840</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -11819,21 +11815,21 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4363</v>
+        <v>4364</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Zontaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum concrescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Pers.) Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
@@ -11843,10 +11839,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>811673</v>
+        <v>811175</v>
       </c>
       <c r="R111" t="n">
-        <v>7391865</v>
+        <v>7391841</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -11905,10 +11901,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119541106</v>
+        <v>119541127</v>
       </c>
       <c r="B112" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -11917,25 +11913,25 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -11945,10 +11941,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>810962</v>
+        <v>811557</v>
       </c>
       <c r="R112" t="n">
-        <v>7392039</v>
+        <v>7391884</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12007,10 +12003,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119541126</v>
+        <v>119541179</v>
       </c>
       <c r="B113" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12019,25 +12015,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12047,10 +12043,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>811473</v>
+        <v>811496</v>
       </c>
       <c r="R113" t="n">
-        <v>7391962</v>
+        <v>7391933</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12109,10 +12105,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119541141</v>
+        <v>119541188</v>
       </c>
       <c r="B114" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12121,25 +12117,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12149,10 +12145,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>811243</v>
+        <v>811059</v>
       </c>
       <c r="R114" t="n">
-        <v>7391854</v>
+        <v>7391942</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12211,7 +12207,7 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119541130</v>
+        <v>119541159</v>
       </c>
       <c r="B115" t="n">
         <v>91840</v>
@@ -12251,10 +12247,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>811571</v>
+        <v>811018</v>
       </c>
       <c r="R115" t="n">
-        <v>7391809</v>
+        <v>7392016</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12313,7 +12309,7 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119541155</v>
+        <v>119541157</v>
       </c>
       <c r="B116" t="n">
         <v>91840</v>
@@ -12353,10 +12349,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>811049</v>
+        <v>811006</v>
       </c>
       <c r="R116" t="n">
-        <v>7391928</v>
+        <v>7391996</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12415,7 +12411,7 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119541117</v>
+        <v>119541164</v>
       </c>
       <c r="B117" t="n">
         <v>91840</v>
@@ -12455,10 +12451,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>811616</v>
+        <v>810929</v>
       </c>
       <c r="R117" t="n">
-        <v>7391803</v>
+        <v>7392042</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12517,10 +12513,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119541159</v>
+        <v>119541183</v>
       </c>
       <c r="B118" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -12529,25 +12525,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -12557,10 +12553,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>811018</v>
+        <v>811180</v>
       </c>
       <c r="R118" t="n">
-        <v>7392016</v>
+        <v>7391829</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12619,10 +12615,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119541061</v>
+        <v>119541093</v>
       </c>
       <c r="B119" t="n">
-        <v>91856</v>
+        <v>78263</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -12635,21 +12631,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -12659,10 +12655,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>811158</v>
+        <v>811120</v>
       </c>
       <c r="R119" t="n">
-        <v>7391914</v>
+        <v>7391955</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -12721,10 +12717,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119541087</v>
+        <v>119541073</v>
       </c>
       <c r="B120" t="n">
-        <v>78263</v>
+        <v>96868</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -12733,25 +12729,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -12761,10 +12757,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>811167</v>
+        <v>811602</v>
       </c>
       <c r="R120" t="n">
-        <v>7391874</v>
+        <v>7391853</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -12805,7 +12801,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -12824,10 +12819,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119541093</v>
+        <v>119541079</v>
       </c>
       <c r="B121" t="n">
-        <v>78263</v>
+        <v>96868</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -12836,25 +12831,25 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>228912</v>
+        <v>221941</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -12864,10 +12859,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>811120</v>
+        <v>811182</v>
       </c>
       <c r="R121" t="n">
-        <v>7391955</v>
+        <v>7391854</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -12926,10 +12921,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119541161</v>
+        <v>119541041</v>
       </c>
       <c r="B122" t="n">
-        <v>91840</v>
+        <v>91826</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -12938,25 +12933,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4364</v>
+        <v>3100</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Bankera fuligineoalba</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schmidt : Fr.) Pouzar</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -12966,10 +12961,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>811032</v>
+        <v>810994</v>
       </c>
       <c r="R122" t="n">
-        <v>7392031</v>
+        <v>7391976</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13028,10 +13023,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119541068</v>
+        <v>119541029</v>
       </c>
       <c r="B123" t="n">
-        <v>91852</v>
+        <v>79144</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13040,25 +13035,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>4366</v>
+        <v>6453</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13068,10 +13063,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>811247</v>
+        <v>811120</v>
       </c>
       <c r="R123" t="n">
-        <v>7391907</v>
+        <v>7391955</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13130,10 +13125,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119541150</v>
+        <v>119541102</v>
       </c>
       <c r="B124" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13142,25 +13137,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13170,10 +13165,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>811181</v>
+        <v>811751</v>
       </c>
       <c r="R124" t="n">
-        <v>7391849</v>
+        <v>7391929</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13232,10 +13227,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>119541147</v>
+        <v>119541075</v>
       </c>
       <c r="B125" t="n">
-        <v>91840</v>
+        <v>96868</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
@@ -13248,21 +13243,21 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
@@ -13272,10 +13267,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>811248</v>
+        <v>811178</v>
       </c>
       <c r="R125" t="n">
-        <v>7391873</v>
+        <v>7391829</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13334,10 +13329,10 @@
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>119541029</v>
+        <v>119541090</v>
       </c>
       <c r="B126" t="n">
-        <v>79144</v>
+        <v>78263</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13350,21 +13345,21 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>6453</v>
+        <v>228912</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
@@ -13374,10 +13369,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>811120</v>
+        <v>811788</v>
       </c>
       <c r="R126" t="n">
-        <v>7391955</v>
+        <v>7391959</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13436,10 +13431,10 @@
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>119541091</v>
+        <v>119541136</v>
       </c>
       <c r="B127" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
@@ -13448,25 +13443,25 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -13476,10 +13471,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>811814</v>
+        <v>811196</v>
       </c>
       <c r="R127" t="n">
-        <v>7391907</v>
+        <v>7391817</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13538,10 +13533,10 @@
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>119541118</v>
+        <v>119541174</v>
       </c>
       <c r="B128" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C128" t="inlineStr">
         <is>
@@ -13550,25 +13545,25 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
@@ -13578,10 +13573,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>811600</v>
+        <v>811427</v>
       </c>
       <c r="R128" t="n">
-        <v>7391842</v>
+        <v>7391805</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13640,7 +13635,7 @@
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>119541124</v>
+        <v>119541142</v>
       </c>
       <c r="B129" t="n">
         <v>91840</v>
@@ -13680,10 +13675,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>811523</v>
+        <v>811226</v>
       </c>
       <c r="R129" t="n">
-        <v>7391986</v>
+        <v>7391836</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -13742,7 +13737,7 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>119541164</v>
+        <v>119541119</v>
       </c>
       <c r="B130" t="n">
         <v>91840</v>
@@ -13782,10 +13777,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>810929</v>
+        <v>811661</v>
       </c>
       <c r="R130" t="n">
-        <v>7392042</v>
+        <v>7391873</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -13844,10 +13839,10 @@
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>119541054</v>
+        <v>119541143</v>
       </c>
       <c r="B131" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
@@ -13856,25 +13851,25 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -13884,10 +13879,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>811358</v>
+        <v>811263</v>
       </c>
       <c r="R131" t="n">
-        <v>7391815</v>
+        <v>7391814</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -13946,10 +13941,10 @@
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>119541066</v>
+        <v>119541038</v>
       </c>
       <c r="B132" t="n">
-        <v>91852</v>
+        <v>56522</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
@@ -13962,21 +13957,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>4366</v>
+        <v>100138</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -13986,10 +13981,10 @@
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>811361</v>
+        <v>811354</v>
       </c>
       <c r="R132" t="n">
-        <v>7391844</v>
+        <v>7391760</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -14048,10 +14043,10 @@
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>119541083</v>
+        <v>119541070</v>
       </c>
       <c r="B133" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
@@ -14060,25 +14055,25 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -14088,10 +14083,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>811752</v>
+        <v>810940</v>
       </c>
       <c r="R133" t="n">
-        <v>7391915</v>
+        <v>7392041</v>
       </c>
       <c r="S133" t="n">
         <v>10</v>
@@ -14150,10 +14145,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>119541084</v>
+        <v>119541055</v>
       </c>
       <c r="B134" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
@@ -14166,21 +14161,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -14190,10 +14185,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>811768</v>
+        <v>811375</v>
       </c>
       <c r="R134" t="n">
-        <v>7391938</v>
+        <v>7391770</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -14252,10 +14247,10 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>119541112</v>
+        <v>119541060</v>
       </c>
       <c r="B135" t="n">
-        <v>91840</v>
+        <v>57326</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
@@ -14264,25 +14259,25 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
@@ -14292,10 +14287,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>811371</v>
+        <v>811547</v>
       </c>
       <c r="R135" t="n">
-        <v>7391863</v>
+        <v>7391873</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14354,10 +14349,10 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>119541040</v>
+        <v>119541148</v>
       </c>
       <c r="B136" t="n">
-        <v>56522</v>
+        <v>91840</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
@@ -14370,21 +14365,21 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14394,10 +14389,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>811186</v>
+        <v>811222</v>
       </c>
       <c r="R136" t="n">
-        <v>7391822</v>
+        <v>7391892</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14456,10 +14451,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>119541102</v>
+        <v>119541085</v>
       </c>
       <c r="B137" t="n">
-        <v>78526</v>
+        <v>91832</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
@@ -14472,21 +14467,21 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>6425</v>
+        <v>4361</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -14496,10 +14491,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>811751</v>
+        <v>811445</v>
       </c>
       <c r="R137" t="n">
-        <v>7391929</v>
+        <v>7391835</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14558,10 +14553,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>119541115</v>
+        <v>119541043</v>
       </c>
       <c r="B138" t="n">
-        <v>91840</v>
+        <v>91463</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
@@ -14570,25 +14565,25 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -14598,10 +14593,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>811544</v>
+        <v>811147</v>
       </c>
       <c r="R138" t="n">
-        <v>7391770</v>
+        <v>7391872</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -14660,10 +14655,10 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>119541129</v>
+        <v>119541049</v>
       </c>
       <c r="B139" t="n">
-        <v>91840</v>
+        <v>91463</v>
       </c>
       <c r="C139" t="inlineStr">
         <is>
@@ -14672,25 +14667,25 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -14700,10 +14695,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>811545</v>
+        <v>811251</v>
       </c>
       <c r="R139" t="n">
-        <v>7391850</v>
+        <v>7391796</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -14762,7 +14757,7 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>119541075</v>
+        <v>119541078</v>
       </c>
       <c r="B140" t="n">
         <v>96868</v>
@@ -14802,10 +14797,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>811178</v>
+        <v>811192</v>
       </c>
       <c r="R140" t="n">
-        <v>7391829</v>
+        <v>7391862</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -14864,10 +14859,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>119541030</v>
+        <v>119541040</v>
       </c>
       <c r="B141" t="n">
-        <v>79115</v>
+        <v>56522</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
@@ -14876,25 +14871,25 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -14904,10 +14899,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>811122</v>
+        <v>811186</v>
       </c>
       <c r="R141" t="n">
-        <v>7391953</v>
+        <v>7391822</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -14948,7 +14943,6 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
@@ -14967,10 +14961,10 @@
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>119541078</v>
+        <v>119541048</v>
       </c>
       <c r="B142" t="n">
-        <v>96868</v>
+        <v>91463</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
@@ -14979,25 +14973,25 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>221941</v>
+        <v>4745</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
@@ -15007,10 +15001,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>811192</v>
+        <v>811437</v>
       </c>
       <c r="R142" t="n">
-        <v>7391862</v>
+        <v>7391823</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -15069,10 +15063,10 @@
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>119541172</v>
+        <v>119541034</v>
       </c>
       <c r="B143" t="n">
-        <v>91834</v>
+        <v>56522</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
@@ -15081,25 +15075,25 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>4362</v>
+        <v>100138</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
@@ -15109,10 +15103,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>811367</v>
+        <v>811472</v>
       </c>
       <c r="R143" t="n">
-        <v>7391855</v>
+        <v>7391805</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -15171,10 +15165,10 @@
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>119541104</v>
+        <v>119541176</v>
       </c>
       <c r="B144" t="n">
-        <v>78526</v>
+        <v>91834</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
@@ -15187,21 +15181,21 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
@@ -15211,10 +15205,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>811313</v>
+        <v>811608</v>
       </c>
       <c r="R144" t="n">
-        <v>7391795</v>
+        <v>7391803</v>
       </c>
       <c r="S144" t="n">
         <v>10</v>
@@ -15273,10 +15267,10 @@
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>119541080</v>
+        <v>119541158</v>
       </c>
       <c r="B145" t="n">
-        <v>56525</v>
+        <v>91840</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
@@ -15289,21 +15283,21 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>102613</v>
+        <v>4364</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
@@ -15313,10 +15307,10 @@
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>811181</v>
+        <v>811003</v>
       </c>
       <c r="R145" t="n">
-        <v>7391940</v>
+        <v>7392012</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -15375,10 +15369,10 @@
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>119541038</v>
+        <v>119541104</v>
       </c>
       <c r="B146" t="n">
-        <v>56522</v>
+        <v>78526</v>
       </c>
       <c r="C146" t="inlineStr">
         <is>
@@ -15387,25 +15381,25 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
@@ -15415,10 +15409,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>811354</v>
+        <v>811313</v>
       </c>
       <c r="R146" t="n">
-        <v>7391760</v>
+        <v>7391795</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -15477,10 +15471,10 @@
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>119541138</v>
+        <v>119541184</v>
       </c>
       <c r="B147" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
@@ -15489,25 +15483,25 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -15517,10 +15511,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>811172</v>
+        <v>811258</v>
       </c>
       <c r="R147" t="n">
-        <v>7391843</v>
+        <v>7391832</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -15579,10 +15573,10 @@
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>119541119</v>
+        <v>119541173</v>
       </c>
       <c r="B148" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
@@ -15591,25 +15585,25 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -15619,10 +15613,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>811661</v>
+        <v>811366</v>
       </c>
       <c r="R148" t="n">
-        <v>7391873</v>
+        <v>7391825</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -15681,10 +15675,10 @@
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>119541058</v>
+        <v>119541146</v>
       </c>
       <c r="B149" t="n">
-        <v>57326</v>
+        <v>91840</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
@@ -15693,25 +15687,25 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -15721,7 +15715,7 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>811109</v>
+        <v>811255</v>
       </c>
       <c r="R149" t="n">
         <v>7391871</v>
@@ -15783,7 +15777,7 @@
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>119541142</v>
+        <v>119541122</v>
       </c>
       <c r="B150" t="n">
         <v>91840</v>
@@ -15823,10 +15817,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>811226</v>
+        <v>811803</v>
       </c>
       <c r="R150" t="n">
-        <v>7391836</v>
+        <v>7391929</v>
       </c>
       <c r="S150" t="n">
         <v>10</v>
@@ -15885,7 +15879,7 @@
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>119541148</v>
+        <v>119541116</v>
       </c>
       <c r="B151" t="n">
         <v>91840</v>
@@ -15925,10 +15919,10 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>811222</v>
+        <v>811589</v>
       </c>
       <c r="R151" t="n">
-        <v>7391892</v>
+        <v>7391777</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -15987,7 +15981,7 @@
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>119541134</v>
+        <v>119541154</v>
       </c>
       <c r="B152" t="n">
         <v>91840</v>
@@ -16027,10 +16021,10 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>811445</v>
+        <v>811034</v>
       </c>
       <c r="R152" t="n">
-        <v>7391835</v>
+        <v>7391905</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -16089,10 +16083,10 @@
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>119541046</v>
+        <v>119541114</v>
       </c>
       <c r="B153" t="n">
-        <v>91463</v>
+        <v>91840</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
@@ -16101,25 +16095,25 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
@@ -16129,10 +16123,10 @@
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>811712</v>
+        <v>811522</v>
       </c>
       <c r="R153" t="n">
-        <v>7391868</v>
+        <v>7391777</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -16191,10 +16185,10 @@
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>119541076</v>
+        <v>119541086</v>
       </c>
       <c r="B154" t="n">
-        <v>96868</v>
+        <v>91832</v>
       </c>
       <c r="C154" t="inlineStr">
         <is>
@@ -16203,25 +16197,25 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>221941</v>
+        <v>4361</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
@@ -16231,10 +16225,10 @@
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>811175</v>
+        <v>811036</v>
       </c>
       <c r="R154" t="n">
-        <v>7391844</v>
+        <v>7391909</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -16293,10 +16287,10 @@
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>119541149</v>
+        <v>119541186</v>
       </c>
       <c r="B155" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
@@ -16305,25 +16299,25 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
@@ -16333,10 +16327,10 @@
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>811213</v>
+        <v>811144</v>
       </c>
       <c r="R155" t="n">
-        <v>7391876</v>
+        <v>7391927</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -16395,10 +16389,10 @@
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>119541146</v>
+        <v>119541178</v>
       </c>
       <c r="B156" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
@@ -16407,25 +16401,25 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -16435,10 +16429,10 @@
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>811255</v>
+        <v>811475</v>
       </c>
       <c r="R156" t="n">
-        <v>7391871</v>
+        <v>7391925</v>
       </c>
       <c r="S156" t="n">
         <v>10</v>
@@ -16497,10 +16491,10 @@
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>119541060</v>
+        <v>119541077</v>
       </c>
       <c r="B157" t="n">
-        <v>57326</v>
+        <v>96868</v>
       </c>
       <c r="C157" t="inlineStr">
         <is>
@@ -16509,25 +16503,25 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>100049</v>
+        <v>221941</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
@@ -16537,10 +16531,10 @@
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>811547</v>
+        <v>811196</v>
       </c>
       <c r="R157" t="n">
-        <v>7391873</v>
+        <v>7391824</v>
       </c>
       <c r="S157" t="n">
         <v>10</v>
@@ -16599,10 +16593,10 @@
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>119541077</v>
+        <v>119541069</v>
       </c>
       <c r="B158" t="n">
-        <v>96868</v>
+        <v>91852</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
@@ -16615,21 +16609,21 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>221941</v>
+        <v>4366</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
@@ -16639,10 +16633,10 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>811196</v>
+        <v>811140</v>
       </c>
       <c r="R158" t="n">
-        <v>7391824</v>
+        <v>7391897</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -16701,10 +16695,10 @@
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>119541081</v>
+        <v>119541065</v>
       </c>
       <c r="B159" t="n">
-        <v>91832</v>
+        <v>91852</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
@@ -16713,25 +16707,25 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>4361</v>
+        <v>4366</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I159" t="inlineStr"/>
@@ -16741,10 +16735,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>811187</v>
+        <v>810977</v>
       </c>
       <c r="R159" t="n">
-        <v>7391879</v>
+        <v>7392031</v>
       </c>
       <c r="S159" t="n">
         <v>10</v>
@@ -16803,10 +16797,10 @@
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>119541187</v>
+        <v>119541151</v>
       </c>
       <c r="B160" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
@@ -16815,25 +16809,25 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
@@ -16843,10 +16837,10 @@
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>811107</v>
+        <v>811142</v>
       </c>
       <c r="R160" t="n">
-        <v>7391952</v>
+        <v>7391892</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -16905,10 +16899,10 @@
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>119541055</v>
+        <v>119541131</v>
       </c>
       <c r="B161" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
@@ -16917,25 +16911,25 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -16945,10 +16939,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>811375</v>
+        <v>811559</v>
       </c>
       <c r="R161" t="n">
-        <v>7391770</v>
+        <v>7391807</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -17007,7 +17001,7 @@
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>119541116</v>
+        <v>119541129</v>
       </c>
       <c r="B162" t="n">
         <v>91840</v>
@@ -17047,10 +17041,10 @@
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>811589</v>
+        <v>811545</v>
       </c>
       <c r="R162" t="n">
-        <v>7391777</v>
+        <v>7391850</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -17109,7 +17103,7 @@
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>119541151</v>
+        <v>119541123</v>
       </c>
       <c r="B163" t="n">
         <v>91840</v>
@@ -17149,10 +17143,10 @@
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>811142</v>
+        <v>811693</v>
       </c>
       <c r="R163" t="n">
-        <v>7391892</v>
+        <v>7391895</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -17211,10 +17205,10 @@
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119541122</v>
+        <v>119541068</v>
       </c>
       <c r="B164" t="n">
-        <v>91840</v>
+        <v>91852</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
@@ -17227,21 +17221,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -17251,10 +17245,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>811803</v>
+        <v>811247</v>
       </c>
       <c r="R164" t="n">
-        <v>7391929</v>
+        <v>7391907</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -17313,10 +17307,10 @@
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>119541131</v>
+        <v>119541101</v>
       </c>
       <c r="B165" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C165" t="inlineStr">
         <is>
@@ -17325,25 +17319,25 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I165" t="inlineStr"/>
@@ -17353,10 +17347,10 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>811559</v>
+        <v>811120</v>
       </c>
       <c r="R165" t="n">
-        <v>7391807</v>
+        <v>7391955</v>
       </c>
       <c r="S165" t="n">
         <v>10</v>
@@ -17415,10 +17409,10 @@
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>119541176</v>
+        <v>119541100</v>
       </c>
       <c r="B166" t="n">
-        <v>91834</v>
+        <v>78262</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
@@ -17431,21 +17425,21 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
@@ -17455,10 +17449,10 @@
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>811608</v>
+        <v>811290</v>
       </c>
       <c r="R166" t="n">
-        <v>7391803</v>
+        <v>7391801</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -17517,10 +17511,10 @@
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>119541085</v>
+        <v>119541098</v>
       </c>
       <c r="B167" t="n">
-        <v>91832</v>
+        <v>78262</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
@@ -17533,21 +17527,21 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>4361</v>
+        <v>6446</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -17557,10 +17551,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>811445</v>
+        <v>811353</v>
       </c>
       <c r="R167" t="n">
-        <v>7391835</v>
+        <v>7391859</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -17619,10 +17613,10 @@
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>119541086</v>
+        <v>119541054</v>
       </c>
       <c r="B168" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C168" t="inlineStr">
         <is>
@@ -17635,21 +17629,21 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
@@ -17659,10 +17653,10 @@
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>811036</v>
+        <v>811358</v>
       </c>
       <c r="R168" t="n">
-        <v>7391909</v>
+        <v>7391815</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -17721,10 +17715,10 @@
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>119541057</v>
+        <v>119541030</v>
       </c>
       <c r="B169" t="n">
-        <v>91884</v>
+        <v>79115</v>
       </c>
       <c r="C169" t="inlineStr">
         <is>
@@ -17737,21 +17731,21 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5449</v>
+        <v>229821</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
@@ -17761,10 +17755,10 @@
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>811123</v>
+        <v>811122</v>
       </c>
       <c r="R169" t="n">
-        <v>7391919</v>
+        <v>7391953</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -17805,6 +17799,7 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
+      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
@@ -17823,10 +17818,10 @@
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>119541101</v>
+        <v>119541031</v>
       </c>
       <c r="B170" t="n">
-        <v>78262</v>
+        <v>56522</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
@@ -17835,25 +17830,25 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -17863,10 +17858,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>811120</v>
+        <v>811012</v>
       </c>
       <c r="R170" t="n">
-        <v>7391955</v>
+        <v>7392154</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -17893,12 +17888,12 @@
       </c>
       <c r="Y170" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -17925,10 +17920,10 @@
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>119541158</v>
+        <v>119541071</v>
       </c>
       <c r="B171" t="n">
-        <v>91840</v>
+        <v>96868</v>
       </c>
       <c r="C171" t="inlineStr">
         <is>
@@ -17941,21 +17936,21 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
@@ -17965,10 +17960,10 @@
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>811003</v>
+        <v>811599</v>
       </c>
       <c r="R171" t="n">
-        <v>7392012</v>
+        <v>7391829</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -18027,10 +18022,10 @@
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>119541064</v>
+        <v>119541095</v>
       </c>
       <c r="B172" t="n">
-        <v>91856</v>
+        <v>78263</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
@@ -18043,21 +18038,21 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>2059</v>
+        <v>228912</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I172" t="inlineStr"/>
@@ -18067,10 +18062,10 @@
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>811042</v>
+        <v>811019</v>
       </c>
       <c r="R172" t="n">
-        <v>7391966</v>
+        <v>7392058</v>
       </c>
       <c r="S172" t="n">
         <v>10</v>
@@ -18129,10 +18124,10 @@
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>119541181</v>
+        <v>119541144</v>
       </c>
       <c r="B173" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
@@ -18141,25 +18136,25 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -18169,10 +18164,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>811465</v>
+        <v>811266</v>
       </c>
       <c r="R173" t="n">
-        <v>7391838</v>
+        <v>7391829</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -18231,10 +18226,10 @@
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>119541069</v>
+        <v>119541135</v>
       </c>
       <c r="B174" t="n">
-        <v>91852</v>
+        <v>91840</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
@@ -18247,21 +18242,21 @@
         </is>
       </c>
       <c r="E174" t="n">
-        <v>4366</v>
+        <v>4364</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I174" t="inlineStr"/>
@@ -18271,10 +18266,10 @@
         </is>
       </c>
       <c r="Q174" t="n">
-        <v>811140</v>
+        <v>811304</v>
       </c>
       <c r="R174" t="n">
-        <v>7391897</v>
+        <v>7391760</v>
       </c>
       <c r="S174" t="n">
         <v>10</v>
@@ -18333,10 +18328,10 @@
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>119541074</v>
+        <v>119541181</v>
       </c>
       <c r="B175" t="n">
-        <v>96868</v>
+        <v>91834</v>
       </c>
       <c r="C175" t="inlineStr">
         <is>
@@ -18345,25 +18340,25 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E175" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I175" t="inlineStr"/>
@@ -18373,10 +18368,10 @@
         </is>
       </c>
       <c r="Q175" t="n">
-        <v>811554</v>
+        <v>811465</v>
       </c>
       <c r="R175" t="n">
-        <v>7391879</v>
+        <v>7391838</v>
       </c>
       <c r="S175" t="n">
         <v>10</v>
@@ -18435,10 +18430,10 @@
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>119541039</v>
+        <v>119541045</v>
       </c>
       <c r="B176" t="n">
-        <v>56522</v>
+        <v>91463</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
@@ -18447,25 +18442,25 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E176" t="n">
-        <v>100138</v>
+        <v>4745</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I176" t="inlineStr"/>
@@ -18475,10 +18470,10 @@
         </is>
       </c>
       <c r="Q176" t="n">
-        <v>811215</v>
+        <v>811207</v>
       </c>
       <c r="R176" t="n">
-        <v>7391820</v>
+        <v>7391947</v>
       </c>
       <c r="S176" t="n">
         <v>10</v>
@@ -18537,10 +18532,10 @@
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>119541034</v>
+        <v>119541066</v>
       </c>
       <c r="B177" t="n">
-        <v>56522</v>
+        <v>91852</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
@@ -18553,21 +18548,21 @@
         </is>
       </c>
       <c r="E177" t="n">
-        <v>100138</v>
+        <v>4366</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I177" t="inlineStr"/>
@@ -18577,10 +18572,10 @@
         </is>
       </c>
       <c r="Q177" t="n">
-        <v>811472</v>
+        <v>811361</v>
       </c>
       <c r="R177" t="n">
-        <v>7391805</v>
+        <v>7391844</v>
       </c>
       <c r="S177" t="n">
         <v>10</v>
@@ -18639,10 +18634,10 @@
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>119541184</v>
+        <v>119541130</v>
       </c>
       <c r="B178" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
@@ -18651,25 +18646,25 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E178" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I178" t="inlineStr"/>
@@ -18679,10 +18674,10 @@
         </is>
       </c>
       <c r="Q178" t="n">
-        <v>811258</v>
+        <v>811571</v>
       </c>
       <c r="R178" t="n">
-        <v>7391832</v>
+        <v>7391809</v>
       </c>
       <c r="S178" t="n">
         <v>10</v>
@@ -18741,10 +18736,10 @@
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>119541056</v>
+        <v>119541150</v>
       </c>
       <c r="B179" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
@@ -18753,25 +18748,25 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E179" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I179" t="inlineStr"/>
@@ -18781,10 +18776,10 @@
         </is>
       </c>
       <c r="Q179" t="n">
-        <v>811402</v>
+        <v>811181</v>
       </c>
       <c r="R179" t="n">
-        <v>7391791</v>
+        <v>7391849</v>
       </c>
       <c r="S179" t="n">
         <v>10</v>
@@ -18843,10 +18838,10 @@
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>119541105</v>
+        <v>119541117</v>
       </c>
       <c r="B180" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C180" t="inlineStr">
         <is>
@@ -18855,25 +18850,25 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E180" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I180" t="inlineStr"/>
@@ -18883,10 +18878,10 @@
         </is>
       </c>
       <c r="Q180" t="n">
-        <v>811251</v>
+        <v>811616</v>
       </c>
       <c r="R180" t="n">
-        <v>7391852</v>
+        <v>7391803</v>
       </c>
       <c r="S180" t="n">
         <v>10</v>
@@ -18945,10 +18940,10 @@
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>119541139</v>
+        <v>119541082</v>
       </c>
       <c r="B181" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
@@ -18957,25 +18952,25 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I181" t="inlineStr"/>
@@ -18985,10 +18980,10 @@
         </is>
       </c>
       <c r="Q181" t="n">
-        <v>811223</v>
+        <v>811354</v>
       </c>
       <c r="R181" t="n">
-        <v>7391823</v>
+        <v>7391857</v>
       </c>
       <c r="S181" t="n">
         <v>10</v>
@@ -19047,10 +19042,10 @@
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>119541033</v>
+        <v>119541126</v>
       </c>
       <c r="B182" t="n">
-        <v>56522</v>
+        <v>91840</v>
       </c>
       <c r="C182" t="inlineStr">
         <is>
@@ -19063,21 +19058,21 @@
         </is>
       </c>
       <c r="E182" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I182" t="inlineStr"/>
@@ -19087,10 +19082,10 @@
         </is>
       </c>
       <c r="Q182" t="n">
-        <v>811505</v>
+        <v>811473</v>
       </c>
       <c r="R182" t="n">
-        <v>7391980</v>
+        <v>7391962</v>
       </c>
       <c r="S182" t="n">
         <v>10</v>
@@ -19123,11 +19118,6 @@
       <c r="AA182" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC182" t="inlineStr">
-        <is>
-          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD182" t="b">
@@ -19154,10 +19144,10 @@
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>119541114</v>
+        <v>119541081</v>
       </c>
       <c r="B183" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
@@ -19166,25 +19156,25 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I183" t="inlineStr"/>
@@ -19194,10 +19184,10 @@
         </is>
       </c>
       <c r="Q183" t="n">
-        <v>811522</v>
+        <v>811187</v>
       </c>
       <c r="R183" t="n">
-        <v>7391777</v>
+        <v>7391879</v>
       </c>
       <c r="S183" t="n">
         <v>10</v>
@@ -19256,10 +19246,10 @@
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>119541127</v>
+        <v>119541084</v>
       </c>
       <c r="B184" t="n">
-        <v>91840</v>
+        <v>91832</v>
       </c>
       <c r="C184" t="inlineStr">
         <is>
@@ -19268,25 +19258,25 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I184" t="inlineStr"/>
@@ -19296,10 +19286,10 @@
         </is>
       </c>
       <c r="Q184" t="n">
-        <v>811557</v>
+        <v>811768</v>
       </c>
       <c r="R184" t="n">
-        <v>7391884</v>
+        <v>7391938</v>
       </c>
       <c r="S184" t="n">
         <v>10</v>
@@ -19358,10 +19348,10 @@
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>119541157</v>
+        <v>119541056</v>
       </c>
       <c r="B185" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C185" t="inlineStr">
         <is>
@@ -19370,25 +19360,25 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E185" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I185" t="inlineStr"/>
@@ -19398,10 +19388,10 @@
         </is>
       </c>
       <c r="Q185" t="n">
-        <v>811006</v>
+        <v>811402</v>
       </c>
       <c r="R185" t="n">
-        <v>7391996</v>
+        <v>7391791</v>
       </c>
       <c r="S185" t="n">
         <v>10</v>
@@ -19460,10 +19450,10 @@
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>119541156</v>
+        <v>119541106</v>
       </c>
       <c r="B186" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C186" t="inlineStr">
         <is>
@@ -19472,25 +19462,25 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I186" t="inlineStr"/>
@@ -19500,10 +19490,10 @@
         </is>
       </c>
       <c r="Q186" t="n">
-        <v>811039</v>
+        <v>810962</v>
       </c>
       <c r="R186" t="n">
-        <v>7391919</v>
+        <v>7392039</v>
       </c>
       <c r="S186" t="n">
         <v>10</v>
@@ -19562,10 +19552,10 @@
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>119541079</v>
+        <v>119541080</v>
       </c>
       <c r="B187" t="n">
-        <v>96868</v>
+        <v>56525</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -19578,21 +19568,21 @@
         </is>
       </c>
       <c r="E187" t="n">
-        <v>221941</v>
+        <v>102613</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I187" t="inlineStr"/>
@@ -19602,10 +19592,10 @@
         </is>
       </c>
       <c r="Q187" t="n">
-        <v>811182</v>
+        <v>811181</v>
       </c>
       <c r="R187" t="n">
-        <v>7391854</v>
+        <v>7391940</v>
       </c>
       <c r="S187" t="n">
         <v>10</v>
@@ -19766,10 +19756,10 @@
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>119541174</v>
+        <v>119541124</v>
       </c>
       <c r="B189" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
@@ -19778,25 +19768,25 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I189" t="inlineStr"/>
@@ -19806,10 +19796,10 @@
         </is>
       </c>
       <c r="Q189" t="n">
-        <v>811427</v>
+        <v>811523</v>
       </c>
       <c r="R189" t="n">
-        <v>7391805</v>
+        <v>7391986</v>
       </c>
       <c r="S189" t="n">
         <v>10</v>
@@ -19868,7 +19858,7 @@
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>119541163</v>
+        <v>119541162</v>
       </c>
       <c r="B190" t="n">
         <v>91840</v>
@@ -19908,10 +19898,10 @@
         </is>
       </c>
       <c r="Q190" t="n">
-        <v>810984</v>
+        <v>811007</v>
       </c>
       <c r="R190" t="n">
-        <v>7392025</v>
+        <v>7392021</v>
       </c>
       <c r="S190" t="n">
         <v>10</v>
@@ -19970,7 +19960,7 @@
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>119541143</v>
+        <v>119541139</v>
       </c>
       <c r="B191" t="n">
         <v>91840</v>
@@ -20010,10 +20000,10 @@
         </is>
       </c>
       <c r="Q191" t="n">
-        <v>811263</v>
+        <v>811223</v>
       </c>
       <c r="R191" t="n">
-        <v>7391814</v>
+        <v>7391823</v>
       </c>
       <c r="S191" t="n">
         <v>10</v>
@@ -20072,10 +20062,10 @@
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>119541107</v>
+        <v>119541046</v>
       </c>
       <c r="B192" t="n">
-        <v>91840</v>
+        <v>91463</v>
       </c>
       <c r="C192" t="inlineStr">
         <is>
@@ -20084,25 +20074,25 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E192" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I192" t="inlineStr"/>
@@ -20112,10 +20102,10 @@
         </is>
       </c>
       <c r="Q192" t="n">
-        <v>811147</v>
+        <v>811712</v>
       </c>
       <c r="R192" t="n">
-        <v>7391914</v>
+        <v>7391868</v>
       </c>
       <c r="S192" t="n">
         <v>10</v>
@@ -20174,10 +20164,10 @@
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>119541162</v>
+        <v>119541033</v>
       </c>
       <c r="B193" t="n">
-        <v>91840</v>
+        <v>56522</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
@@ -20190,21 +20180,21 @@
         </is>
       </c>
       <c r="E193" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I193" t="inlineStr"/>
@@ -20214,10 +20204,10 @@
         </is>
       </c>
       <c r="Q193" t="n">
-        <v>811007</v>
+        <v>811505</v>
       </c>
       <c r="R193" t="n">
-        <v>7392021</v>
+        <v>7391980</v>
       </c>
       <c r="S193" t="n">
         <v>10</v>
@@ -20250,6 +20240,11 @@
       <c r="AA193" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD193" t="b">
@@ -20276,10 +20271,10 @@
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>119541179</v>
+        <v>119541063</v>
       </c>
       <c r="B194" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
@@ -20292,21 +20287,21 @@
         </is>
       </c>
       <c r="E194" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I194" t="inlineStr"/>
@@ -20316,10 +20311,10 @@
         </is>
       </c>
       <c r="Q194" t="n">
-        <v>811496</v>
+        <v>811474</v>
       </c>
       <c r="R194" t="n">
-        <v>7391933</v>
+        <v>7391808</v>
       </c>
       <c r="S194" t="n">
         <v>10</v>
@@ -20378,10 +20373,10 @@
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>119541188</v>
+        <v>119541087</v>
       </c>
       <c r="B195" t="n">
-        <v>91834</v>
+        <v>78263</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
@@ -20394,21 +20389,21 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>4362</v>
+        <v>228912</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I195" t="inlineStr"/>
@@ -20418,10 +20413,10 @@
         </is>
       </c>
       <c r="Q195" t="n">
-        <v>811059</v>
+        <v>811167</v>
       </c>
       <c r="R195" t="n">
-        <v>7391942</v>
+        <v>7391874</v>
       </c>
       <c r="S195" t="n">
         <v>10</v>
@@ -20462,6 +20457,7 @@
       <c r="AE195" t="b">
         <v>0</v>
       </c>
+      <c r="AF195" t="inlineStr"/>
       <c r="AG195" t="b">
         <v>0</v>
       </c>
@@ -20480,7 +20476,7 @@
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>119541178</v>
+        <v>119541190</v>
       </c>
       <c r="B196" t="n">
         <v>91834</v>
@@ -20520,10 +20516,10 @@
         </is>
       </c>
       <c r="Q196" t="n">
-        <v>811475</v>
+        <v>811005</v>
       </c>
       <c r="R196" t="n">
-        <v>7391925</v>
+        <v>7391977</v>
       </c>
       <c r="S196" t="n">
         <v>10</v>
@@ -20582,10 +20578,10 @@
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>119541035</v>
+        <v>119541120</v>
       </c>
       <c r="B197" t="n">
-        <v>56522</v>
+        <v>91840</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
@@ -20598,21 +20594,21 @@
         </is>
       </c>
       <c r="E197" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I197" t="inlineStr"/>
@@ -20622,10 +20618,10 @@
         </is>
       </c>
       <c r="Q197" t="n">
-        <v>811805</v>
+        <v>811720</v>
       </c>
       <c r="R197" t="n">
-        <v>7391923</v>
+        <v>7391872</v>
       </c>
       <c r="S197" t="n">
         <v>10</v>
@@ -20684,10 +20680,10 @@
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>119541095</v>
+        <v>119541110</v>
       </c>
       <c r="B198" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
@@ -20696,25 +20692,25 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I198" t="inlineStr"/>
@@ -20724,10 +20720,10 @@
         </is>
       </c>
       <c r="Q198" t="n">
-        <v>811019</v>
+        <v>811189</v>
       </c>
       <c r="R198" t="n">
-        <v>7392058</v>
+        <v>7391809</v>
       </c>
       <c r="S198" t="n">
         <v>10</v>
@@ -20786,10 +20782,10 @@
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>119541092</v>
+        <v>119541141</v>
       </c>
       <c r="B199" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
@@ -20798,25 +20794,25 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E199" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I199" t="inlineStr"/>
@@ -20826,10 +20822,10 @@
         </is>
       </c>
       <c r="Q199" t="n">
-        <v>811155</v>
+        <v>811243</v>
       </c>
       <c r="R199" t="n">
-        <v>7391931</v>
+        <v>7391854</v>
       </c>
       <c r="S199" t="n">
         <v>10</v>
@@ -20888,10 +20884,10 @@
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>119541183</v>
+        <v>119541149</v>
       </c>
       <c r="B200" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C200" t="inlineStr">
         <is>
@@ -20900,25 +20896,25 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E200" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I200" t="inlineStr"/>
@@ -20928,10 +20924,10 @@
         </is>
       </c>
       <c r="Q200" t="n">
-        <v>811180</v>
+        <v>811213</v>
       </c>
       <c r="R200" t="n">
-        <v>7391829</v>
+        <v>7391876</v>
       </c>
       <c r="S200" t="n">
         <v>10</v>
@@ -20990,10 +20986,10 @@
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>119541177</v>
+        <v>119541156</v>
       </c>
       <c r="B201" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
@@ -21002,25 +20998,25 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E201" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I201" t="inlineStr"/>
@@ -21030,10 +21026,10 @@
         </is>
       </c>
       <c r="Q201" t="n">
-        <v>811607</v>
+        <v>811039</v>
       </c>
       <c r="R201" t="n">
-        <v>7391859</v>
+        <v>7391919</v>
       </c>
       <c r="S201" t="n">
         <v>10</v>
@@ -21092,10 +21088,10 @@
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>119541043</v>
+        <v>119541147</v>
       </c>
       <c r="B202" t="n">
-        <v>91463</v>
+        <v>91840</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
@@ -21104,25 +21100,25 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E202" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I202" t="inlineStr"/>
@@ -21132,10 +21128,10 @@
         </is>
       </c>
       <c r="Q202" t="n">
-        <v>811147</v>
+        <v>811248</v>
       </c>
       <c r="R202" t="n">
-        <v>7391872</v>
+        <v>7391873</v>
       </c>
       <c r="S202" t="n">
         <v>10</v>
@@ -21194,10 +21190,10 @@
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>119541045</v>
+        <v>119541172</v>
       </c>
       <c r="B203" t="n">
-        <v>91463</v>
+        <v>91834</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
@@ -21210,21 +21206,21 @@
         </is>
       </c>
       <c r="E203" t="n">
-        <v>4745</v>
+        <v>4362</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I203" t="inlineStr"/>
@@ -21234,10 +21230,10 @@
         </is>
       </c>
       <c r="Q203" t="n">
-        <v>811207</v>
+        <v>811367</v>
       </c>
       <c r="R203" t="n">
-        <v>7391947</v>
+        <v>7391855</v>
       </c>
       <c r="S203" t="n">
         <v>10</v>
@@ -21296,10 +21292,10 @@
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>119541044</v>
+        <v>119541163</v>
       </c>
       <c r="B204" t="n">
-        <v>91463</v>
+        <v>91840</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
@@ -21308,25 +21304,25 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E204" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I204" t="inlineStr"/>
@@ -21336,10 +21332,10 @@
         </is>
       </c>
       <c r="Q204" t="n">
-        <v>811162</v>
+        <v>810984</v>
       </c>
       <c r="R204" t="n">
-        <v>7391926</v>
+        <v>7392025</v>
       </c>
       <c r="S204" t="n">
         <v>10</v>
@@ -21398,10 +21394,10 @@
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>119541103</v>
+        <v>119541175</v>
       </c>
       <c r="B205" t="n">
-        <v>78526</v>
+        <v>91834</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
@@ -21414,21 +21410,21 @@
         </is>
       </c>
       <c r="E205" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I205" t="inlineStr"/>
@@ -21438,10 +21434,10 @@
         </is>
       </c>
       <c r="Q205" t="n">
-        <v>811689</v>
+        <v>811484</v>
       </c>
       <c r="R205" t="n">
-        <v>7391899</v>
+        <v>7391790</v>
       </c>
       <c r="S205" t="n">
         <v>10</v>
@@ -21500,10 +21496,10 @@
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>119541070</v>
+        <v>119541059</v>
       </c>
       <c r="B206" t="n">
-        <v>91852</v>
+        <v>57326</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
@@ -21512,25 +21508,25 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E206" t="n">
-        <v>4366</v>
+        <v>100049</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I206" t="inlineStr"/>
@@ -21540,10 +21536,10 @@
         </is>
       </c>
       <c r="Q206" t="n">
-        <v>810940</v>
+        <v>811490</v>
       </c>
       <c r="R206" t="n">
-        <v>7392041</v>
+        <v>7391874</v>
       </c>
       <c r="S206" t="n">
         <v>10</v>
@@ -21602,7 +21598,7 @@
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>119541154</v>
+        <v>119541134</v>
       </c>
       <c r="B207" t="n">
         <v>91840</v>
@@ -21642,10 +21638,10 @@
         </is>
       </c>
       <c r="Q207" t="n">
-        <v>811034</v>
+        <v>811445</v>
       </c>
       <c r="R207" t="n">
-        <v>7391905</v>
+        <v>7391835</v>
       </c>
       <c r="S207" t="n">
         <v>10</v>
@@ -21704,10 +21700,10 @@
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>119541113</v>
+        <v>119541180</v>
       </c>
       <c r="B208" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
@@ -21716,25 +21712,25 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E208" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I208" t="inlineStr"/>
@@ -21744,10 +21740,10 @@
         </is>
       </c>
       <c r="Q208" t="n">
-        <v>811489</v>
+        <v>811501</v>
       </c>
       <c r="R208" t="n">
-        <v>7391792</v>
+        <v>7391868</v>
       </c>
       <c r="S208" t="n">
         <v>10</v>
@@ -21806,10 +21802,10 @@
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>119541090</v>
+        <v>119541187</v>
       </c>
       <c r="B209" t="n">
-        <v>78263</v>
+        <v>91834</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
@@ -21822,21 +21818,21 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>228912</v>
+        <v>4362</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I209" t="inlineStr"/>
@@ -21846,10 +21842,10 @@
         </is>
       </c>
       <c r="Q209" t="n">
-        <v>811788</v>
+        <v>811107</v>
       </c>
       <c r="R209" t="n">
-        <v>7391959</v>
+        <v>7391952</v>
       </c>
       <c r="S209" t="n">
         <v>10</v>
@@ -21908,10 +21904,10 @@
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>119541120</v>
+        <v>119541096</v>
       </c>
       <c r="B210" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
@@ -21920,25 +21916,25 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E210" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I210" t="inlineStr"/>
@@ -21948,10 +21944,10 @@
         </is>
       </c>
       <c r="Q210" t="n">
-        <v>811720</v>
+        <v>810955</v>
       </c>
       <c r="R210" t="n">
-        <v>7391872</v>
+        <v>7392033</v>
       </c>
       <c r="S210" t="n">
         <v>10</v>
@@ -22010,10 +22006,10 @@
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>119541065</v>
+        <v>119541032</v>
       </c>
       <c r="B211" t="n">
-        <v>91852</v>
+        <v>56522</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
@@ -22026,21 +22022,21 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>4366</v>
+        <v>100138</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I211" t="inlineStr"/>
@@ -22050,10 +22046,10 @@
         </is>
       </c>
       <c r="Q211" t="n">
-        <v>810977</v>
+        <v>811213</v>
       </c>
       <c r="R211" t="n">
-        <v>7392031</v>
+        <v>7391942</v>
       </c>
       <c r="S211" t="n">
         <v>10</v>
@@ -22086,6 +22082,11 @@
       <c r="AA211" t="inlineStr">
         <is>
           <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AC211" t="inlineStr">
+        <is>
+          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD211" t="b">
@@ -22112,10 +22113,10 @@
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>119541132</v>
+        <v>119541076</v>
       </c>
       <c r="B212" t="n">
-        <v>91840</v>
+        <v>96868</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
@@ -22128,21 +22129,21 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I212" t="inlineStr"/>
@@ -22152,10 +22153,10 @@
         </is>
       </c>
       <c r="Q212" t="n">
-        <v>811532</v>
+        <v>811175</v>
       </c>
       <c r="R212" t="n">
-        <v>7391774</v>
+        <v>7391844</v>
       </c>
       <c r="S212" t="n">
         <v>10</v>
@@ -22214,10 +22215,10 @@
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>119541098</v>
+        <v>119541177</v>
       </c>
       <c r="B213" t="n">
-        <v>78262</v>
+        <v>91834</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
@@ -22230,21 +22231,21 @@
         </is>
       </c>
       <c r="E213" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I213" t="inlineStr"/>
@@ -22254,7 +22255,7 @@
         </is>
       </c>
       <c r="Q213" t="n">
-        <v>811353</v>
+        <v>811607</v>
       </c>
       <c r="R213" t="n">
         <v>7391859</v>
@@ -22316,10 +22317,10 @@
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>119541071</v>
+        <v>119541025</v>
       </c>
       <c r="B214" t="n">
-        <v>96868</v>
+        <v>91836</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
@@ -22332,21 +22333,21 @@
         </is>
       </c>
       <c r="E214" t="n">
-        <v>221941</v>
+        <v>4363</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Zontaggsvamp</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum concrescens</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Banker</t>
         </is>
       </c>
       <c r="I214" t="inlineStr"/>
@@ -22356,10 +22357,10 @@
         </is>
       </c>
       <c r="Q214" t="n">
-        <v>811599</v>
+        <v>811673</v>
       </c>
       <c r="R214" t="n">
-        <v>7391829</v>
+        <v>7391865</v>
       </c>
       <c r="S214" t="n">
         <v>10</v>
@@ -22418,10 +22419,10 @@
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>119541180</v>
+        <v>119541115</v>
       </c>
       <c r="B215" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
@@ -22430,25 +22431,25 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E215" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I215" t="inlineStr"/>
@@ -22458,10 +22459,10 @@
         </is>
       </c>
       <c r="Q215" t="n">
-        <v>811501</v>
+        <v>811544</v>
       </c>
       <c r="R215" t="n">
-        <v>7391868</v>
+        <v>7391770</v>
       </c>
       <c r="S215" t="n">
         <v>10</v>
@@ -22520,10 +22521,10 @@
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>119541051</v>
+        <v>119541153</v>
       </c>
       <c r="B216" t="n">
-        <v>90953</v>
+        <v>91840</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
@@ -22532,20 +22533,25 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E216" t="n">
-        <v>6040162</v>
+        <v>4364</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I216" t="inlineStr"/>
@@ -22555,10 +22561,10 @@
         </is>
       </c>
       <c r="Q216" t="n">
-        <v>811305</v>
+        <v>811147</v>
       </c>
       <c r="R216" t="n">
-        <v>7391791</v>
+        <v>7391936</v>
       </c>
       <c r="S216" t="n">
         <v>10</v>
@@ -22599,7 +22605,6 @@
       <c r="AE216" t="b">
         <v>0</v>
       </c>
-      <c r="AF216" t="inlineStr"/>
       <c r="AG216" t="b">
         <v>0</v>
       </c>
@@ -22618,10 +22623,10 @@
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>119541125</v>
+        <v>119541039</v>
       </c>
       <c r="B217" t="n">
-        <v>91840</v>
+        <v>56522</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
@@ -22634,21 +22639,21 @@
         </is>
       </c>
       <c r="E217" t="n">
-        <v>4364</v>
+        <v>100138</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I217" t="inlineStr"/>
@@ -22658,10 +22663,10 @@
         </is>
       </c>
       <c r="Q217" t="n">
-        <v>811502</v>
+        <v>811215</v>
       </c>
       <c r="R217" t="n">
-        <v>7391976</v>
+        <v>7391820</v>
       </c>
       <c r="S217" t="n">
         <v>10</v>
@@ -22720,10 +22725,10 @@
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>119541144</v>
+        <v>119541092</v>
       </c>
       <c r="B218" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
@@ -22732,25 +22737,25 @@
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E218" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G218" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I218" t="inlineStr"/>
@@ -22760,10 +22765,10 @@
         </is>
       </c>
       <c r="Q218" t="n">
-        <v>811266</v>
+        <v>811155</v>
       </c>
       <c r="R218" t="n">
-        <v>7391829</v>
+        <v>7391931</v>
       </c>
       <c r="S218" t="n">
         <v>10</v>
@@ -22822,10 +22827,10 @@
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>119541175</v>
+        <v>119541061</v>
       </c>
       <c r="B219" t="n">
-        <v>91834</v>
+        <v>91856</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
@@ -22838,21 +22843,21 @@
         </is>
       </c>
       <c r="E219" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I219" t="inlineStr"/>
@@ -22862,10 +22867,10 @@
         </is>
       </c>
       <c r="Q219" t="n">
-        <v>811484</v>
+        <v>811158</v>
       </c>
       <c r="R219" t="n">
-        <v>7391790</v>
+        <v>7391914</v>
       </c>
       <c r="S219" t="n">
         <v>10</v>
@@ -22924,10 +22929,10 @@
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>119541082</v>
+        <v>119541044</v>
       </c>
       <c r="B220" t="n">
-        <v>91832</v>
+        <v>91463</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
@@ -22940,21 +22945,21 @@
         </is>
       </c>
       <c r="E220" t="n">
-        <v>4361</v>
+        <v>4745</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I220" t="inlineStr"/>
@@ -22964,10 +22969,10 @@
         </is>
       </c>
       <c r="Q220" t="n">
-        <v>811354</v>
+        <v>811162</v>
       </c>
       <c r="R220" t="n">
-        <v>7391857</v>
+        <v>7391926</v>
       </c>
       <c r="S220" t="n">
         <v>10</v>
@@ -23026,10 +23031,10 @@
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>119541059</v>
+        <v>119541107</v>
       </c>
       <c r="B221" t="n">
-        <v>57326</v>
+        <v>91840</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
@@ -23038,25 +23043,25 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E221" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G221" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I221" t="inlineStr"/>
@@ -23066,10 +23071,10 @@
         </is>
       </c>
       <c r="Q221" t="n">
-        <v>811490</v>
+        <v>811147</v>
       </c>
       <c r="R221" t="n">
-        <v>7391874</v>
+        <v>7391914</v>
       </c>
       <c r="S221" t="n">
         <v>10</v>
@@ -23128,10 +23133,10 @@
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>119541032</v>
+        <v>119541105</v>
       </c>
       <c r="B222" t="n">
-        <v>56522</v>
+        <v>78526</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
@@ -23140,25 +23145,25 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E222" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I222" t="inlineStr"/>
@@ -23168,10 +23173,10 @@
         </is>
       </c>
       <c r="Q222" t="n">
-        <v>811213</v>
+        <v>811251</v>
       </c>
       <c r="R222" t="n">
-        <v>7391942</v>
+        <v>7391852</v>
       </c>
       <c r="S222" t="n">
         <v>10</v>
@@ -23204,11 +23209,6 @@
       <c r="AA222" t="inlineStr">
         <is>
           <t>2024-08-15</t>
-        </is>
-      </c>
-      <c r="AC222" t="inlineStr">
-        <is>
-          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD222" t="b">
@@ -23235,10 +23235,10 @@
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>119541089</v>
+        <v>119541083</v>
       </c>
       <c r="B223" t="n">
-        <v>78263</v>
+        <v>91832</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
@@ -23251,21 +23251,21 @@
         </is>
       </c>
       <c r="E223" t="n">
-        <v>228912</v>
+        <v>4361</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I223" t="inlineStr"/>
@@ -23275,10 +23275,10 @@
         </is>
       </c>
       <c r="Q223" t="n">
-        <v>811635</v>
+        <v>811752</v>
       </c>
       <c r="R223" t="n">
-        <v>7391860</v>
+        <v>7391915</v>
       </c>
       <c r="S223" t="n">
         <v>10</v>
@@ -23337,10 +23337,10 @@
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>119541096</v>
+        <v>119541165</v>
       </c>
       <c r="B224" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
@@ -23349,25 +23349,25 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E224" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I224" t="inlineStr"/>
@@ -23377,10 +23377,10 @@
         </is>
       </c>
       <c r="Q224" t="n">
-        <v>810955</v>
+        <v>810902</v>
       </c>
       <c r="R224" t="n">
-        <v>7392033</v>
+        <v>7392035</v>
       </c>
       <c r="S224" t="n">
         <v>10</v>
@@ -23439,10 +23439,10 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>119541041</v>
+        <v>119541113</v>
       </c>
       <c r="B225" t="n">
-        <v>91826</v>
+        <v>91840</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
@@ -23451,25 +23451,25 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E225" t="n">
-        <v>3100</v>
+        <v>4364</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G225" t="inlineStr">
         <is>
-          <t>Bankera fuligineoalba</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>(Schmidt : Fr.) Pouzar</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I225" t="inlineStr"/>
@@ -23479,10 +23479,10 @@
         </is>
       </c>
       <c r="Q225" t="n">
-        <v>810994</v>
+        <v>811489</v>
       </c>
       <c r="R225" t="n">
-        <v>7391976</v>
+        <v>7391792</v>
       </c>
       <c r="S225" t="n">
         <v>10</v>
@@ -23541,7 +23541,7 @@
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>119541135</v>
+        <v>119541125</v>
       </c>
       <c r="B226" t="n">
         <v>91840</v>
@@ -23581,10 +23581,10 @@
         </is>
       </c>
       <c r="Q226" t="n">
-        <v>811304</v>
+        <v>811502</v>
       </c>
       <c r="R226" t="n">
-        <v>7391760</v>
+        <v>7391976</v>
       </c>
       <c r="S226" t="n">
         <v>10</v>
@@ -23643,7 +23643,7 @@
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>119541110</v>
+        <v>119541118</v>
       </c>
       <c r="B227" t="n">
         <v>91840</v>
@@ -23683,10 +23683,10 @@
         </is>
       </c>
       <c r="Q227" t="n">
-        <v>811189</v>
+        <v>811600</v>
       </c>
       <c r="R227" t="n">
-        <v>7391809</v>
+        <v>7391842</v>
       </c>
       <c r="S227" t="n">
         <v>10</v>
@@ -23745,10 +23745,10 @@
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>119541123</v>
+        <v>119541074</v>
       </c>
       <c r="B228" t="n">
-        <v>91840</v>
+        <v>96868</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
@@ -23761,21 +23761,21 @@
         </is>
       </c>
       <c r="E228" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
@@ -23785,10 +23785,10 @@
         </is>
       </c>
       <c r="Q228" t="n">
-        <v>811693</v>
+        <v>811554</v>
       </c>
       <c r="R228" t="n">
-        <v>7391895</v>
+        <v>7391879</v>
       </c>
       <c r="S228" t="n">
         <v>10</v>
@@ -23847,10 +23847,10 @@
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>119541153</v>
+        <v>119541089</v>
       </c>
       <c r="B229" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
@@ -23859,25 +23859,25 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E229" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
@@ -23887,10 +23887,10 @@
         </is>
       </c>
       <c r="Q229" t="n">
-        <v>811147</v>
+        <v>811635</v>
       </c>
       <c r="R229" t="n">
-        <v>7391936</v>
+        <v>7391860</v>
       </c>
       <c r="S229" t="n">
         <v>10</v>
@@ -23949,10 +23949,10 @@
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>119541031</v>
+        <v>119541091</v>
       </c>
       <c r="B230" t="n">
-        <v>56522</v>
+        <v>78263</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
@@ -23961,25 +23961,25 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E230" t="n">
-        <v>100138</v>
+        <v>228912</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
@@ -23989,10 +23989,10 @@
         </is>
       </c>
       <c r="Q230" t="n">
-        <v>811012</v>
+        <v>811814</v>
       </c>
       <c r="R230" t="n">
-        <v>7392154</v>
+        <v>7391907</v>
       </c>
       <c r="S230" t="n">
         <v>10</v>
@@ -24019,12 +24019,12 @@
       </c>
       <c r="Y230" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA230" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD230" t="b">
@@ -24051,10 +24051,10 @@
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>119541186</v>
+        <v>119541099</v>
       </c>
       <c r="B231" t="n">
-        <v>91834</v>
+        <v>78262</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
@@ -24067,21 +24067,21 @@
         </is>
       </c>
       <c r="E231" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
@@ -24091,10 +24091,10 @@
         </is>
       </c>
       <c r="Q231" t="n">
-        <v>811144</v>
+        <v>811540</v>
       </c>
       <c r="R231" t="n">
-        <v>7391927</v>
+        <v>7391755</v>
       </c>
       <c r="S231" t="n">
         <v>10</v>

--- a/artfynd/A 10151-2023 artfynd.xlsx
+++ b/artfynd/A 10151-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY231"/>
+  <dimension ref="A1:AY232"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24151,6 +24151,108 @@
       </c>
       <c r="AY231" t="inlineStr"/>
     </row>
+    <row r="232">
+      <c r="A232" t="n">
+        <v>120402148</v>
+      </c>
+      <c r="B232" t="n">
+        <v>91862</v>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E232" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H232" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I232" t="inlineStr"/>
+      <c r="P232" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q232" t="n">
+        <v>811248</v>
+      </c>
+      <c r="R232" t="n">
+        <v>7391857</v>
+      </c>
+      <c r="S232" t="n">
+        <v>10</v>
+      </c>
+      <c r="T232" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U232" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W232" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y232" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AA232" t="inlineStr">
+        <is>
+          <t>2024-08-15</t>
+        </is>
+      </c>
+      <c r="AD232" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE232" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG232" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT232" t="inlineStr"/>
+      <c r="AW232" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX232" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY232" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10151-2023 artfynd.xlsx
+++ b/artfynd/A 10151-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY232"/>
+  <dimension ref="A1:AY298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24253,6 +24253,6740 @@
       </c>
       <c r="AY232" t="inlineStr"/>
     </row>
+    <row r="233">
+      <c r="A233" t="n">
+        <v>120434872</v>
+      </c>
+      <c r="B233" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E233" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H233" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I233" t="inlineStr"/>
+      <c r="P233" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q233" t="n">
+        <v>811073</v>
+      </c>
+      <c r="R233" t="n">
+        <v>7391995</v>
+      </c>
+      <c r="S233" t="n">
+        <v>10</v>
+      </c>
+      <c r="T233" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U233" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W233" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y233" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA233" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD233" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE233" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG233" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT233" t="inlineStr"/>
+      <c r="AW233" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX233" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY233" t="inlineStr"/>
+    </row>
+    <row r="234">
+      <c r="A234" t="n">
+        <v>120434828</v>
+      </c>
+      <c r="B234" t="n">
+        <v>91904</v>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E234" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I234" t="inlineStr"/>
+      <c r="P234" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q234" t="n">
+        <v>811160</v>
+      </c>
+      <c r="R234" t="n">
+        <v>7392120</v>
+      </c>
+      <c r="S234" t="n">
+        <v>10</v>
+      </c>
+      <c r="T234" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U234" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W234" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y234" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA234" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD234" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE234" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF234" t="inlineStr"/>
+      <c r="AG234" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT234" t="inlineStr"/>
+      <c r="AW234" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX234" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY234" t="inlineStr"/>
+    </row>
+    <row r="235">
+      <c r="A235" t="n">
+        <v>120434854</v>
+      </c>
+      <c r="B235" t="n">
+        <v>78278</v>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E235" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I235" t="inlineStr"/>
+      <c r="P235" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q235" t="n">
+        <v>811151</v>
+      </c>
+      <c r="R235" t="n">
+        <v>7392024</v>
+      </c>
+      <c r="S235" t="n">
+        <v>10</v>
+      </c>
+      <c r="T235" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U235" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V235" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W235" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y235" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA235" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD235" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE235" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG235" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT235" t="inlineStr"/>
+      <c r="AW235" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX235" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY235" t="inlineStr"/>
+    </row>
+    <row r="236">
+      <c r="A236" t="n">
+        <v>120434852</v>
+      </c>
+      <c r="B236" t="n">
+        <v>57431</v>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E236" t="n">
+        <v>103031</v>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>Lavskrika</t>
+        </is>
+      </c>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>Perisoreus infaustus</t>
+        </is>
+      </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I236" t="inlineStr"/>
+      <c r="P236" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q236" t="n">
+        <v>810910</v>
+      </c>
+      <c r="R236" t="n">
+        <v>7392005</v>
+      </c>
+      <c r="S236" t="n">
+        <v>10</v>
+      </c>
+      <c r="T236" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U236" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V236" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W236" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y236" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA236" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD236" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE236" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG236" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT236" t="inlineStr"/>
+      <c r="AW236" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX236" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY236" t="inlineStr"/>
+    </row>
+    <row r="237">
+      <c r="A237" t="n">
+        <v>120434846</v>
+      </c>
+      <c r="B237" t="n">
+        <v>96891</v>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E237" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I237" t="inlineStr"/>
+      <c r="P237" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q237" t="n">
+        <v>811187</v>
+      </c>
+      <c r="R237" t="n">
+        <v>7392082</v>
+      </c>
+      <c r="S237" t="n">
+        <v>10</v>
+      </c>
+      <c r="T237" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U237" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V237" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W237" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y237" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA237" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD237" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE237" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG237" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT237" t="inlineStr"/>
+      <c r="AW237" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX237" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY237" t="inlineStr"/>
+    </row>
+    <row r="238">
+      <c r="A238" t="n">
+        <v>120434898</v>
+      </c>
+      <c r="B238" t="n">
+        <v>91852</v>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E238" t="n">
+        <v>4362</v>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>Blå taggsvamp</t>
+        </is>
+      </c>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>Hydnellum caeruleum</t>
+        </is>
+      </c>
+      <c r="H238" t="inlineStr">
+        <is>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I238" t="inlineStr"/>
+      <c r="P238" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q238" t="n">
+        <v>811095</v>
+      </c>
+      <c r="R238" t="n">
+        <v>7392048</v>
+      </c>
+      <c r="S238" t="n">
+        <v>10</v>
+      </c>
+      <c r="T238" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U238" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V238" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W238" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y238" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA238" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG238" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT238" t="inlineStr"/>
+      <c r="AW238" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX238" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY238" t="inlineStr"/>
+    </row>
+    <row r="239">
+      <c r="A239" t="n">
+        <v>120434853</v>
+      </c>
+      <c r="B239" t="n">
+        <v>78278</v>
+      </c>
+      <c r="C239" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D239" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E239" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H239" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I239" t="inlineStr"/>
+      <c r="P239" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q239" t="n">
+        <v>811148</v>
+      </c>
+      <c r="R239" t="n">
+        <v>7391971</v>
+      </c>
+      <c r="S239" t="n">
+        <v>10</v>
+      </c>
+      <c r="T239" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U239" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V239" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W239" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y239" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA239" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD239" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE239" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG239" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT239" t="inlineStr"/>
+      <c r="AW239" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX239" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY239" t="inlineStr"/>
+    </row>
+    <row r="240">
+      <c r="A240" t="n">
+        <v>120434831</v>
+      </c>
+      <c r="B240" t="n">
+        <v>91901</v>
+      </c>
+      <c r="C240" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D240" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E240" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>Phellodon connatus</t>
+        </is>
+      </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr"/>
+      <c r="P240" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q240" t="n">
+        <v>811112</v>
+      </c>
+      <c r="R240" t="n">
+        <v>7392215</v>
+      </c>
+      <c r="S240" t="n">
+        <v>10</v>
+      </c>
+      <c r="T240" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U240" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V240" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W240" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y240" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA240" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD240" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE240" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG240" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT240" t="inlineStr"/>
+      <c r="AW240" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX240" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY240" t="inlineStr"/>
+    </row>
+    <row r="241">
+      <c r="A241" t="n">
+        <v>120434838</v>
+      </c>
+      <c r="B241" t="n">
+        <v>91839</v>
+      </c>
+      <c r="C241" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D241" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E241" t="n">
+        <v>6055</v>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>Spadskinn</t>
+        </is>
+      </c>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>Stereopsis vitellina</t>
+        </is>
+      </c>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>(S.Lundell) D.A.Reid</t>
+        </is>
+      </c>
+      <c r="I241" t="inlineStr"/>
+      <c r="P241" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q241" t="n">
+        <v>811032</v>
+      </c>
+      <c r="R241" t="n">
+        <v>7392087</v>
+      </c>
+      <c r="S241" t="n">
+        <v>10</v>
+      </c>
+      <c r="T241" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U241" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V241" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W241" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y241" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA241" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD241" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE241" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG241" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT241" t="inlineStr"/>
+      <c r="AW241" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX241" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="n">
+        <v>120434889</v>
+      </c>
+      <c r="B242" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C242" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D242" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E242" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H242" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I242" t="inlineStr"/>
+      <c r="P242" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q242" t="n">
+        <v>811045</v>
+      </c>
+      <c r="R242" t="n">
+        <v>7392096</v>
+      </c>
+      <c r="S242" t="n">
+        <v>10</v>
+      </c>
+      <c r="T242" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U242" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V242" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W242" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y242" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA242" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD242" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE242" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG242" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT242" t="inlineStr"/>
+      <c r="AW242" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX242" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY242" t="inlineStr"/>
+    </row>
+    <row r="243">
+      <c r="A243" t="n">
+        <v>120434895</v>
+      </c>
+      <c r="B243" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C243" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E243" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H243" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I243" t="inlineStr"/>
+      <c r="P243" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q243" t="n">
+        <v>811053</v>
+      </c>
+      <c r="R243" t="n">
+        <v>7392247</v>
+      </c>
+      <c r="S243" t="n">
+        <v>10</v>
+      </c>
+      <c r="T243" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U243" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V243" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W243" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y243" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA243" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD243" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE243" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG243" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT243" t="inlineStr"/>
+      <c r="AW243" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX243" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY243" t="inlineStr"/>
+    </row>
+    <row r="244">
+      <c r="A244" t="n">
+        <v>120434822</v>
+      </c>
+      <c r="B244" t="n">
+        <v>89650</v>
+      </c>
+      <c r="C244" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D244" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E244" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H244" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I244" t="inlineStr"/>
+      <c r="P244" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q244" t="n">
+        <v>811056</v>
+      </c>
+      <c r="R244" t="n">
+        <v>7392242</v>
+      </c>
+      <c r="S244" t="n">
+        <v>10</v>
+      </c>
+      <c r="T244" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U244" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V244" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W244" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y244" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA244" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD244" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE244" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG244" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT244" t="inlineStr"/>
+      <c r="AW244" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX244" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY244" t="inlineStr"/>
+    </row>
+    <row r="245">
+      <c r="A245" t="n">
+        <v>120434869</v>
+      </c>
+      <c r="B245" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C245" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D245" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E245" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I245" t="inlineStr"/>
+      <c r="P245" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q245" t="n">
+        <v>811038</v>
+      </c>
+      <c r="R245" t="n">
+        <v>7392074</v>
+      </c>
+      <c r="S245" t="n">
+        <v>10</v>
+      </c>
+      <c r="T245" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U245" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V245" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W245" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y245" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA245" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD245" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE245" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG245" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT245" t="inlineStr"/>
+      <c r="AW245" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX245" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY245" t="inlineStr"/>
+    </row>
+    <row r="246">
+      <c r="A246" t="n">
+        <v>120434842</v>
+      </c>
+      <c r="B246" t="n">
+        <v>91874</v>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E246" t="n">
+        <v>2059</v>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>Skrovlig taggsvamp</t>
+        </is>
+      </c>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>Hydnellum scabrosum</t>
+        </is>
+      </c>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I246" t="inlineStr"/>
+      <c r="P246" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q246" t="n">
+        <v>811110</v>
+      </c>
+      <c r="R246" t="n">
+        <v>7392006</v>
+      </c>
+      <c r="S246" t="n">
+        <v>10</v>
+      </c>
+      <c r="T246" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U246" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V246" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W246" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y246" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA246" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD246" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE246" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG246" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT246" t="inlineStr"/>
+      <c r="AW246" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX246" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="n">
+        <v>120434867</v>
+      </c>
+      <c r="B247" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E247" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H247" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I247" t="inlineStr"/>
+      <c r="P247" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q247" t="n">
+        <v>810911</v>
+      </c>
+      <c r="R247" t="n">
+        <v>7392181</v>
+      </c>
+      <c r="S247" t="n">
+        <v>10</v>
+      </c>
+      <c r="T247" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U247" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V247" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W247" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y247" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA247" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD247" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE247" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG247" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT247" t="inlineStr"/>
+      <c r="AW247" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX247" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY247" t="inlineStr"/>
+    </row>
+    <row r="248">
+      <c r="A248" t="n">
+        <v>120434855</v>
+      </c>
+      <c r="B248" t="n">
+        <v>78278</v>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E248" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H248" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I248" t="inlineStr"/>
+      <c r="P248" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q248" t="n">
+        <v>811078</v>
+      </c>
+      <c r="R248" t="n">
+        <v>7392236</v>
+      </c>
+      <c r="S248" t="n">
+        <v>10</v>
+      </c>
+      <c r="T248" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U248" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V248" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W248" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y248" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA248" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD248" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE248" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG248" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT248" t="inlineStr"/>
+      <c r="AW248" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX248" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY248" t="inlineStr"/>
+    </row>
+    <row r="249">
+      <c r="A249" t="n">
+        <v>120434871</v>
+      </c>
+      <c r="B249" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E249" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H249" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I249" t="inlineStr"/>
+      <c r="P249" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q249" t="n">
+        <v>811046</v>
+      </c>
+      <c r="R249" t="n">
+        <v>7392008</v>
+      </c>
+      <c r="S249" t="n">
+        <v>10</v>
+      </c>
+      <c r="T249" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U249" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V249" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W249" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y249" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA249" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD249" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE249" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG249" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT249" t="inlineStr"/>
+      <c r="AW249" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX249" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY249" t="inlineStr"/>
+    </row>
+    <row r="250">
+      <c r="A250" t="n">
+        <v>120434873</v>
+      </c>
+      <c r="B250" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E250" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I250" t="inlineStr"/>
+      <c r="P250" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q250" t="n">
+        <v>811170</v>
+      </c>
+      <c r="R250" t="n">
+        <v>7391994</v>
+      </c>
+      <c r="S250" t="n">
+        <v>10</v>
+      </c>
+      <c r="T250" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U250" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V250" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W250" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y250" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA250" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD250" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE250" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG250" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT250" t="inlineStr"/>
+      <c r="AW250" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX250" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY250" t="inlineStr"/>
+    </row>
+    <row r="251">
+      <c r="A251" t="n">
+        <v>120434818</v>
+      </c>
+      <c r="B251" t="n">
+        <v>89650</v>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E251" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I251" t="inlineStr"/>
+      <c r="P251" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q251" t="n">
+        <v>811170</v>
+      </c>
+      <c r="R251" t="n">
+        <v>7391994</v>
+      </c>
+      <c r="S251" t="n">
+        <v>10</v>
+      </c>
+      <c r="T251" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U251" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V251" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W251" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y251" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA251" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD251" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE251" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG251" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT251" t="inlineStr"/>
+      <c r="AW251" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX251" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY251" t="inlineStr"/>
+    </row>
+    <row r="252">
+      <c r="A252" t="n">
+        <v>120434894</v>
+      </c>
+      <c r="B252" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E252" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H252" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I252" t="inlineStr"/>
+      <c r="P252" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q252" t="n">
+        <v>811099</v>
+      </c>
+      <c r="R252" t="n">
+        <v>7392252</v>
+      </c>
+      <c r="S252" t="n">
+        <v>10</v>
+      </c>
+      <c r="T252" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U252" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V252" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W252" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y252" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA252" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD252" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE252" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG252" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT252" t="inlineStr"/>
+      <c r="AW252" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX252" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="n">
+        <v>120434890</v>
+      </c>
+      <c r="B253" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E253" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H253" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I253" t="inlineStr"/>
+      <c r="P253" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q253" t="n">
+        <v>811035</v>
+      </c>
+      <c r="R253" t="n">
+        <v>7392102</v>
+      </c>
+      <c r="S253" t="n">
+        <v>10</v>
+      </c>
+      <c r="T253" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U253" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V253" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W253" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y253" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA253" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD253" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE253" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG253" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT253" t="inlineStr"/>
+      <c r="AW253" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX253" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY253" t="inlineStr"/>
+    </row>
+    <row r="254">
+      <c r="A254" t="n">
+        <v>120434891</v>
+      </c>
+      <c r="B254" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E254" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H254" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I254" t="inlineStr"/>
+      <c r="P254" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q254" t="n">
+        <v>811023</v>
+      </c>
+      <c r="R254" t="n">
+        <v>7392157</v>
+      </c>
+      <c r="S254" t="n">
+        <v>10</v>
+      </c>
+      <c r="T254" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U254" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V254" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W254" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y254" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA254" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD254" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE254" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG254" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT254" t="inlineStr"/>
+      <c r="AW254" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX254" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY254" t="inlineStr"/>
+    </row>
+    <row r="255">
+      <c r="A255" t="n">
+        <v>120434877</v>
+      </c>
+      <c r="B255" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E255" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H255" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I255" t="inlineStr"/>
+      <c r="P255" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q255" t="n">
+        <v>811135</v>
+      </c>
+      <c r="R255" t="n">
+        <v>7392085</v>
+      </c>
+      <c r="S255" t="n">
+        <v>10</v>
+      </c>
+      <c r="T255" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U255" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V255" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W255" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y255" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA255" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD255" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE255" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG255" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT255" t="inlineStr"/>
+      <c r="AW255" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX255" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY255" t="inlineStr"/>
+    </row>
+    <row r="256">
+      <c r="A256" t="n">
+        <v>120434866</v>
+      </c>
+      <c r="B256" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E256" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H256" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I256" t="inlineStr"/>
+      <c r="P256" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q256" t="n">
+        <v>810910</v>
+      </c>
+      <c r="R256" t="n">
+        <v>7392182</v>
+      </c>
+      <c r="S256" t="n">
+        <v>10</v>
+      </c>
+      <c r="T256" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U256" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V256" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W256" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y256" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA256" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG256" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT256" t="inlineStr"/>
+      <c r="AW256" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX256" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY256" t="inlineStr"/>
+    </row>
+    <row r="257">
+      <c r="A257" t="n">
+        <v>120434821</v>
+      </c>
+      <c r="B257" t="n">
+        <v>89650</v>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E257" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H257" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I257" t="inlineStr"/>
+      <c r="P257" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q257" t="n">
+        <v>811073</v>
+      </c>
+      <c r="R257" t="n">
+        <v>7392186</v>
+      </c>
+      <c r="S257" t="n">
+        <v>10</v>
+      </c>
+      <c r="T257" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U257" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V257" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W257" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y257" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA257" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG257" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT257" t="inlineStr"/>
+      <c r="AW257" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX257" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY257" t="inlineStr"/>
+    </row>
+    <row r="258">
+      <c r="A258" t="n">
+        <v>120434819</v>
+      </c>
+      <c r="B258" t="n">
+        <v>89650</v>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E258" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H258" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I258" t="inlineStr"/>
+      <c r="P258" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q258" t="n">
+        <v>811135</v>
+      </c>
+      <c r="R258" t="n">
+        <v>7392091</v>
+      </c>
+      <c r="S258" t="n">
+        <v>10</v>
+      </c>
+      <c r="T258" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U258" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V258" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W258" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y258" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA258" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG258" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT258" t="inlineStr"/>
+      <c r="AW258" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX258" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY258" t="inlineStr"/>
+    </row>
+    <row r="259">
+      <c r="A259" t="n">
+        <v>120434884</v>
+      </c>
+      <c r="B259" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C259" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D259" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E259" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H259" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I259" t="inlineStr"/>
+      <c r="P259" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q259" t="n">
+        <v>811098</v>
+      </c>
+      <c r="R259" t="n">
+        <v>7392240</v>
+      </c>
+      <c r="S259" t="n">
+        <v>10</v>
+      </c>
+      <c r="T259" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U259" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V259" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W259" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y259" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA259" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD259" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE259" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG259" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT259" t="inlineStr"/>
+      <c r="AW259" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX259" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY259" t="inlineStr"/>
+    </row>
+    <row r="260">
+      <c r="A260" t="n">
+        <v>120434886</v>
+      </c>
+      <c r="B260" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C260" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D260" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E260" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I260" t="inlineStr"/>
+      <c r="P260" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q260" t="n">
+        <v>811121</v>
+      </c>
+      <c r="R260" t="n">
+        <v>7392171</v>
+      </c>
+      <c r="S260" t="n">
+        <v>10</v>
+      </c>
+      <c r="T260" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U260" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V260" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W260" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y260" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA260" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD260" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE260" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG260" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT260" t="inlineStr"/>
+      <c r="AW260" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX260" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY260" t="inlineStr"/>
+    </row>
+    <row r="261">
+      <c r="A261" t="n">
+        <v>120434881</v>
+      </c>
+      <c r="B261" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C261" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D261" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E261" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H261" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I261" t="inlineStr"/>
+      <c r="P261" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q261" t="n">
+        <v>811165</v>
+      </c>
+      <c r="R261" t="n">
+        <v>7392196</v>
+      </c>
+      <c r="S261" t="n">
+        <v>10</v>
+      </c>
+      <c r="T261" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U261" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V261" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W261" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y261" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA261" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD261" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE261" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG261" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT261" t="inlineStr"/>
+      <c r="AW261" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX261" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY261" t="inlineStr"/>
+    </row>
+    <row r="262">
+      <c r="A262" t="n">
+        <v>120434820</v>
+      </c>
+      <c r="B262" t="n">
+        <v>89650</v>
+      </c>
+      <c r="C262" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D262" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E262" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H262" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I262" t="inlineStr"/>
+      <c r="P262" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q262" t="n">
+        <v>811135</v>
+      </c>
+      <c r="R262" t="n">
+        <v>7392090</v>
+      </c>
+      <c r="S262" t="n">
+        <v>10</v>
+      </c>
+      <c r="T262" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U262" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V262" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W262" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y262" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA262" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD262" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE262" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG262" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT262" t="inlineStr"/>
+      <c r="AW262" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX262" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY262" t="inlineStr"/>
+    </row>
+    <row r="263">
+      <c r="A263" t="n">
+        <v>120434850</v>
+      </c>
+      <c r="B263" t="n">
+        <v>88170</v>
+      </c>
+      <c r="C263" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D263" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E263" t="n">
+        <v>4962</v>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>Mjölsvärting</t>
+        </is>
+      </c>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>Lyophyllum semitale</t>
+        </is>
+      </c>
+      <c r="H263" t="inlineStr">
+        <is>
+          <t>(Fr. : Fr.) Kühner</t>
+        </is>
+      </c>
+      <c r="I263" t="inlineStr"/>
+      <c r="P263" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q263" t="n">
+        <v>811200</v>
+      </c>
+      <c r="R263" t="n">
+        <v>7392176</v>
+      </c>
+      <c r="S263" t="n">
+        <v>10</v>
+      </c>
+      <c r="T263" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U263" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V263" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W263" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y263" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA263" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD263" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE263" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG263" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT263" t="inlineStr"/>
+      <c r="AW263" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX263" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY263" t="inlineStr"/>
+    </row>
+    <row r="264">
+      <c r="A264" t="n">
+        <v>120434829</v>
+      </c>
+      <c r="B264" t="n">
+        <v>91904</v>
+      </c>
+      <c r="C264" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D264" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E264" t="n">
+        <v>232140</v>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>Tajgataggsvamp</t>
+        </is>
+      </c>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>Phellodon secretus</t>
+        </is>
+      </c>
+      <c r="H264" t="inlineStr">
+        <is>
+          <t>Niemelä &amp; Kinnunen</t>
+        </is>
+      </c>
+      <c r="I264" t="inlineStr"/>
+      <c r="P264" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q264" t="n">
+        <v>811018</v>
+      </c>
+      <c r="R264" t="n">
+        <v>7392095</v>
+      </c>
+      <c r="S264" t="n">
+        <v>10</v>
+      </c>
+      <c r="T264" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U264" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V264" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W264" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y264" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA264" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD264" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE264" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF264" t="inlineStr"/>
+      <c r="AG264" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT264" t="inlineStr"/>
+      <c r="AW264" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX264" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY264" t="inlineStr"/>
+    </row>
+    <row r="265">
+      <c r="A265" t="n">
+        <v>120434874</v>
+      </c>
+      <c r="B265" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C265" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D265" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E265" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H265" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I265" t="inlineStr"/>
+      <c r="P265" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q265" t="n">
+        <v>811138</v>
+      </c>
+      <c r="R265" t="n">
+        <v>7392034</v>
+      </c>
+      <c r="S265" t="n">
+        <v>10</v>
+      </c>
+      <c r="T265" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U265" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V265" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W265" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y265" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA265" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD265" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE265" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG265" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT265" t="inlineStr"/>
+      <c r="AW265" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX265" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY265" t="inlineStr"/>
+    </row>
+    <row r="266">
+      <c r="A266" t="n">
+        <v>120434878</v>
+      </c>
+      <c r="B266" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C266" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E266" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H266" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I266" t="inlineStr"/>
+      <c r="P266" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q266" t="n">
+        <v>811137</v>
+      </c>
+      <c r="R266" t="n">
+        <v>7392085</v>
+      </c>
+      <c r="S266" t="n">
+        <v>10</v>
+      </c>
+      <c r="T266" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U266" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V266" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W266" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y266" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA266" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD266" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE266" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG266" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT266" t="inlineStr"/>
+      <c r="AW266" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX266" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY266" t="inlineStr"/>
+    </row>
+    <row r="267">
+      <c r="A267" t="n">
+        <v>120434876</v>
+      </c>
+      <c r="B267" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C267" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D267" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E267" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H267" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I267" t="inlineStr"/>
+      <c r="P267" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q267" t="n">
+        <v>811136</v>
+      </c>
+      <c r="R267" t="n">
+        <v>7392082</v>
+      </c>
+      <c r="S267" t="n">
+        <v>10</v>
+      </c>
+      <c r="T267" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U267" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V267" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W267" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y267" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA267" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD267" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE267" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG267" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT267" t="inlineStr"/>
+      <c r="AW267" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX267" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY267" t="inlineStr"/>
+    </row>
+    <row r="268">
+      <c r="A268" t="n">
+        <v>120434883</v>
+      </c>
+      <c r="B268" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C268" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D268" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E268" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H268" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I268" t="inlineStr"/>
+      <c r="P268" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q268" t="n">
+        <v>811129</v>
+      </c>
+      <c r="R268" t="n">
+        <v>7392249</v>
+      </c>
+      <c r="S268" t="n">
+        <v>10</v>
+      </c>
+      <c r="T268" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U268" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V268" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W268" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y268" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA268" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD268" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE268" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG268" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT268" t="inlineStr"/>
+      <c r="AW268" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX268" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY268" t="inlineStr"/>
+    </row>
+    <row r="269">
+      <c r="A269" t="n">
+        <v>120434885</v>
+      </c>
+      <c r="B269" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C269" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D269" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E269" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H269" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I269" t="inlineStr"/>
+      <c r="P269" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q269" t="n">
+        <v>811136</v>
+      </c>
+      <c r="R269" t="n">
+        <v>7392197</v>
+      </c>
+      <c r="S269" t="n">
+        <v>10</v>
+      </c>
+      <c r="T269" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U269" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V269" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W269" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y269" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA269" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD269" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE269" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG269" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT269" t="inlineStr"/>
+      <c r="AW269" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX269" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY269" t="inlineStr"/>
+    </row>
+    <row r="270">
+      <c r="A270" t="n">
+        <v>120434839</v>
+      </c>
+      <c r="B270" t="n">
+        <v>91862</v>
+      </c>
+      <c r="C270" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D270" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E270" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I270" t="inlineStr"/>
+      <c r="P270" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q270" t="n">
+        <v>811144</v>
+      </c>
+      <c r="R270" t="n">
+        <v>7392037</v>
+      </c>
+      <c r="S270" t="n">
+        <v>10</v>
+      </c>
+      <c r="T270" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U270" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V270" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W270" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y270" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA270" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD270" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE270" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG270" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT270" t="inlineStr"/>
+      <c r="AW270" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX270" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY270" t="inlineStr"/>
+    </row>
+    <row r="271">
+      <c r="A271" t="n">
+        <v>120434879</v>
+      </c>
+      <c r="B271" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C271" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D271" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E271" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H271" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I271" t="inlineStr"/>
+      <c r="P271" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q271" t="n">
+        <v>811161</v>
+      </c>
+      <c r="R271" t="n">
+        <v>7392143</v>
+      </c>
+      <c r="S271" t="n">
+        <v>10</v>
+      </c>
+      <c r="T271" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U271" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V271" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W271" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y271" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA271" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD271" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE271" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG271" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT271" t="inlineStr"/>
+      <c r="AW271" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX271" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY271" t="inlineStr"/>
+    </row>
+    <row r="272">
+      <c r="A272" t="n">
+        <v>120434823</v>
+      </c>
+      <c r="B272" t="n">
+        <v>89650</v>
+      </c>
+      <c r="C272" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D272" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E272" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H272" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I272" t="inlineStr"/>
+      <c r="P272" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q272" t="n">
+        <v>811063</v>
+      </c>
+      <c r="R272" t="n">
+        <v>7392237</v>
+      </c>
+      <c r="S272" t="n">
+        <v>10</v>
+      </c>
+      <c r="T272" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U272" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V272" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W272" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y272" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA272" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD272" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE272" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG272" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT272" t="inlineStr"/>
+      <c r="AW272" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX272" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY272" t="inlineStr"/>
+    </row>
+    <row r="273">
+      <c r="A273" t="n">
+        <v>120434841</v>
+      </c>
+      <c r="B273" t="n">
+        <v>91862</v>
+      </c>
+      <c r="C273" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D273" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E273" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H273" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I273" t="inlineStr"/>
+      <c r="P273" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q273" t="n">
+        <v>811019</v>
+      </c>
+      <c r="R273" t="n">
+        <v>7392096</v>
+      </c>
+      <c r="S273" t="n">
+        <v>10</v>
+      </c>
+      <c r="T273" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U273" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V273" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W273" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y273" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA273" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD273" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE273" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG273" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT273" t="inlineStr"/>
+      <c r="AW273" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX273" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY273" t="inlineStr"/>
+    </row>
+    <row r="274">
+      <c r="A274" t="n">
+        <v>120434851</v>
+      </c>
+      <c r="B274" t="n">
+        <v>88170</v>
+      </c>
+      <c r="C274" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D274" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E274" t="n">
+        <v>4962</v>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>Mjölsvärting</t>
+        </is>
+      </c>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>Lyophyllum semitale</t>
+        </is>
+      </c>
+      <c r="H274" t="inlineStr">
+        <is>
+          <t>(Fr. : Fr.) Kühner</t>
+        </is>
+      </c>
+      <c r="I274" t="inlineStr"/>
+      <c r="P274" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q274" t="n">
+        <v>811087</v>
+      </c>
+      <c r="R274" t="n">
+        <v>7392152</v>
+      </c>
+      <c r="S274" t="n">
+        <v>10</v>
+      </c>
+      <c r="T274" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U274" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V274" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W274" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y274" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA274" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD274" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE274" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG274" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT274" t="inlineStr"/>
+      <c r="AW274" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX274" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY274" t="inlineStr"/>
+    </row>
+    <row r="275">
+      <c r="A275" t="n">
+        <v>120434880</v>
+      </c>
+      <c r="B275" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C275" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D275" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E275" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I275" t="inlineStr"/>
+      <c r="P275" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q275" t="n">
+        <v>811219</v>
+      </c>
+      <c r="R275" t="n">
+        <v>7392151</v>
+      </c>
+      <c r="S275" t="n">
+        <v>10</v>
+      </c>
+      <c r="T275" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U275" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V275" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W275" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y275" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA275" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD275" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE275" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG275" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT275" t="inlineStr"/>
+      <c r="AW275" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX275" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY275" t="inlineStr"/>
+    </row>
+    <row r="276">
+      <c r="A276" t="n">
+        <v>120434892</v>
+      </c>
+      <c r="B276" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C276" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D276" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E276" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H276" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I276" t="inlineStr"/>
+      <c r="P276" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q276" t="n">
+        <v>811071</v>
+      </c>
+      <c r="R276" t="n">
+        <v>7392203</v>
+      </c>
+      <c r="S276" t="n">
+        <v>10</v>
+      </c>
+      <c r="T276" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U276" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V276" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W276" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y276" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA276" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD276" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE276" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG276" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT276" t="inlineStr"/>
+      <c r="AW276" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX276" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY276" t="inlineStr"/>
+    </row>
+    <row r="277">
+      <c r="A277" t="n">
+        <v>120434827</v>
+      </c>
+      <c r="B277" t="n">
+        <v>91481</v>
+      </c>
+      <c r="C277" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D277" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E277" t="n">
+        <v>4745</v>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>Tallriska</t>
+        </is>
+      </c>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>Lactarius musteus</t>
+        </is>
+      </c>
+      <c r="H277" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I277" t="inlineStr"/>
+      <c r="P277" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q277" t="n">
+        <v>810903</v>
+      </c>
+      <c r="R277" t="n">
+        <v>7392182</v>
+      </c>
+      <c r="S277" t="n">
+        <v>10</v>
+      </c>
+      <c r="T277" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U277" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V277" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W277" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y277" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA277" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD277" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE277" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG277" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT277" t="inlineStr"/>
+      <c r="AW277" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX277" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY277" t="inlineStr"/>
+    </row>
+    <row r="278">
+      <c r="A278" t="n">
+        <v>120434833</v>
+      </c>
+      <c r="B278" t="n">
+        <v>91901</v>
+      </c>
+      <c r="C278" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D278" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E278" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>Phellodon connatus</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr">
+        <is>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I278" t="inlineStr"/>
+      <c r="P278" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q278" t="n">
+        <v>810850</v>
+      </c>
+      <c r="R278" t="n">
+        <v>7392159</v>
+      </c>
+      <c r="S278" t="n">
+        <v>10</v>
+      </c>
+      <c r="T278" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U278" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V278" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W278" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y278" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA278" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD278" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE278" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG278" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT278" t="inlineStr"/>
+      <c r="AW278" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX278" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY278" t="inlineStr"/>
+    </row>
+    <row r="279">
+      <c r="A279" t="n">
+        <v>120434836</v>
+      </c>
+      <c r="B279" t="n">
+        <v>91902</v>
+      </c>
+      <c r="C279" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D279" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E279" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H279" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I279" t="inlineStr"/>
+      <c r="P279" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q279" t="n">
+        <v>811206</v>
+      </c>
+      <c r="R279" t="n">
+        <v>7392173</v>
+      </c>
+      <c r="S279" t="n">
+        <v>10</v>
+      </c>
+      <c r="T279" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U279" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V279" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W279" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y279" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA279" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD279" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE279" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG279" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT279" t="inlineStr"/>
+      <c r="AW279" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX279" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY279" t="inlineStr"/>
+    </row>
+    <row r="280">
+      <c r="A280" t="n">
+        <v>120434830</v>
+      </c>
+      <c r="B280" t="n">
+        <v>91902</v>
+      </c>
+      <c r="C280" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D280" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E280" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H280" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I280" t="inlineStr"/>
+      <c r="P280" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q280" t="n">
+        <v>811019</v>
+      </c>
+      <c r="R280" t="n">
+        <v>7392096</v>
+      </c>
+      <c r="S280" t="n">
+        <v>10</v>
+      </c>
+      <c r="T280" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U280" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V280" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W280" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y280" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA280" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD280" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE280" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG280" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT280" t="inlineStr"/>
+      <c r="AW280" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX280" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY280" t="inlineStr"/>
+    </row>
+    <row r="281">
+      <c r="A281" t="n">
+        <v>120434847</v>
+      </c>
+      <c r="B281" t="n">
+        <v>96891</v>
+      </c>
+      <c r="C281" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D281" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E281" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H281" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I281" t="inlineStr"/>
+      <c r="P281" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q281" t="n">
+        <v>811044</v>
+      </c>
+      <c r="R281" t="n">
+        <v>7392264</v>
+      </c>
+      <c r="S281" t="n">
+        <v>10</v>
+      </c>
+      <c r="T281" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U281" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V281" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W281" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y281" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA281" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD281" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE281" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG281" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT281" t="inlineStr"/>
+      <c r="AW281" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX281" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY281" t="inlineStr"/>
+    </row>
+    <row r="282">
+      <c r="A282" t="n">
+        <v>120434875</v>
+      </c>
+      <c r="B282" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C282" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D282" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E282" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H282" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I282" t="inlineStr"/>
+      <c r="P282" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q282" t="n">
+        <v>811108</v>
+      </c>
+      <c r="R282" t="n">
+        <v>7392073</v>
+      </c>
+      <c r="S282" t="n">
+        <v>10</v>
+      </c>
+      <c r="T282" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U282" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V282" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W282" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y282" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA282" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD282" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE282" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG282" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT282" t="inlineStr"/>
+      <c r="AW282" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX282" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY282" t="inlineStr"/>
+    </row>
+    <row r="283">
+      <c r="A283" t="n">
+        <v>120434899</v>
+      </c>
+      <c r="B283" t="n">
+        <v>91862</v>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D283" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E283" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I283" t="inlineStr"/>
+      <c r="P283" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q283" t="n">
+        <v>811192</v>
+      </c>
+      <c r="R283" t="n">
+        <v>7392146</v>
+      </c>
+      <c r="S283" t="n">
+        <v>10</v>
+      </c>
+      <c r="T283" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U283" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V283" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W283" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y283" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA283" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD283" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE283" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG283" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT283" t="inlineStr"/>
+      <c r="AW283" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX283" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY283" t="inlineStr"/>
+    </row>
+    <row r="284">
+      <c r="A284" t="n">
+        <v>120434865</v>
+      </c>
+      <c r="B284" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D284" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E284" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I284" t="inlineStr"/>
+      <c r="P284" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q284" t="n">
+        <v>810887</v>
+      </c>
+      <c r="R284" t="n">
+        <v>7392183</v>
+      </c>
+      <c r="S284" t="n">
+        <v>10</v>
+      </c>
+      <c r="T284" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U284" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V284" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W284" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y284" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA284" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD284" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE284" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG284" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT284" t="inlineStr"/>
+      <c r="AW284" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX284" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY284" t="inlineStr"/>
+    </row>
+    <row r="285">
+      <c r="A285" t="n">
+        <v>120434888</v>
+      </c>
+      <c r="B285" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E285" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H285" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I285" t="inlineStr"/>
+      <c r="P285" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q285" t="n">
+        <v>811101</v>
+      </c>
+      <c r="R285" t="n">
+        <v>7392164</v>
+      </c>
+      <c r="S285" t="n">
+        <v>10</v>
+      </c>
+      <c r="T285" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U285" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V285" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W285" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y285" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA285" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD285" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE285" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG285" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT285" t="inlineStr"/>
+      <c r="AW285" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX285" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY285" t="inlineStr"/>
+    </row>
+    <row r="286">
+      <c r="A286" t="n">
+        <v>120434845</v>
+      </c>
+      <c r="B286" t="n">
+        <v>96891</v>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D286" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E286" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I286" t="inlineStr"/>
+      <c r="P286" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q286" t="n">
+        <v>810859</v>
+      </c>
+      <c r="R286" t="n">
+        <v>7392159</v>
+      </c>
+      <c r="S286" t="n">
+        <v>10</v>
+      </c>
+      <c r="T286" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U286" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V286" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W286" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y286" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA286" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD286" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE286" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG286" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT286" t="inlineStr"/>
+      <c r="AW286" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX286" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY286" t="inlineStr"/>
+    </row>
+    <row r="287">
+      <c r="A287" t="n">
+        <v>120434893</v>
+      </c>
+      <c r="B287" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr"/>
+      <c r="P287" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q287" t="n">
+        <v>811088</v>
+      </c>
+      <c r="R287" t="n">
+        <v>7392240</v>
+      </c>
+      <c r="S287" t="n">
+        <v>10</v>
+      </c>
+      <c r="T287" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U287" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V287" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W287" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y287" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA287" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD287" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE287" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG287" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT287" t="inlineStr"/>
+      <c r="AW287" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX287" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY287" t="inlineStr"/>
+    </row>
+    <row r="288">
+      <c r="A288" t="n">
+        <v>120434840</v>
+      </c>
+      <c r="B288" t="n">
+        <v>91862</v>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E288" t="n">
+        <v>4365</v>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>Smalfotad taggsvamp</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>Hydnellum gracilipes</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>(P.Karst) P.Karst</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr"/>
+      <c r="P288" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q288" t="n">
+        <v>811025</v>
+      </c>
+      <c r="R288" t="n">
+        <v>7392081</v>
+      </c>
+      <c r="S288" t="n">
+        <v>10</v>
+      </c>
+      <c r="T288" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U288" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V288" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W288" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y288" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA288" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD288" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE288" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG288" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT288" t="inlineStr"/>
+      <c r="AW288" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX288" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY288" t="inlineStr"/>
+    </row>
+    <row r="289">
+      <c r="A289" t="n">
+        <v>120434832</v>
+      </c>
+      <c r="B289" t="n">
+        <v>91901</v>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D289" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E289" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>Phellodon connatus</t>
+        </is>
+      </c>
+      <c r="H289" t="inlineStr">
+        <is>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I289" t="inlineStr"/>
+      <c r="P289" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q289" t="n">
+        <v>811072</v>
+      </c>
+      <c r="R289" t="n">
+        <v>7392186</v>
+      </c>
+      <c r="S289" t="n">
+        <v>10</v>
+      </c>
+      <c r="T289" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U289" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V289" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W289" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y289" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA289" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD289" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE289" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG289" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT289" t="inlineStr"/>
+      <c r="AW289" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX289" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY289" t="inlineStr"/>
+    </row>
+    <row r="290">
+      <c r="A290" t="n">
+        <v>120434870</v>
+      </c>
+      <c r="B290" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D290" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E290" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H290" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I290" t="inlineStr"/>
+      <c r="P290" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q290" t="n">
+        <v>811034</v>
+      </c>
+      <c r="R290" t="n">
+        <v>7392011</v>
+      </c>
+      <c r="S290" t="n">
+        <v>10</v>
+      </c>
+      <c r="T290" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U290" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V290" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W290" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y290" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA290" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD290" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE290" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG290" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT290" t="inlineStr"/>
+      <c r="AW290" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX290" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY290" t="inlineStr"/>
+    </row>
+    <row r="291">
+      <c r="A291" t="n">
+        <v>120434864</v>
+      </c>
+      <c r="B291" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D291" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E291" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H291" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I291" t="inlineStr"/>
+      <c r="P291" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q291" t="n">
+        <v>810914</v>
+      </c>
+      <c r="R291" t="n">
+        <v>7392166</v>
+      </c>
+      <c r="S291" t="n">
+        <v>10</v>
+      </c>
+      <c r="T291" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U291" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V291" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W291" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y291" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA291" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD291" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE291" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG291" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT291" t="inlineStr"/>
+      <c r="AW291" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX291" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY291" t="inlineStr"/>
+    </row>
+    <row r="292">
+      <c r="A292" t="n">
+        <v>120434868</v>
+      </c>
+      <c r="B292" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D292" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E292" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H292" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I292" t="inlineStr"/>
+      <c r="P292" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q292" t="n">
+        <v>811010</v>
+      </c>
+      <c r="R292" t="n">
+        <v>7392090</v>
+      </c>
+      <c r="S292" t="n">
+        <v>10</v>
+      </c>
+      <c r="T292" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U292" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V292" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W292" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y292" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA292" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD292" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE292" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG292" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT292" t="inlineStr"/>
+      <c r="AW292" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX292" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY292" t="inlineStr"/>
+    </row>
+    <row r="293">
+      <c r="A293" t="n">
+        <v>120434849</v>
+      </c>
+      <c r="B293" t="n">
+        <v>88170</v>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D293" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E293" t="n">
+        <v>4962</v>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>Mjölsvärting</t>
+        </is>
+      </c>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>Lyophyllum semitale</t>
+        </is>
+      </c>
+      <c r="H293" t="inlineStr">
+        <is>
+          <t>(Fr. : Fr.) Kühner</t>
+        </is>
+      </c>
+      <c r="I293" t="inlineStr"/>
+      <c r="P293" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q293" t="n">
+        <v>811223</v>
+      </c>
+      <c r="R293" t="n">
+        <v>7392167</v>
+      </c>
+      <c r="S293" t="n">
+        <v>10</v>
+      </c>
+      <c r="T293" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U293" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V293" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W293" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y293" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA293" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD293" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE293" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG293" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT293" t="inlineStr"/>
+      <c r="AW293" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX293" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY293" t="inlineStr"/>
+    </row>
+    <row r="294">
+      <c r="A294" t="n">
+        <v>120434817</v>
+      </c>
+      <c r="B294" t="n">
+        <v>79160</v>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E294" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H294" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I294" t="inlineStr"/>
+      <c r="P294" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q294" t="n">
+        <v>811018</v>
+      </c>
+      <c r="R294" t="n">
+        <v>7392105</v>
+      </c>
+      <c r="S294" t="n">
+        <v>10</v>
+      </c>
+      <c r="T294" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U294" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V294" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W294" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y294" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA294" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD294" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE294" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG294" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT294" t="inlineStr"/>
+      <c r="AW294" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX294" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY294" t="inlineStr"/>
+    </row>
+    <row r="295">
+      <c r="A295" t="n">
+        <v>120434887</v>
+      </c>
+      <c r="B295" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E295" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H295" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I295" t="inlineStr"/>
+      <c r="P295" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q295" t="n">
+        <v>811128</v>
+      </c>
+      <c r="R295" t="n">
+        <v>7392175</v>
+      </c>
+      <c r="S295" t="n">
+        <v>10</v>
+      </c>
+      <c r="T295" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U295" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V295" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W295" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y295" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA295" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD295" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE295" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG295" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT295" t="inlineStr"/>
+      <c r="AW295" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX295" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY295" t="inlineStr"/>
+    </row>
+    <row r="296">
+      <c r="A296" t="n">
+        <v>120434835</v>
+      </c>
+      <c r="B296" t="n">
+        <v>91902</v>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E296" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H296" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I296" t="inlineStr"/>
+      <c r="P296" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q296" t="n">
+        <v>811225</v>
+      </c>
+      <c r="R296" t="n">
+        <v>7392170</v>
+      </c>
+      <c r="S296" t="n">
+        <v>10</v>
+      </c>
+      <c r="T296" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U296" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V296" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W296" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y296" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA296" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD296" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE296" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG296" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT296" t="inlineStr"/>
+      <c r="AW296" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX296" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY296" t="inlineStr"/>
+    </row>
+    <row r="297">
+      <c r="A297" t="n">
+        <v>120434837</v>
+      </c>
+      <c r="B297" t="n">
+        <v>91902</v>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E297" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H297" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr"/>
+      <c r="P297" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q297" t="n">
+        <v>811044</v>
+      </c>
+      <c r="R297" t="n">
+        <v>7392261</v>
+      </c>
+      <c r="S297" t="n">
+        <v>10</v>
+      </c>
+      <c r="T297" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U297" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V297" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W297" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y297" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA297" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD297" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE297" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG297" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT297" t="inlineStr"/>
+      <c r="AW297" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX297" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY297" t="inlineStr"/>
+    </row>
+    <row r="298">
+      <c r="A298" t="n">
+        <v>120434882</v>
+      </c>
+      <c r="B298" t="n">
+        <v>91858</v>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E298" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr"/>
+      <c r="P298" t="inlineStr">
+        <is>
+          <t>Gårsågielas, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q298" t="n">
+        <v>811166</v>
+      </c>
+      <c r="R298" t="n">
+        <v>7392206</v>
+      </c>
+      <c r="S298" t="n">
+        <v>10</v>
+      </c>
+      <c r="T298" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U298" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="V298" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W298" t="inlineStr">
+        <is>
+          <t>Gällivare</t>
+        </is>
+      </c>
+      <c r="Y298" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AA298" t="inlineStr">
+        <is>
+          <t>2024-10-15</t>
+        </is>
+      </c>
+      <c r="AD298" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE298" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG298" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT298" t="inlineStr"/>
+      <c r="AW298" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX298" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY298" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 10151-2023 artfynd.xlsx
+++ b/artfynd/A 10151-2023 artfynd.xlsx
@@ -24255,7 +24255,7 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>120434872</v>
+        <v>120434886</v>
       </c>
       <c r="B233" t="n">
         <v>91858</v>
@@ -24295,10 +24295,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>811073</v>
+        <v>811121</v>
       </c>
       <c r="R233" t="n">
-        <v>7391995</v>
+        <v>7392171</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24357,7 +24357,7 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>120434828</v>
+        <v>120434829</v>
       </c>
       <c r="B234" t="n">
         <v>91904</v>
@@ -24397,10 +24397,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>811160</v>
+        <v>811018</v>
       </c>
       <c r="R234" t="n">
-        <v>7392120</v>
+        <v>7392095</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24460,10 +24460,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>120434854</v>
+        <v>120434828</v>
       </c>
       <c r="B235" t="n">
-        <v>78278</v>
+        <v>91904</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -24472,25 +24472,25 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>6446</v>
+        <v>232140</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -24500,10 +24500,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>811151</v>
+        <v>811160</v>
       </c>
       <c r="R235" t="n">
-        <v>7392024</v>
+        <v>7392120</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -24544,6 +24544,7 @@
       <c r="AE235" t="b">
         <v>0</v>
       </c>
+      <c r="AF235" t="inlineStr"/>
       <c r="AG235" t="b">
         <v>0</v>
       </c>
@@ -24562,10 +24563,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>120434852</v>
+        <v>120434864</v>
       </c>
       <c r="B236" t="n">
-        <v>57431</v>
+        <v>91858</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -24578,21 +24579,21 @@
         </is>
       </c>
       <c r="E236" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -24602,10 +24603,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>810910</v>
+        <v>810914</v>
       </c>
       <c r="R236" t="n">
-        <v>7392005</v>
+        <v>7392166</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24664,10 +24665,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>120434846</v>
+        <v>120434881</v>
       </c>
       <c r="B237" t="n">
-        <v>96891</v>
+        <v>91858</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -24680,21 +24681,21 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -24704,10 +24705,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>811187</v>
+        <v>811165</v>
       </c>
       <c r="R237" t="n">
-        <v>7392082</v>
+        <v>7392196</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24766,10 +24767,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>120434898</v>
+        <v>120434871</v>
       </c>
       <c r="B238" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -24778,25 +24779,25 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -24806,10 +24807,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>811095</v>
+        <v>811046</v>
       </c>
       <c r="R238" t="n">
-        <v>7392048</v>
+        <v>7392008</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -24868,10 +24869,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>120434853</v>
+        <v>120434817</v>
       </c>
       <c r="B239" t="n">
-        <v>78278</v>
+        <v>79160</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -24884,21 +24885,21 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>6446</v>
+        <v>6453</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -24908,10 +24909,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>811148</v>
+        <v>811018</v>
       </c>
       <c r="R239" t="n">
-        <v>7391971</v>
+        <v>7392105</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24970,10 +24971,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>120434831</v>
+        <v>120434876</v>
       </c>
       <c r="B240" t="n">
-        <v>91901</v>
+        <v>91858</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -24982,25 +24983,25 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -25010,10 +25011,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>811112</v>
+        <v>811136</v>
       </c>
       <c r="R240" t="n">
-        <v>7392215</v>
+        <v>7392082</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25072,10 +25073,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>120434838</v>
+        <v>120434853</v>
       </c>
       <c r="B241" t="n">
-        <v>91839</v>
+        <v>78278</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -25084,25 +25085,25 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6055</v>
+        <v>6446</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -25112,10 +25113,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>811032</v>
+        <v>811148</v>
       </c>
       <c r="R241" t="n">
-        <v>7392087</v>
+        <v>7391971</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25174,10 +25175,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>120434889</v>
+        <v>120434833</v>
       </c>
       <c r="B242" t="n">
-        <v>91858</v>
+        <v>91901</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -25186,25 +25187,25 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -25214,10 +25215,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>811045</v>
+        <v>810850</v>
       </c>
       <c r="R242" t="n">
-        <v>7392096</v>
+        <v>7392159</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -25276,7 +25277,7 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>120434895</v>
+        <v>120434883</v>
       </c>
       <c r="B243" t="n">
         <v>91858</v>
@@ -25316,10 +25317,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>811053</v>
+        <v>811129</v>
       </c>
       <c r="R243" t="n">
-        <v>7392247</v>
+        <v>7392249</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25378,10 +25379,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>120434822</v>
+        <v>120434898</v>
       </c>
       <c r="B244" t="n">
-        <v>89650</v>
+        <v>91852</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -25394,21 +25395,21 @@
         </is>
       </c>
       <c r="E244" t="n">
-        <v>1962</v>
+        <v>4362</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -25418,10 +25419,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>811056</v>
+        <v>811095</v>
       </c>
       <c r="R244" t="n">
-        <v>7392242</v>
+        <v>7392048</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25480,7 +25481,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>120434869</v>
+        <v>120434894</v>
       </c>
       <c r="B245" t="n">
         <v>91858</v>
@@ -25520,10 +25521,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>811038</v>
+        <v>811099</v>
       </c>
       <c r="R245" t="n">
-        <v>7392074</v>
+        <v>7392252</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25582,10 +25583,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>120434842</v>
+        <v>120434873</v>
       </c>
       <c r="B246" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -25594,25 +25595,25 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -25622,10 +25623,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>811110</v>
+        <v>811170</v>
       </c>
       <c r="R246" t="n">
-        <v>7392006</v>
+        <v>7391994</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25684,7 +25685,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>120434867</v>
+        <v>120434880</v>
       </c>
       <c r="B247" t="n">
         <v>91858</v>
@@ -25724,10 +25725,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>810911</v>
+        <v>811219</v>
       </c>
       <c r="R247" t="n">
-        <v>7392181</v>
+        <v>7392151</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25786,10 +25787,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>120434855</v>
+        <v>120434819</v>
       </c>
       <c r="B248" t="n">
-        <v>78278</v>
+        <v>89650</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -25802,21 +25803,21 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -25826,10 +25827,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>811078</v>
+        <v>811135</v>
       </c>
       <c r="R248" t="n">
-        <v>7392236</v>
+        <v>7392091</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25888,7 +25889,7 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>120434871</v>
+        <v>120434890</v>
       </c>
       <c r="B249" t="n">
         <v>91858</v>
@@ -25928,10 +25929,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>811046</v>
+        <v>811035</v>
       </c>
       <c r="R249" t="n">
-        <v>7392008</v>
+        <v>7392102</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -25990,7 +25991,7 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>120434873</v>
+        <v>120434888</v>
       </c>
       <c r="B250" t="n">
         <v>91858</v>
@@ -26030,10 +26031,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>811170</v>
+        <v>811101</v>
       </c>
       <c r="R250" t="n">
-        <v>7391994</v>
+        <v>7392164</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -26092,10 +26093,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>120434818</v>
+        <v>120434851</v>
       </c>
       <c r="B251" t="n">
-        <v>89650</v>
+        <v>88170</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -26108,21 +26109,21 @@
         </is>
       </c>
       <c r="E251" t="n">
-        <v>1962</v>
+        <v>4962</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -26132,10 +26133,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>811170</v>
+        <v>811087</v>
       </c>
       <c r="R251" t="n">
-        <v>7391994</v>
+        <v>7392152</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -26194,10 +26195,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>120434894</v>
+        <v>120434842</v>
       </c>
       <c r="B252" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -26206,25 +26207,25 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -26234,10 +26235,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>811099</v>
+        <v>811110</v>
       </c>
       <c r="R252" t="n">
-        <v>7392252</v>
+        <v>7392006</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -26296,10 +26297,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>120434890</v>
+        <v>120434838</v>
       </c>
       <c r="B253" t="n">
-        <v>91858</v>
+        <v>91839</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -26308,25 +26309,25 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -26336,10 +26337,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>811035</v>
+        <v>811032</v>
       </c>
       <c r="R253" t="n">
-        <v>7392102</v>
+        <v>7392087</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26398,10 +26399,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>120434891</v>
+        <v>120434831</v>
       </c>
       <c r="B254" t="n">
-        <v>91858</v>
+        <v>91901</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -26410,25 +26411,25 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -26438,10 +26439,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>811023</v>
+        <v>811112</v>
       </c>
       <c r="R254" t="n">
-        <v>7392157</v>
+        <v>7392215</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26602,7 +26603,7 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>120434866</v>
+        <v>120434870</v>
       </c>
       <c r="B256" t="n">
         <v>91858</v>
@@ -26642,10 +26643,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>810910</v>
+        <v>811034</v>
       </c>
       <c r="R256" t="n">
-        <v>7392182</v>
+        <v>7392011</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26704,10 +26705,10 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>120434821</v>
+        <v>120434885</v>
       </c>
       <c r="B257" t="n">
-        <v>89650</v>
+        <v>91858</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
@@ -26716,25 +26717,25 @@
       </c>
       <c r="D257" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E257" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G257" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
@@ -26744,10 +26745,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>811073</v>
+        <v>811136</v>
       </c>
       <c r="R257" t="n">
-        <v>7392186</v>
+        <v>7392197</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -26806,10 +26807,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>120434819</v>
+        <v>120434841</v>
       </c>
       <c r="B258" t="n">
-        <v>89650</v>
+        <v>91862</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -26818,25 +26819,25 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>1962</v>
+        <v>4365</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -26846,10 +26847,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>811135</v>
+        <v>811019</v>
       </c>
       <c r="R258" t="n">
-        <v>7392091</v>
+        <v>7392096</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -26908,7 +26909,7 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>120434884</v>
+        <v>120434878</v>
       </c>
       <c r="B259" t="n">
         <v>91858</v>
@@ -26948,10 +26949,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>811098</v>
+        <v>811137</v>
       </c>
       <c r="R259" t="n">
-        <v>7392240</v>
+        <v>7392085</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -27010,10 +27011,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>120434886</v>
+        <v>120434840</v>
       </c>
       <c r="B260" t="n">
-        <v>91858</v>
+        <v>91862</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -27022,25 +27023,25 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -27050,10 +27051,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>811121</v>
+        <v>811025</v>
       </c>
       <c r="R260" t="n">
-        <v>7392171</v>
+        <v>7392081</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -27112,10 +27113,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>120434881</v>
+        <v>120434822</v>
       </c>
       <c r="B261" t="n">
-        <v>91858</v>
+        <v>89650</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -27124,25 +27125,25 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -27152,10 +27153,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>811165</v>
+        <v>811056</v>
       </c>
       <c r="R261" t="n">
-        <v>7392196</v>
+        <v>7392242</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -27214,7 +27215,7 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>120434820</v>
+        <v>120434818</v>
       </c>
       <c r="B262" t="n">
         <v>89650</v>
@@ -27254,10 +27255,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>811135</v>
+        <v>811170</v>
       </c>
       <c r="R262" t="n">
-        <v>7392090</v>
+        <v>7391994</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27316,10 +27317,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>120434850</v>
+        <v>120434854</v>
       </c>
       <c r="B263" t="n">
-        <v>88170</v>
+        <v>78278</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -27332,21 +27333,21 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>4962</v>
+        <v>6446</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -27356,10 +27357,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>811200</v>
+        <v>811151</v>
       </c>
       <c r="R263" t="n">
-        <v>7392176</v>
+        <v>7392024</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -27418,10 +27419,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>120434829</v>
+        <v>120434850</v>
       </c>
       <c r="B264" t="n">
-        <v>91904</v>
+        <v>88170</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -27430,25 +27431,25 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>232140</v>
+        <v>4962</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
@@ -27458,10 +27459,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>811018</v>
+        <v>811200</v>
       </c>
       <c r="R264" t="n">
-        <v>7392095</v>
+        <v>7392176</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27502,7 +27503,6 @@
       <c r="AE264" t="b">
         <v>0</v>
       </c>
-      <c r="AF264" t="inlineStr"/>
       <c r="AG264" t="b">
         <v>0</v>
       </c>
@@ -27521,7 +27521,7 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>120434874</v>
+        <v>120434866</v>
       </c>
       <c r="B265" t="n">
         <v>91858</v>
@@ -27561,10 +27561,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>811138</v>
+        <v>810910</v>
       </c>
       <c r="R265" t="n">
-        <v>7392034</v>
+        <v>7392182</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27623,7 +27623,7 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>120434878</v>
+        <v>120434882</v>
       </c>
       <c r="B266" t="n">
         <v>91858</v>
@@ -27663,10 +27663,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>811137</v>
+        <v>811166</v>
       </c>
       <c r="R266" t="n">
-        <v>7392085</v>
+        <v>7392206</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -27725,7 +27725,7 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>120434876</v>
+        <v>120434869</v>
       </c>
       <c r="B267" t="n">
         <v>91858</v>
@@ -27765,10 +27765,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>811136</v>
+        <v>811038</v>
       </c>
       <c r="R267" t="n">
-        <v>7392082</v>
+        <v>7392074</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -27827,7 +27827,7 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>120434883</v>
+        <v>120434879</v>
       </c>
       <c r="B268" t="n">
         <v>91858</v>
@@ -27867,10 +27867,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>811129</v>
+        <v>811161</v>
       </c>
       <c r="R268" t="n">
-        <v>7392249</v>
+        <v>7392143</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -27929,10 +27929,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>120434885</v>
+        <v>120434846</v>
       </c>
       <c r="B269" t="n">
-        <v>91858</v>
+        <v>96891</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -27945,21 +27945,21 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -27969,10 +27969,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>811136</v>
+        <v>811187</v>
       </c>
       <c r="R269" t="n">
-        <v>7392197</v>
+        <v>7392082</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -28031,10 +28031,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>120434839</v>
+        <v>120434867</v>
       </c>
       <c r="B270" t="n">
-        <v>91862</v>
+        <v>91858</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -28043,25 +28043,25 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
@@ -28071,10 +28071,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>811144</v>
+        <v>810911</v>
       </c>
       <c r="R270" t="n">
-        <v>7392037</v>
+        <v>7392181</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -28133,10 +28133,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>120434879</v>
+        <v>120434821</v>
       </c>
       <c r="B271" t="n">
-        <v>91858</v>
+        <v>89650</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -28145,25 +28145,25 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
@@ -28173,10 +28173,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>811161</v>
+        <v>811073</v>
       </c>
       <c r="R271" t="n">
-        <v>7392143</v>
+        <v>7392186</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -28235,10 +28235,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>120434823</v>
+        <v>120434830</v>
       </c>
       <c r="B272" t="n">
-        <v>89650</v>
+        <v>91902</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -28251,21 +28251,21 @@
         </is>
       </c>
       <c r="E272" t="n">
-        <v>1962</v>
+        <v>5449</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
@@ -28275,10 +28275,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>811063</v>
+        <v>811019</v>
       </c>
       <c r="R272" t="n">
-        <v>7392237</v>
+        <v>7392096</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -28337,10 +28337,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>120434841</v>
+        <v>120434837</v>
       </c>
       <c r="B273" t="n">
-        <v>91862</v>
+        <v>91902</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -28349,25 +28349,25 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
@@ -28377,10 +28377,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>811019</v>
+        <v>811044</v>
       </c>
       <c r="R273" t="n">
-        <v>7392096</v>
+        <v>7392261</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -28439,10 +28439,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>120434851</v>
+        <v>120434893</v>
       </c>
       <c r="B274" t="n">
-        <v>88170</v>
+        <v>91858</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -28451,25 +28451,25 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -28479,10 +28479,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>811087</v>
+        <v>811088</v>
       </c>
       <c r="R274" t="n">
-        <v>7392152</v>
+        <v>7392240</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -28541,10 +28541,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>120434880</v>
+        <v>120434845</v>
       </c>
       <c r="B275" t="n">
-        <v>91858</v>
+        <v>96891</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -28557,21 +28557,21 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -28581,10 +28581,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>811219</v>
+        <v>810859</v>
       </c>
       <c r="R275" t="n">
-        <v>7392151</v>
+        <v>7392159</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -28643,7 +28643,7 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>120434892</v>
+        <v>120434895</v>
       </c>
       <c r="B276" t="n">
         <v>91858</v>
@@ -28683,10 +28683,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>811071</v>
+        <v>811053</v>
       </c>
       <c r="R276" t="n">
-        <v>7392203</v>
+        <v>7392247</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -28847,10 +28847,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>120434833</v>
+        <v>120434820</v>
       </c>
       <c r="B278" t="n">
-        <v>91901</v>
+        <v>89650</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -28863,21 +28863,21 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>5448</v>
+        <v>1962</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
@@ -28887,10 +28887,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>810850</v>
+        <v>811135</v>
       </c>
       <c r="R278" t="n">
-        <v>7392159</v>
+        <v>7392090</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -28949,10 +28949,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>120434836</v>
+        <v>120434832</v>
       </c>
       <c r="B279" t="n">
-        <v>91902</v>
+        <v>91901</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -28965,21 +28965,21 @@
         </is>
       </c>
       <c r="E279" t="n">
-        <v>5449</v>
+        <v>5448</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
@@ -28989,10 +28989,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>811206</v>
+        <v>811072</v>
       </c>
       <c r="R279" t="n">
-        <v>7392173</v>
+        <v>7392186</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -29051,10 +29051,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>120434830</v>
+        <v>120434847</v>
       </c>
       <c r="B280" t="n">
-        <v>91902</v>
+        <v>96891</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -29063,25 +29063,25 @@
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E280" t="n">
-        <v>5449</v>
+        <v>221941</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
@@ -29091,10 +29091,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>811019</v>
+        <v>811044</v>
       </c>
       <c r="R280" t="n">
-        <v>7392096</v>
+        <v>7392264</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -29153,10 +29153,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>120434847</v>
+        <v>120434852</v>
       </c>
       <c r="B281" t="n">
-        <v>96891</v>
+        <v>57431</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -29169,21 +29169,21 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>221941</v>
+        <v>103031</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
@@ -29193,10 +29193,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>811044</v>
+        <v>810910</v>
       </c>
       <c r="R281" t="n">
-        <v>7392264</v>
+        <v>7392005</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -29255,10 +29255,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>120434875</v>
+        <v>120434899</v>
       </c>
       <c r="B282" t="n">
-        <v>91858</v>
+        <v>91862</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -29267,25 +29267,25 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
@@ -29295,10 +29295,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>811108</v>
+        <v>811192</v>
       </c>
       <c r="R282" t="n">
-        <v>7392073</v>
+        <v>7392146</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -29357,10 +29357,10 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>120434899</v>
+        <v>120434836</v>
       </c>
       <c r="B283" t="n">
-        <v>91862</v>
+        <v>91902</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -29369,25 +29369,25 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
@@ -29397,10 +29397,10 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>811192</v>
+        <v>811206</v>
       </c>
       <c r="R283" t="n">
-        <v>7392146</v>
+        <v>7392173</v>
       </c>
       <c r="S283" t="n">
         <v>10</v>
@@ -29459,7 +29459,7 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>120434865</v>
+        <v>120434884</v>
       </c>
       <c r="B284" t="n">
         <v>91858</v>
@@ -29499,10 +29499,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>810887</v>
+        <v>811098</v>
       </c>
       <c r="R284" t="n">
-        <v>7392183</v>
+        <v>7392240</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -29561,7 +29561,7 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>120434888</v>
+        <v>120434865</v>
       </c>
       <c r="B285" t="n">
         <v>91858</v>
@@ -29601,10 +29601,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>811101</v>
+        <v>810887</v>
       </c>
       <c r="R285" t="n">
-        <v>7392164</v>
+        <v>7392183</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -29663,10 +29663,10 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>120434845</v>
+        <v>120434872</v>
       </c>
       <c r="B286" t="n">
-        <v>96891</v>
+        <v>91858</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -29679,21 +29679,21 @@
         </is>
       </c>
       <c r="E286" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I286" t="inlineStr"/>
@@ -29703,10 +29703,10 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>810859</v>
+        <v>811073</v>
       </c>
       <c r="R286" t="n">
-        <v>7392159</v>
+        <v>7391995</v>
       </c>
       <c r="S286" t="n">
         <v>10</v>
@@ -29765,7 +29765,7 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>120434893</v>
+        <v>120434887</v>
       </c>
       <c r="B287" t="n">
         <v>91858</v>
@@ -29805,10 +29805,10 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>811088</v>
+        <v>811128</v>
       </c>
       <c r="R287" t="n">
-        <v>7392240</v>
+        <v>7392175</v>
       </c>
       <c r="S287" t="n">
         <v>10</v>
@@ -29867,7 +29867,7 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>120434840</v>
+        <v>120434839</v>
       </c>
       <c r="B288" t="n">
         <v>91862</v>
@@ -29907,10 +29907,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>811025</v>
+        <v>811144</v>
       </c>
       <c r="R288" t="n">
-        <v>7392081</v>
+        <v>7392037</v>
       </c>
       <c r="S288" t="n">
         <v>10</v>
@@ -29969,10 +29969,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>120434832</v>
+        <v>120434874</v>
       </c>
       <c r="B289" t="n">
-        <v>91901</v>
+        <v>91858</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -29981,25 +29981,25 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
@@ -30009,10 +30009,10 @@
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>811072</v>
+        <v>811138</v>
       </c>
       <c r="R289" t="n">
-        <v>7392186</v>
+        <v>7392034</v>
       </c>
       <c r="S289" t="n">
         <v>10</v>
@@ -30071,7 +30071,7 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>120434870</v>
+        <v>120434889</v>
       </c>
       <c r="B290" t="n">
         <v>91858</v>
@@ -30111,10 +30111,10 @@
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>811034</v>
+        <v>811045</v>
       </c>
       <c r="R290" t="n">
-        <v>7392011</v>
+        <v>7392096</v>
       </c>
       <c r="S290" t="n">
         <v>10</v>
@@ -30173,7 +30173,7 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>120434864</v>
+        <v>120434875</v>
       </c>
       <c r="B291" t="n">
         <v>91858</v>
@@ -30213,10 +30213,10 @@
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>810914</v>
+        <v>811108</v>
       </c>
       <c r="R291" t="n">
-        <v>7392166</v>
+        <v>7392073</v>
       </c>
       <c r="S291" t="n">
         <v>10</v>
@@ -30275,10 +30275,10 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>120434868</v>
+        <v>120434855</v>
       </c>
       <c r="B292" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -30287,25 +30287,25 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I292" t="inlineStr"/>
@@ -30315,10 +30315,10 @@
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>811010</v>
+        <v>811078</v>
       </c>
       <c r="R292" t="n">
-        <v>7392090</v>
+        <v>7392236</v>
       </c>
       <c r="S292" t="n">
         <v>10</v>
@@ -30479,10 +30479,10 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>120434817</v>
+        <v>120434823</v>
       </c>
       <c r="B294" t="n">
-        <v>79160</v>
+        <v>89650</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -30495,21 +30495,21 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I294" t="inlineStr"/>
@@ -30519,10 +30519,10 @@
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>811018</v>
+        <v>811063</v>
       </c>
       <c r="R294" t="n">
-        <v>7392105</v>
+        <v>7392237</v>
       </c>
       <c r="S294" t="n">
         <v>10</v>
@@ -30581,10 +30581,10 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>120434887</v>
+        <v>120434835</v>
       </c>
       <c r="B295" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -30593,25 +30593,25 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I295" t="inlineStr"/>
@@ -30621,10 +30621,10 @@
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>811128</v>
+        <v>811225</v>
       </c>
       <c r="R295" t="n">
-        <v>7392175</v>
+        <v>7392170</v>
       </c>
       <c r="S295" t="n">
         <v>10</v>
@@ -30683,10 +30683,10 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>120434835</v>
+        <v>120434891</v>
       </c>
       <c r="B296" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
@@ -30695,25 +30695,25 @@
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E296" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I296" t="inlineStr"/>
@@ -30723,10 +30723,10 @@
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>811225</v>
+        <v>811023</v>
       </c>
       <c r="R296" t="n">
-        <v>7392170</v>
+        <v>7392157</v>
       </c>
       <c r="S296" t="n">
         <v>10</v>
@@ -30785,10 +30785,10 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>120434837</v>
+        <v>120434868</v>
       </c>
       <c r="B297" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -30797,25 +30797,25 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I297" t="inlineStr"/>
@@ -30825,10 +30825,10 @@
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>811044</v>
+        <v>811010</v>
       </c>
       <c r="R297" t="n">
-        <v>7392261</v>
+        <v>7392090</v>
       </c>
       <c r="S297" t="n">
         <v>10</v>
@@ -30887,7 +30887,7 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>120434882</v>
+        <v>120434892</v>
       </c>
       <c r="B298" t="n">
         <v>91858</v>
@@ -30927,10 +30927,10 @@
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>811166</v>
+        <v>811071</v>
       </c>
       <c r="R298" t="n">
-        <v>7392206</v>
+        <v>7392203</v>
       </c>
       <c r="S298" t="n">
         <v>10</v>

--- a/artfynd/A 10151-2023 artfynd.xlsx
+++ b/artfynd/A 10151-2023 artfynd.xlsx
@@ -24255,10 +24255,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>120434886</v>
+        <v>120434823</v>
       </c>
       <c r="B233" t="n">
-        <v>91858</v>
+        <v>89650</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -24267,25 +24267,25 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -24295,10 +24295,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>811121</v>
+        <v>811063</v>
       </c>
       <c r="R233" t="n">
-        <v>7392171</v>
+        <v>7392237</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24357,10 +24357,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>120434829</v>
+        <v>120434892</v>
       </c>
       <c r="B234" t="n">
-        <v>91904</v>
+        <v>91858</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -24369,25 +24369,25 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -24397,10 +24397,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>811018</v>
+        <v>811071</v>
       </c>
       <c r="R234" t="n">
-        <v>7392095</v>
+        <v>7392203</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24441,7 +24441,6 @@
       <c r="AE234" t="b">
         <v>0</v>
       </c>
-      <c r="AF234" t="inlineStr"/>
       <c r="AG234" t="b">
         <v>0</v>
       </c>
@@ -24460,10 +24459,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>120434828</v>
+        <v>120434889</v>
       </c>
       <c r="B235" t="n">
-        <v>91904</v>
+        <v>91858</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -24472,25 +24471,25 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -24500,10 +24499,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>811160</v>
+        <v>811045</v>
       </c>
       <c r="R235" t="n">
-        <v>7392120</v>
+        <v>7392096</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -24544,7 +24543,6 @@
       <c r="AE235" t="b">
         <v>0</v>
       </c>
-      <c r="AF235" t="inlineStr"/>
       <c r="AG235" t="b">
         <v>0</v>
       </c>
@@ -24563,10 +24561,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>120434864</v>
+        <v>120434820</v>
       </c>
       <c r="B236" t="n">
-        <v>91858</v>
+        <v>89650</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -24575,25 +24573,25 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -24603,10 +24601,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>810914</v>
+        <v>811135</v>
       </c>
       <c r="R236" t="n">
-        <v>7392166</v>
+        <v>7392090</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24665,10 +24663,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>120434881</v>
+        <v>120434822</v>
       </c>
       <c r="B237" t="n">
-        <v>91858</v>
+        <v>89650</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -24677,25 +24675,25 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -24705,10 +24703,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>811165</v>
+        <v>811056</v>
       </c>
       <c r="R237" t="n">
-        <v>7392196</v>
+        <v>7392242</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24767,10 +24765,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>120434871</v>
+        <v>120434837</v>
       </c>
       <c r="B238" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -24779,25 +24777,25 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -24807,10 +24805,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>811046</v>
+        <v>811044</v>
       </c>
       <c r="R238" t="n">
-        <v>7392008</v>
+        <v>7392261</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -24869,10 +24867,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>120434817</v>
+        <v>120434836</v>
       </c>
       <c r="B239" t="n">
-        <v>79160</v>
+        <v>91902</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -24885,21 +24883,21 @@
         </is>
       </c>
       <c r="E239" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -24909,10 +24907,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>811018</v>
+        <v>811206</v>
       </c>
       <c r="R239" t="n">
-        <v>7392105</v>
+        <v>7392173</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24971,10 +24969,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>120434876</v>
+        <v>120434831</v>
       </c>
       <c r="B240" t="n">
-        <v>91858</v>
+        <v>91901</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -24983,25 +24981,25 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -25011,10 +25009,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>811136</v>
+        <v>811112</v>
       </c>
       <c r="R240" t="n">
-        <v>7392082</v>
+        <v>7392215</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25073,10 +25071,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>120434853</v>
+        <v>120434852</v>
       </c>
       <c r="B241" t="n">
-        <v>78278</v>
+        <v>57431</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -25085,25 +25083,25 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E241" t="n">
-        <v>6446</v>
+        <v>103031</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -25113,10 +25111,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>811148</v>
+        <v>810910</v>
       </c>
       <c r="R241" t="n">
-        <v>7391971</v>
+        <v>7392005</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25175,10 +25173,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>120434833</v>
+        <v>120434849</v>
       </c>
       <c r="B242" t="n">
-        <v>91901</v>
+        <v>88170</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -25191,21 +25189,21 @@
         </is>
       </c>
       <c r="E242" t="n">
-        <v>5448</v>
+        <v>4962</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -25215,10 +25213,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>810850</v>
+        <v>811223</v>
       </c>
       <c r="R242" t="n">
-        <v>7392159</v>
+        <v>7392167</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -25277,7 +25275,7 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>120434883</v>
+        <v>120434882</v>
       </c>
       <c r="B243" t="n">
         <v>91858</v>
@@ -25317,10 +25315,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>811129</v>
+        <v>811166</v>
       </c>
       <c r="R243" t="n">
-        <v>7392249</v>
+        <v>7392206</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25379,10 +25377,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>120434898</v>
+        <v>120434828</v>
       </c>
       <c r="B244" t="n">
-        <v>91852</v>
+        <v>91904</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -25391,25 +25389,25 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>4362</v>
+        <v>232140</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -25419,10 +25417,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>811095</v>
+        <v>811160</v>
       </c>
       <c r="R244" t="n">
-        <v>7392048</v>
+        <v>7392120</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25463,6 +25461,7 @@
       <c r="AE244" t="b">
         <v>0</v>
       </c>
+      <c r="AF244" t="inlineStr"/>
       <c r="AG244" t="b">
         <v>0</v>
       </c>
@@ -25481,7 +25480,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>120434894</v>
+        <v>120434869</v>
       </c>
       <c r="B245" t="n">
         <v>91858</v>
@@ -25521,10 +25520,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>811099</v>
+        <v>811038</v>
       </c>
       <c r="R245" t="n">
-        <v>7392252</v>
+        <v>7392074</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25583,7 +25582,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>120434873</v>
+        <v>120434875</v>
       </c>
       <c r="B246" t="n">
         <v>91858</v>
@@ -25623,10 +25622,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>811170</v>
+        <v>811108</v>
       </c>
       <c r="R246" t="n">
-        <v>7391994</v>
+        <v>7392073</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25685,10 +25684,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>120434880</v>
+        <v>120434833</v>
       </c>
       <c r="B247" t="n">
-        <v>91858</v>
+        <v>91901</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -25697,25 +25696,25 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -25725,10 +25724,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>811219</v>
+        <v>810850</v>
       </c>
       <c r="R247" t="n">
-        <v>7392151</v>
+        <v>7392159</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25787,10 +25786,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>120434819</v>
+        <v>120434835</v>
       </c>
       <c r="B248" t="n">
-        <v>89650</v>
+        <v>91902</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -25803,21 +25802,21 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>1962</v>
+        <v>5449</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -25827,10 +25826,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>811135</v>
+        <v>811225</v>
       </c>
       <c r="R248" t="n">
-        <v>7392091</v>
+        <v>7392170</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25889,10 +25888,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>120434890</v>
+        <v>120434845</v>
       </c>
       <c r="B249" t="n">
-        <v>91858</v>
+        <v>96891</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -25905,21 +25904,21 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -25929,10 +25928,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>811035</v>
+        <v>810859</v>
       </c>
       <c r="R249" t="n">
-        <v>7392102</v>
+        <v>7392159</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -25991,7 +25990,7 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>120434888</v>
+        <v>120434868</v>
       </c>
       <c r="B250" t="n">
         <v>91858</v>
@@ -26031,10 +26030,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>811101</v>
+        <v>811010</v>
       </c>
       <c r="R250" t="n">
-        <v>7392164</v>
+        <v>7392090</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -26093,10 +26092,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>120434851</v>
+        <v>120434878</v>
       </c>
       <c r="B251" t="n">
-        <v>88170</v>
+        <v>91858</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -26105,25 +26104,25 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -26133,10 +26132,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>811087</v>
+        <v>811137</v>
       </c>
       <c r="R251" t="n">
-        <v>7392152</v>
+        <v>7392085</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -26195,10 +26194,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>120434842</v>
+        <v>120434885</v>
       </c>
       <c r="B252" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -26207,25 +26206,25 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -26235,10 +26234,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>811110</v>
+        <v>811136</v>
       </c>
       <c r="R252" t="n">
-        <v>7392006</v>
+        <v>7392197</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -26297,10 +26296,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>120434838</v>
+        <v>120434876</v>
       </c>
       <c r="B253" t="n">
-        <v>91839</v>
+        <v>91858</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -26309,25 +26308,25 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -26337,10 +26336,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>811032</v>
+        <v>811136</v>
       </c>
       <c r="R253" t="n">
-        <v>7392087</v>
+        <v>7392082</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26399,10 +26398,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>120434831</v>
+        <v>120434850</v>
       </c>
       <c r="B254" t="n">
-        <v>91901</v>
+        <v>88170</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -26415,21 +26414,21 @@
         </is>
       </c>
       <c r="E254" t="n">
-        <v>5448</v>
+        <v>4962</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -26439,10 +26438,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>811112</v>
+        <v>811200</v>
       </c>
       <c r="R254" t="n">
-        <v>7392215</v>
+        <v>7392176</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26501,7 +26500,7 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>120434877</v>
+        <v>120434888</v>
       </c>
       <c r="B255" t="n">
         <v>91858</v>
@@ -26541,10 +26540,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>811135</v>
+        <v>811101</v>
       </c>
       <c r="R255" t="n">
-        <v>7392085</v>
+        <v>7392164</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26603,10 +26602,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>120434870</v>
+        <v>120434853</v>
       </c>
       <c r="B256" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -26615,25 +26614,25 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -26643,10 +26642,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>811034</v>
+        <v>811148</v>
       </c>
       <c r="R256" t="n">
-        <v>7392011</v>
+        <v>7391971</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26705,7 +26704,7 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>120434885</v>
+        <v>120434871</v>
       </c>
       <c r="B257" t="n">
         <v>91858</v>
@@ -26745,10 +26744,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>811136</v>
+        <v>811046</v>
       </c>
       <c r="R257" t="n">
-        <v>7392197</v>
+        <v>7392008</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -26807,10 +26806,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>120434841</v>
+        <v>120434883</v>
       </c>
       <c r="B258" t="n">
-        <v>91862</v>
+        <v>91858</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -26819,25 +26818,25 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -26847,10 +26846,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>811019</v>
+        <v>811129</v>
       </c>
       <c r="R258" t="n">
-        <v>7392096</v>
+        <v>7392249</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -26909,10 +26908,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>120434878</v>
+        <v>120434846</v>
       </c>
       <c r="B259" t="n">
-        <v>91858</v>
+        <v>96891</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -26925,21 +26924,21 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -26949,10 +26948,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>811137</v>
+        <v>811187</v>
       </c>
       <c r="R259" t="n">
-        <v>7392085</v>
+        <v>7392082</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -27011,10 +27010,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>120434840</v>
+        <v>120434819</v>
       </c>
       <c r="B260" t="n">
-        <v>91862</v>
+        <v>89650</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -27023,25 +27022,25 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>4365</v>
+        <v>1962</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -27051,10 +27050,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>811025</v>
+        <v>811135</v>
       </c>
       <c r="R260" t="n">
-        <v>7392081</v>
+        <v>7392091</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -27113,10 +27112,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>120434822</v>
+        <v>120434864</v>
       </c>
       <c r="B261" t="n">
-        <v>89650</v>
+        <v>91858</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -27125,25 +27124,25 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -27153,10 +27152,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>811056</v>
+        <v>810914</v>
       </c>
       <c r="R261" t="n">
-        <v>7392242</v>
+        <v>7392166</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -27215,10 +27214,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>120434818</v>
+        <v>120434872</v>
       </c>
       <c r="B262" t="n">
-        <v>89650</v>
+        <v>91858</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -27227,25 +27226,25 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -27255,10 +27254,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>811170</v>
+        <v>811073</v>
       </c>
       <c r="R262" t="n">
-        <v>7391994</v>
+        <v>7391995</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27317,10 +27316,10 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>120434854</v>
+        <v>120434870</v>
       </c>
       <c r="B263" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C263" t="inlineStr">
         <is>
@@ -27329,25 +27328,25 @@
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E263" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F263" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G263" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I263" t="inlineStr"/>
@@ -27357,10 +27356,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>811151</v>
+        <v>811034</v>
       </c>
       <c r="R263" t="n">
-        <v>7392024</v>
+        <v>7392011</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -27419,10 +27418,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>120434850</v>
+        <v>120434839</v>
       </c>
       <c r="B264" t="n">
-        <v>88170</v>
+        <v>91862</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -27431,25 +27430,25 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>4962</v>
+        <v>4365</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
@@ -27459,10 +27458,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>811200</v>
+        <v>811144</v>
       </c>
       <c r="R264" t="n">
-        <v>7392176</v>
+        <v>7392037</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27521,7 +27520,7 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>120434866</v>
+        <v>120434884</v>
       </c>
       <c r="B265" t="n">
         <v>91858</v>
@@ -27561,10 +27560,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>810910</v>
+        <v>811098</v>
       </c>
       <c r="R265" t="n">
-        <v>7392182</v>
+        <v>7392240</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27623,10 +27622,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>120434882</v>
+        <v>120434847</v>
       </c>
       <c r="B266" t="n">
-        <v>91858</v>
+        <v>96891</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -27639,21 +27638,21 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
@@ -27663,10 +27662,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>811166</v>
+        <v>811044</v>
       </c>
       <c r="R266" t="n">
-        <v>7392206</v>
+        <v>7392264</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -27725,10 +27724,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>120434869</v>
+        <v>120434821</v>
       </c>
       <c r="B267" t="n">
-        <v>91858</v>
+        <v>89650</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -27737,25 +27736,25 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -27765,10 +27764,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>811038</v>
+        <v>811073</v>
       </c>
       <c r="R267" t="n">
-        <v>7392074</v>
+        <v>7392186</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -27827,10 +27826,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>120434879</v>
+        <v>120434851</v>
       </c>
       <c r="B268" t="n">
-        <v>91858</v>
+        <v>88170</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -27839,25 +27838,25 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -27867,10 +27866,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>811161</v>
+        <v>811087</v>
       </c>
       <c r="R268" t="n">
-        <v>7392143</v>
+        <v>7392152</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -27929,10 +27928,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>120434846</v>
+        <v>120434841</v>
       </c>
       <c r="B269" t="n">
-        <v>96891</v>
+        <v>91862</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -27941,25 +27940,25 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>221941</v>
+        <v>4365</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -27969,10 +27968,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>811187</v>
+        <v>811019</v>
       </c>
       <c r="R269" t="n">
-        <v>7392082</v>
+        <v>7392096</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -28031,7 +28030,7 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>120434867</v>
+        <v>120434891</v>
       </c>
       <c r="B270" t="n">
         <v>91858</v>
@@ -28071,10 +28070,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>810911</v>
+        <v>811023</v>
       </c>
       <c r="R270" t="n">
-        <v>7392181</v>
+        <v>7392157</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -28133,10 +28132,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>120434821</v>
+        <v>120434830</v>
       </c>
       <c r="B271" t="n">
-        <v>89650</v>
+        <v>91902</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -28149,21 +28148,21 @@
         </is>
       </c>
       <c r="E271" t="n">
-        <v>1962</v>
+        <v>5449</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
@@ -28173,10 +28172,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>811073</v>
+        <v>811019</v>
       </c>
       <c r="R271" t="n">
-        <v>7392186</v>
+        <v>7392096</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -28235,10 +28234,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>120434830</v>
+        <v>120434866</v>
       </c>
       <c r="B272" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -28247,25 +28246,25 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
@@ -28275,10 +28274,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>811019</v>
+        <v>810910</v>
       </c>
       <c r="R272" t="n">
-        <v>7392096</v>
+        <v>7392182</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -28337,10 +28336,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>120434837</v>
+        <v>120434827</v>
       </c>
       <c r="B273" t="n">
-        <v>91902</v>
+        <v>91481</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -28353,21 +28352,21 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>5449</v>
+        <v>4745</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
@@ -28377,10 +28376,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>811044</v>
+        <v>810903</v>
       </c>
       <c r="R273" t="n">
-        <v>7392261</v>
+        <v>7392182</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -28439,10 +28438,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>120434893</v>
+        <v>120434842</v>
       </c>
       <c r="B274" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -28451,25 +28450,25 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -28479,10 +28478,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>811088</v>
+        <v>811110</v>
       </c>
       <c r="R274" t="n">
-        <v>7392240</v>
+        <v>7392006</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -28541,10 +28540,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>120434845</v>
+        <v>120434865</v>
       </c>
       <c r="B275" t="n">
-        <v>96891</v>
+        <v>91858</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -28557,21 +28556,21 @@
         </is>
       </c>
       <c r="E275" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -28581,10 +28580,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>810859</v>
+        <v>810887</v>
       </c>
       <c r="R275" t="n">
-        <v>7392159</v>
+        <v>7392183</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -28643,7 +28642,7 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>120434895</v>
+        <v>120434893</v>
       </c>
       <c r="B276" t="n">
         <v>91858</v>
@@ -28683,10 +28682,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>811053</v>
+        <v>811088</v>
       </c>
       <c r="R276" t="n">
-        <v>7392247</v>
+        <v>7392240</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -28745,10 +28744,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>120434827</v>
+        <v>120434879</v>
       </c>
       <c r="B277" t="n">
-        <v>91481</v>
+        <v>91858</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -28757,25 +28756,25 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
@@ -28785,10 +28784,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>810903</v>
+        <v>811161</v>
       </c>
       <c r="R277" t="n">
-        <v>7392182</v>
+        <v>7392143</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -28847,10 +28846,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>120434820</v>
+        <v>120434855</v>
       </c>
       <c r="B278" t="n">
-        <v>89650</v>
+        <v>78278</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -28863,21 +28862,21 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
@@ -28887,10 +28886,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>811135</v>
+        <v>811078</v>
       </c>
       <c r="R278" t="n">
-        <v>7392090</v>
+        <v>7392236</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -28949,10 +28948,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>120434832</v>
+        <v>120434829</v>
       </c>
       <c r="B279" t="n">
-        <v>91901</v>
+        <v>91904</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -28961,25 +28960,25 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>5448</v>
+        <v>232140</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
@@ -28989,10 +28988,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>811072</v>
+        <v>811018</v>
       </c>
       <c r="R279" t="n">
-        <v>7392186</v>
+        <v>7392095</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -29033,6 +29032,7 @@
       <c r="AE279" t="b">
         <v>0</v>
       </c>
+      <c r="AF279" t="inlineStr"/>
       <c r="AG279" t="b">
         <v>0</v>
       </c>
@@ -29051,10 +29051,10 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>120434847</v>
+        <v>120434887</v>
       </c>
       <c r="B280" t="n">
-        <v>96891</v>
+        <v>91858</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
@@ -29067,21 +29067,21 @@
         </is>
       </c>
       <c r="E280" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G280" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I280" t="inlineStr"/>
@@ -29091,10 +29091,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>811044</v>
+        <v>811128</v>
       </c>
       <c r="R280" t="n">
-        <v>7392264</v>
+        <v>7392175</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -29153,10 +29153,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>120434852</v>
+        <v>120434895</v>
       </c>
       <c r="B281" t="n">
-        <v>57431</v>
+        <v>91858</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -29169,21 +29169,21 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
@@ -29193,10 +29193,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>810910</v>
+        <v>811053</v>
       </c>
       <c r="R281" t="n">
-        <v>7392005</v>
+        <v>7392247</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -29255,10 +29255,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>120434899</v>
+        <v>120434894</v>
       </c>
       <c r="B282" t="n">
-        <v>91862</v>
+        <v>91858</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -29267,25 +29267,25 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
@@ -29295,10 +29295,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>811192</v>
+        <v>811099</v>
       </c>
       <c r="R282" t="n">
-        <v>7392146</v>
+        <v>7392252</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -29357,10 +29357,10 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>120434836</v>
+        <v>120434867</v>
       </c>
       <c r="B283" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -29369,25 +29369,25 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
@@ -29397,10 +29397,10 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>811206</v>
+        <v>810911</v>
       </c>
       <c r="R283" t="n">
-        <v>7392173</v>
+        <v>7392181</v>
       </c>
       <c r="S283" t="n">
         <v>10</v>
@@ -29459,10 +29459,10 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>120434884</v>
+        <v>120434840</v>
       </c>
       <c r="B284" t="n">
-        <v>91858</v>
+        <v>91862</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -29471,25 +29471,25 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -29499,10 +29499,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>811098</v>
+        <v>811025</v>
       </c>
       <c r="R284" t="n">
-        <v>7392240</v>
+        <v>7392081</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -29561,7 +29561,7 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>120434865</v>
+        <v>120434890</v>
       </c>
       <c r="B285" t="n">
         <v>91858</v>
@@ -29601,10 +29601,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>810887</v>
+        <v>811035</v>
       </c>
       <c r="R285" t="n">
-        <v>7392183</v>
+        <v>7392102</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -29663,7 +29663,7 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>120434872</v>
+        <v>120434881</v>
       </c>
       <c r="B286" t="n">
         <v>91858</v>
@@ -29703,10 +29703,10 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>811073</v>
+        <v>811165</v>
       </c>
       <c r="R286" t="n">
-        <v>7391995</v>
+        <v>7392196</v>
       </c>
       <c r="S286" t="n">
         <v>10</v>
@@ -29765,7 +29765,7 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>120434887</v>
+        <v>120434877</v>
       </c>
       <c r="B287" t="n">
         <v>91858</v>
@@ -29805,10 +29805,10 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>811128</v>
+        <v>811135</v>
       </c>
       <c r="R287" t="n">
-        <v>7392175</v>
+        <v>7392085</v>
       </c>
       <c r="S287" t="n">
         <v>10</v>
@@ -29867,10 +29867,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>120434839</v>
+        <v>120434874</v>
       </c>
       <c r="B288" t="n">
-        <v>91862</v>
+        <v>91858</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -29879,25 +29879,25 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I288" t="inlineStr"/>
@@ -29907,10 +29907,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>811144</v>
+        <v>811138</v>
       </c>
       <c r="R288" t="n">
-        <v>7392037</v>
+        <v>7392034</v>
       </c>
       <c r="S288" t="n">
         <v>10</v>
@@ -29969,7 +29969,7 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>120434874</v>
+        <v>120434886</v>
       </c>
       <c r="B289" t="n">
         <v>91858</v>
@@ -30009,10 +30009,10 @@
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>811138</v>
+        <v>811121</v>
       </c>
       <c r="R289" t="n">
-        <v>7392034</v>
+        <v>7392171</v>
       </c>
       <c r="S289" t="n">
         <v>10</v>
@@ -30071,10 +30071,10 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>120434889</v>
+        <v>120434898</v>
       </c>
       <c r="B290" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -30083,25 +30083,25 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I290" t="inlineStr"/>
@@ -30111,10 +30111,10 @@
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>811045</v>
+        <v>811095</v>
       </c>
       <c r="R290" t="n">
-        <v>7392096</v>
+        <v>7392048</v>
       </c>
       <c r="S290" t="n">
         <v>10</v>
@@ -30173,7 +30173,7 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>120434875</v>
+        <v>120434880</v>
       </c>
       <c r="B291" t="n">
         <v>91858</v>
@@ -30213,10 +30213,10 @@
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>811108</v>
+        <v>811219</v>
       </c>
       <c r="R291" t="n">
-        <v>7392073</v>
+        <v>7392151</v>
       </c>
       <c r="S291" t="n">
         <v>10</v>
@@ -30275,10 +30275,10 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>120434855</v>
+        <v>120434818</v>
       </c>
       <c r="B292" t="n">
-        <v>78278</v>
+        <v>89650</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -30291,21 +30291,21 @@
         </is>
       </c>
       <c r="E292" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I292" t="inlineStr"/>
@@ -30315,10 +30315,10 @@
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>811078</v>
+        <v>811170</v>
       </c>
       <c r="R292" t="n">
-        <v>7392236</v>
+        <v>7391994</v>
       </c>
       <c r="S292" t="n">
         <v>10</v>
@@ -30377,10 +30377,10 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>120434849</v>
+        <v>120434899</v>
       </c>
       <c r="B293" t="n">
-        <v>88170</v>
+        <v>91862</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -30389,25 +30389,25 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>4962</v>
+        <v>4365</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I293" t="inlineStr"/>
@@ -30417,10 +30417,10 @@
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>811223</v>
+        <v>811192</v>
       </c>
       <c r="R293" t="n">
-        <v>7392167</v>
+        <v>7392146</v>
       </c>
       <c r="S293" t="n">
         <v>10</v>
@@ -30479,10 +30479,10 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>120434823</v>
+        <v>120434817</v>
       </c>
       <c r="B294" t="n">
-        <v>89650</v>
+        <v>79160</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -30495,21 +30495,21 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I294" t="inlineStr"/>
@@ -30519,10 +30519,10 @@
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>811063</v>
+        <v>811018</v>
       </c>
       <c r="R294" t="n">
-        <v>7392237</v>
+        <v>7392105</v>
       </c>
       <c r="S294" t="n">
         <v>10</v>
@@ -30581,10 +30581,10 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>120434835</v>
+        <v>120434838</v>
       </c>
       <c r="B295" t="n">
-        <v>91902</v>
+        <v>91839</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -30593,25 +30593,25 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>5449</v>
+        <v>6055</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I295" t="inlineStr"/>
@@ -30621,10 +30621,10 @@
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>811225</v>
+        <v>811032</v>
       </c>
       <c r="R295" t="n">
-        <v>7392170</v>
+        <v>7392087</v>
       </c>
       <c r="S295" t="n">
         <v>10</v>
@@ -30683,7 +30683,7 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>120434891</v>
+        <v>120434873</v>
       </c>
       <c r="B296" t="n">
         <v>91858</v>
@@ -30723,10 +30723,10 @@
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>811023</v>
+        <v>811170</v>
       </c>
       <c r="R296" t="n">
-        <v>7392157</v>
+        <v>7391994</v>
       </c>
       <c r="S296" t="n">
         <v>10</v>
@@ -30785,10 +30785,10 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>120434868</v>
+        <v>120434854</v>
       </c>
       <c r="B297" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -30797,25 +30797,25 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I297" t="inlineStr"/>
@@ -30825,10 +30825,10 @@
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>811010</v>
+        <v>811151</v>
       </c>
       <c r="R297" t="n">
-        <v>7392090</v>
+        <v>7392024</v>
       </c>
       <c r="S297" t="n">
         <v>10</v>
@@ -30887,10 +30887,10 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>120434892</v>
+        <v>120434832</v>
       </c>
       <c r="B298" t="n">
-        <v>91858</v>
+        <v>91901</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -30899,25 +30899,25 @@
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E298" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I298" t="inlineStr"/>
@@ -30927,10 +30927,10 @@
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>811071</v>
+        <v>811072</v>
       </c>
       <c r="R298" t="n">
-        <v>7392203</v>
+        <v>7392186</v>
       </c>
       <c r="S298" t="n">
         <v>10</v>

--- a/artfynd/A 10151-2023 artfynd.xlsx
+++ b/artfynd/A 10151-2023 artfynd.xlsx
@@ -25480,10 +25480,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>120434869</v>
+        <v>120434845</v>
       </c>
       <c r="B245" t="n">
-        <v>91858</v>
+        <v>96891</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -25496,21 +25496,21 @@
         </is>
       </c>
       <c r="E245" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -25520,10 +25520,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>811038</v>
+        <v>810859</v>
       </c>
       <c r="R245" t="n">
-        <v>7392074</v>
+        <v>7392159</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25684,10 +25684,10 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>120434833</v>
+        <v>120434869</v>
       </c>
       <c r="B247" t="n">
-        <v>91901</v>
+        <v>91858</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
@@ -25696,25 +25696,25 @@
       </c>
       <c r="D247" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E247" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G247" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I247" t="inlineStr"/>
@@ -25724,10 +25724,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>810850</v>
+        <v>811038</v>
       </c>
       <c r="R247" t="n">
-        <v>7392159</v>
+        <v>7392074</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25786,10 +25786,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>120434835</v>
+        <v>120434833</v>
       </c>
       <c r="B248" t="n">
-        <v>91902</v>
+        <v>91901</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -25802,21 +25802,21 @@
         </is>
       </c>
       <c r="E248" t="n">
-        <v>5449</v>
+        <v>5448</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -25826,10 +25826,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>811225</v>
+        <v>810850</v>
       </c>
       <c r="R248" t="n">
-        <v>7392170</v>
+        <v>7392159</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25888,10 +25888,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>120434845</v>
+        <v>120434835</v>
       </c>
       <c r="B249" t="n">
-        <v>96891</v>
+        <v>91902</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -25900,25 +25900,25 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>221941</v>
+        <v>5449</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -25928,10 +25928,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>810859</v>
+        <v>811225</v>
       </c>
       <c r="R249" t="n">
-        <v>7392159</v>
+        <v>7392170</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -27010,10 +27010,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>120434819</v>
+        <v>120434872</v>
       </c>
       <c r="B260" t="n">
-        <v>89650</v>
+        <v>91858</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -27022,25 +27022,25 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -27050,10 +27050,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>811135</v>
+        <v>811073</v>
       </c>
       <c r="R260" t="n">
-        <v>7392091</v>
+        <v>7391995</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -27112,10 +27112,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>120434864</v>
+        <v>120434819</v>
       </c>
       <c r="B261" t="n">
-        <v>91858</v>
+        <v>89650</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -27124,25 +27124,25 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -27152,10 +27152,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>810914</v>
+        <v>811135</v>
       </c>
       <c r="R261" t="n">
-        <v>7392166</v>
+        <v>7392091</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -27214,7 +27214,7 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>120434872</v>
+        <v>120434864</v>
       </c>
       <c r="B262" t="n">
         <v>91858</v>
@@ -27254,10 +27254,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>811073</v>
+        <v>810914</v>
       </c>
       <c r="R262" t="n">
-        <v>7391995</v>
+        <v>7392166</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27520,10 +27520,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>120434884</v>
+        <v>120434847</v>
       </c>
       <c r="B265" t="n">
-        <v>91858</v>
+        <v>96891</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -27536,21 +27536,21 @@
         </is>
       </c>
       <c r="E265" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
@@ -27560,10 +27560,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>811098</v>
+        <v>811044</v>
       </c>
       <c r="R265" t="n">
-        <v>7392240</v>
+        <v>7392264</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27622,10 +27622,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>120434847</v>
+        <v>120434884</v>
       </c>
       <c r="B266" t="n">
-        <v>96891</v>
+        <v>91858</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -27638,21 +27638,21 @@
         </is>
       </c>
       <c r="E266" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
@@ -27662,10 +27662,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>811044</v>
+        <v>811098</v>
       </c>
       <c r="R266" t="n">
-        <v>7392264</v>
+        <v>7392240</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -27724,10 +27724,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>120434821</v>
+        <v>120434851</v>
       </c>
       <c r="B267" t="n">
-        <v>89650</v>
+        <v>88170</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -27740,21 +27740,21 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>1962</v>
+        <v>4962</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -27764,10 +27764,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>811073</v>
+        <v>811087</v>
       </c>
       <c r="R267" t="n">
-        <v>7392186</v>
+        <v>7392152</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -27826,10 +27826,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>120434851</v>
+        <v>120434841</v>
       </c>
       <c r="B268" t="n">
-        <v>88170</v>
+        <v>91862</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -27838,25 +27838,25 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>4962</v>
+        <v>4365</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -27866,10 +27866,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>811087</v>
+        <v>811019</v>
       </c>
       <c r="R268" t="n">
-        <v>7392152</v>
+        <v>7392096</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -27928,10 +27928,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>120434841</v>
+        <v>120434830</v>
       </c>
       <c r="B269" t="n">
-        <v>91862</v>
+        <v>91902</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -27940,25 +27940,25 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -28030,10 +28030,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>120434891</v>
+        <v>120434821</v>
       </c>
       <c r="B270" t="n">
-        <v>91858</v>
+        <v>89650</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -28042,25 +28042,25 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
@@ -28070,10 +28070,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>811023</v>
+        <v>811073</v>
       </c>
       <c r="R270" t="n">
-        <v>7392157</v>
+        <v>7392186</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -28132,10 +28132,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>120434830</v>
+        <v>120434891</v>
       </c>
       <c r="B271" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -28144,25 +28144,25 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
@@ -28172,10 +28172,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>811019</v>
+        <v>811023</v>
       </c>
       <c r="R271" t="n">
-        <v>7392096</v>
+        <v>7392157</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -28438,10 +28438,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>120434842</v>
+        <v>120434865</v>
       </c>
       <c r="B274" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -28450,25 +28450,25 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -28478,10 +28478,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>811110</v>
+        <v>810887</v>
       </c>
       <c r="R274" t="n">
-        <v>7392006</v>
+        <v>7392183</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -28540,7 +28540,7 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>120434865</v>
+        <v>120434893</v>
       </c>
       <c r="B275" t="n">
         <v>91858</v>
@@ -28580,10 +28580,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>810887</v>
+        <v>811088</v>
       </c>
       <c r="R275" t="n">
-        <v>7392183</v>
+        <v>7392240</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -28642,10 +28642,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>120434893</v>
+        <v>120434842</v>
       </c>
       <c r="B276" t="n">
-        <v>91858</v>
+        <v>91874</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -28654,25 +28654,25 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>4364</v>
+        <v>2059</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -28682,10 +28682,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>811088</v>
+        <v>811110</v>
       </c>
       <c r="R276" t="n">
-        <v>7392240</v>
+        <v>7392006</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -28948,10 +28948,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>120434829</v>
+        <v>120434887</v>
       </c>
       <c r="B279" t="n">
-        <v>91904</v>
+        <v>91858</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -28960,25 +28960,25 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
@@ -28988,10 +28988,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>811018</v>
+        <v>811128</v>
       </c>
       <c r="R279" t="n">
-        <v>7392095</v>
+        <v>7392175</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -29032,7 +29032,6 @@
       <c r="AE279" t="b">
         <v>0</v>
       </c>
-      <c r="AF279" t="inlineStr"/>
       <c r="AG279" t="b">
         <v>0</v>
       </c>
@@ -29051,7 +29050,7 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>120434887</v>
+        <v>120434895</v>
       </c>
       <c r="B280" t="n">
         <v>91858</v>
@@ -29091,10 +29090,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>811128</v>
+        <v>811053</v>
       </c>
       <c r="R280" t="n">
-        <v>7392175</v>
+        <v>7392247</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -29153,7 +29152,7 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>120434895</v>
+        <v>120434894</v>
       </c>
       <c r="B281" t="n">
         <v>91858</v>
@@ -29193,10 +29192,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>811053</v>
+        <v>811099</v>
       </c>
       <c r="R281" t="n">
-        <v>7392247</v>
+        <v>7392252</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -29255,10 +29254,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>120434894</v>
+        <v>120434829</v>
       </c>
       <c r="B282" t="n">
-        <v>91858</v>
+        <v>91904</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -29267,25 +29266,25 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>4364</v>
+        <v>232140</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
@@ -29295,10 +29294,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>811099</v>
+        <v>811018</v>
       </c>
       <c r="R282" t="n">
-        <v>7392252</v>
+        <v>7392095</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -29339,6 +29338,7 @@
       <c r="AE282" t="b">
         <v>0</v>
       </c>
+      <c r="AF282" t="inlineStr"/>
       <c r="AG282" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 10151-2023 artfynd.xlsx
+++ b/artfynd/A 10151-2023 artfynd.xlsx
@@ -24255,10 +24255,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>120434823</v>
+        <v>120434832</v>
       </c>
       <c r="B233" t="n">
-        <v>89650</v>
+        <v>91901</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -24271,21 +24271,21 @@
         </is>
       </c>
       <c r="E233" t="n">
-        <v>1962</v>
+        <v>5448</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -24295,10 +24295,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>811063</v>
+        <v>811072</v>
       </c>
       <c r="R233" t="n">
-        <v>7392237</v>
+        <v>7392186</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24357,10 +24357,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>120434892</v>
+        <v>120434838</v>
       </c>
       <c r="B234" t="n">
-        <v>91858</v>
+        <v>91839</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -24369,25 +24369,25 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>4364</v>
+        <v>6055</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -24397,10 +24397,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>811071</v>
+        <v>811032</v>
       </c>
       <c r="R234" t="n">
-        <v>7392203</v>
+        <v>7392087</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24459,7 +24459,7 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>120434889</v>
+        <v>120434864</v>
       </c>
       <c r="B235" t="n">
         <v>91858</v>
@@ -24499,10 +24499,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>811045</v>
+        <v>810914</v>
       </c>
       <c r="R235" t="n">
-        <v>7392096</v>
+        <v>7392166</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -24561,10 +24561,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>120434820</v>
+        <v>120434899</v>
       </c>
       <c r="B236" t="n">
-        <v>89650</v>
+        <v>91862</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -24573,25 +24573,25 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>1962</v>
+        <v>4365</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -24601,10 +24601,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>811135</v>
+        <v>811192</v>
       </c>
       <c r="R236" t="n">
-        <v>7392090</v>
+        <v>7392146</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24663,10 +24663,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>120434822</v>
+        <v>120434895</v>
       </c>
       <c r="B237" t="n">
-        <v>89650</v>
+        <v>91858</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -24675,25 +24675,25 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -24703,10 +24703,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>811056</v>
+        <v>811053</v>
       </c>
       <c r="R237" t="n">
-        <v>7392242</v>
+        <v>7392247</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24765,10 +24765,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>120434837</v>
+        <v>120434879</v>
       </c>
       <c r="B238" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -24777,25 +24777,25 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -24805,10 +24805,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>811044</v>
+        <v>811161</v>
       </c>
       <c r="R238" t="n">
-        <v>7392261</v>
+        <v>7392143</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -24867,10 +24867,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>120434836</v>
+        <v>120434894</v>
       </c>
       <c r="B239" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -24879,25 +24879,25 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -24907,10 +24907,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>811206</v>
+        <v>811099</v>
       </c>
       <c r="R239" t="n">
-        <v>7392173</v>
+        <v>7392252</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24969,10 +24969,10 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>120434831</v>
+        <v>120434873</v>
       </c>
       <c r="B240" t="n">
-        <v>91901</v>
+        <v>91858</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
@@ -24981,25 +24981,25 @@
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E240" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G240" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
@@ -25009,10 +25009,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>811112</v>
+        <v>811170</v>
       </c>
       <c r="R240" t="n">
-        <v>7392215</v>
+        <v>7391994</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25071,10 +25071,10 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>120434852</v>
+        <v>120434877</v>
       </c>
       <c r="B241" t="n">
-        <v>57431</v>
+        <v>91858</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
@@ -25087,21 +25087,21 @@
         </is>
       </c>
       <c r="E241" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G241" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
@@ -25111,10 +25111,10 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>810910</v>
+        <v>811135</v>
       </c>
       <c r="R241" t="n">
-        <v>7392005</v>
+        <v>7392085</v>
       </c>
       <c r="S241" t="n">
         <v>10</v>
@@ -25173,10 +25173,10 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>120434849</v>
+        <v>120434889</v>
       </c>
       <c r="B242" t="n">
-        <v>88170</v>
+        <v>91858</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
@@ -25185,25 +25185,25 @@
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E242" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G242" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
@@ -25213,10 +25213,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>811223</v>
+        <v>811045</v>
       </c>
       <c r="R242" t="n">
-        <v>7392167</v>
+        <v>7392096</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -25275,7 +25275,7 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>120434882</v>
+        <v>120434881</v>
       </c>
       <c r="B243" t="n">
         <v>91858</v>
@@ -25315,10 +25315,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>811166</v>
+        <v>811165</v>
       </c>
       <c r="R243" t="n">
-        <v>7392206</v>
+        <v>7392196</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25480,10 +25480,10 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>120434845</v>
+        <v>120434822</v>
       </c>
       <c r="B245" t="n">
-        <v>96891</v>
+        <v>89650</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
@@ -25492,25 +25492,25 @@
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E245" t="n">
-        <v>221941</v>
+        <v>1962</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G245" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
@@ -25520,10 +25520,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>810859</v>
+        <v>811056</v>
       </c>
       <c r="R245" t="n">
-        <v>7392159</v>
+        <v>7392242</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25582,10 +25582,10 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>120434875</v>
+        <v>120434818</v>
       </c>
       <c r="B246" t="n">
-        <v>91858</v>
+        <v>89650</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
@@ -25594,25 +25594,25 @@
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E246" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G246" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
@@ -25622,10 +25622,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>811108</v>
+        <v>811170</v>
       </c>
       <c r="R246" t="n">
-        <v>7392073</v>
+        <v>7391994</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25786,10 +25786,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>120434833</v>
+        <v>120434878</v>
       </c>
       <c r="B248" t="n">
-        <v>91901</v>
+        <v>91858</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -25798,25 +25798,25 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -25826,10 +25826,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>810850</v>
+        <v>811137</v>
       </c>
       <c r="R248" t="n">
-        <v>7392159</v>
+        <v>7392085</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25888,10 +25888,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>120434835</v>
+        <v>120434871</v>
       </c>
       <c r="B249" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -25900,25 +25900,25 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -25928,10 +25928,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>811225</v>
+        <v>811046</v>
       </c>
       <c r="R249" t="n">
-        <v>7392170</v>
+        <v>7392008</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -25990,7 +25990,7 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>120434868</v>
+        <v>120434866</v>
       </c>
       <c r="B250" t="n">
         <v>91858</v>
@@ -26030,10 +26030,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>811010</v>
+        <v>810910</v>
       </c>
       <c r="R250" t="n">
-        <v>7392090</v>
+        <v>7392182</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -26092,10 +26092,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>120434878</v>
+        <v>120434840</v>
       </c>
       <c r="B251" t="n">
-        <v>91858</v>
+        <v>91862</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -26104,25 +26104,25 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -26132,10 +26132,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>811137</v>
+        <v>811025</v>
       </c>
       <c r="R251" t="n">
-        <v>7392085</v>
+        <v>7392081</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -26194,7 +26194,7 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>120434885</v>
+        <v>120434870</v>
       </c>
       <c r="B252" t="n">
         <v>91858</v>
@@ -26234,10 +26234,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>811136</v>
+        <v>811034</v>
       </c>
       <c r="R252" t="n">
-        <v>7392197</v>
+        <v>7392011</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -26296,10 +26296,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>120434876</v>
+        <v>120434827</v>
       </c>
       <c r="B253" t="n">
-        <v>91858</v>
+        <v>91481</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -26308,25 +26308,25 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -26336,10 +26336,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>811136</v>
+        <v>810903</v>
       </c>
       <c r="R253" t="n">
-        <v>7392082</v>
+        <v>7392182</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26398,10 +26398,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>120434850</v>
+        <v>120434839</v>
       </c>
       <c r="B254" t="n">
-        <v>88170</v>
+        <v>91862</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -26410,25 +26410,25 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>4962</v>
+        <v>4365</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -26438,10 +26438,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>811200</v>
+        <v>811144</v>
       </c>
       <c r="R254" t="n">
-        <v>7392176</v>
+        <v>7392037</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26500,10 +26500,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>120434888</v>
+        <v>120434847</v>
       </c>
       <c r="B255" t="n">
-        <v>91858</v>
+        <v>96891</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -26516,21 +26516,21 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -26540,10 +26540,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>811101</v>
+        <v>811044</v>
       </c>
       <c r="R255" t="n">
-        <v>7392164</v>
+        <v>7392264</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26602,10 +26602,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>120434853</v>
+        <v>120434833</v>
       </c>
       <c r="B256" t="n">
-        <v>78278</v>
+        <v>91901</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -26618,21 +26618,21 @@
         </is>
       </c>
       <c r="E256" t="n">
-        <v>6446</v>
+        <v>5448</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -26642,10 +26642,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>811148</v>
+        <v>810850</v>
       </c>
       <c r="R256" t="n">
-        <v>7391971</v>
+        <v>7392159</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26704,7 +26704,7 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>120434871</v>
+        <v>120434887</v>
       </c>
       <c r="B257" t="n">
         <v>91858</v>
@@ -26744,10 +26744,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>811046</v>
+        <v>811128</v>
       </c>
       <c r="R257" t="n">
-        <v>7392008</v>
+        <v>7392175</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -26806,7 +26806,7 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>120434883</v>
+        <v>120434885</v>
       </c>
       <c r="B258" t="n">
         <v>91858</v>
@@ -26846,10 +26846,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>811129</v>
+        <v>811136</v>
       </c>
       <c r="R258" t="n">
-        <v>7392249</v>
+        <v>7392197</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -26908,10 +26908,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>120434846</v>
+        <v>120434874</v>
       </c>
       <c r="B259" t="n">
-        <v>96891</v>
+        <v>91858</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -26924,21 +26924,21 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -26948,10 +26948,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>811187</v>
+        <v>811138</v>
       </c>
       <c r="R259" t="n">
-        <v>7392082</v>
+        <v>7392034</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -27010,10 +27010,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>120434872</v>
+        <v>120434898</v>
       </c>
       <c r="B260" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -27022,25 +27022,25 @@
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E260" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -27050,10 +27050,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>811073</v>
+        <v>811095</v>
       </c>
       <c r="R260" t="n">
-        <v>7391995</v>
+        <v>7392048</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -27112,10 +27112,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>120434819</v>
+        <v>120434867</v>
       </c>
       <c r="B261" t="n">
-        <v>89650</v>
+        <v>91858</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -27124,25 +27124,25 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -27152,10 +27152,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>811135</v>
+        <v>810911</v>
       </c>
       <c r="R261" t="n">
-        <v>7392091</v>
+        <v>7392181</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -27214,10 +27214,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>120434864</v>
+        <v>120434841</v>
       </c>
       <c r="B262" t="n">
-        <v>91858</v>
+        <v>91862</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -27226,25 +27226,25 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -27254,10 +27254,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>810914</v>
+        <v>811019</v>
       </c>
       <c r="R262" t="n">
-        <v>7392166</v>
+        <v>7392096</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27316,7 +27316,7 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>120434870</v>
+        <v>120434884</v>
       </c>
       <c r="B263" t="n">
         <v>91858</v>
@@ -27356,10 +27356,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>811034</v>
+        <v>811098</v>
       </c>
       <c r="R263" t="n">
-        <v>7392011</v>
+        <v>7392240</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -27418,10 +27418,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>120434839</v>
+        <v>120434852</v>
       </c>
       <c r="B264" t="n">
-        <v>91862</v>
+        <v>57431</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -27430,25 +27430,25 @@
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E264" t="n">
-        <v>4365</v>
+        <v>103031</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
@@ -27458,10 +27458,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>811144</v>
+        <v>810910</v>
       </c>
       <c r="R264" t="n">
-        <v>7392037</v>
+        <v>7392005</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27520,10 +27520,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>120434847</v>
+        <v>120434842</v>
       </c>
       <c r="B265" t="n">
-        <v>96891</v>
+        <v>91874</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -27532,25 +27532,25 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>221941</v>
+        <v>2059</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
@@ -27560,10 +27560,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>811044</v>
+        <v>811110</v>
       </c>
       <c r="R265" t="n">
-        <v>7392264</v>
+        <v>7392006</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27622,7 +27622,7 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>120434884</v>
+        <v>120434882</v>
       </c>
       <c r="B266" t="n">
         <v>91858</v>
@@ -27662,10 +27662,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>811098</v>
+        <v>811166</v>
       </c>
       <c r="R266" t="n">
-        <v>7392240</v>
+        <v>7392206</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -27724,7 +27724,7 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>120434851</v>
+        <v>120434849</v>
       </c>
       <c r="B267" t="n">
         <v>88170</v>
@@ -27764,10 +27764,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>811087</v>
+        <v>811223</v>
       </c>
       <c r="R267" t="n">
-        <v>7392152</v>
+        <v>7392167</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -27826,10 +27826,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>120434841</v>
+        <v>120434888</v>
       </c>
       <c r="B268" t="n">
-        <v>91862</v>
+        <v>91858</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -27838,25 +27838,25 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -27866,10 +27866,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>811019</v>
+        <v>811101</v>
       </c>
       <c r="R268" t="n">
-        <v>7392096</v>
+        <v>7392164</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -27928,10 +27928,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>120434830</v>
+        <v>120434821</v>
       </c>
       <c r="B269" t="n">
-        <v>91902</v>
+        <v>89650</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -27944,21 +27944,21 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>5449</v>
+        <v>1962</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -27968,10 +27968,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>811019</v>
+        <v>811073</v>
       </c>
       <c r="R269" t="n">
-        <v>7392096</v>
+        <v>7392186</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -28030,10 +28030,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>120434821</v>
+        <v>120434853</v>
       </c>
       <c r="B270" t="n">
-        <v>89650</v>
+        <v>78278</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -28046,21 +28046,21 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
@@ -28070,10 +28070,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>811073</v>
+        <v>811148</v>
       </c>
       <c r="R270" t="n">
-        <v>7392186</v>
+        <v>7391971</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -28132,10 +28132,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>120434891</v>
+        <v>120434817</v>
       </c>
       <c r="B271" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -28144,25 +28144,25 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
@@ -28172,10 +28172,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>811023</v>
+        <v>811018</v>
       </c>
       <c r="R271" t="n">
-        <v>7392157</v>
+        <v>7392105</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -28234,7 +28234,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>120434866</v>
+        <v>120434886</v>
       </c>
       <c r="B272" t="n">
         <v>91858</v>
@@ -28274,10 +28274,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>810910</v>
+        <v>811121</v>
       </c>
       <c r="R272" t="n">
-        <v>7392182</v>
+        <v>7392171</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -28336,10 +28336,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>120434827</v>
+        <v>120434875</v>
       </c>
       <c r="B273" t="n">
-        <v>91481</v>
+        <v>91858</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -28348,25 +28348,25 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>4745</v>
+        <v>4364</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
@@ -28376,10 +28376,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>810903</v>
+        <v>811108</v>
       </c>
       <c r="R273" t="n">
-        <v>7392182</v>
+        <v>7392073</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -28438,10 +28438,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>120434865</v>
+        <v>120434819</v>
       </c>
       <c r="B274" t="n">
-        <v>91858</v>
+        <v>89650</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -28450,25 +28450,25 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -28478,10 +28478,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>810887</v>
+        <v>811135</v>
       </c>
       <c r="R274" t="n">
-        <v>7392183</v>
+        <v>7392091</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -28540,10 +28540,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>120434893</v>
+        <v>120434835</v>
       </c>
       <c r="B275" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -28552,25 +28552,25 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -28580,10 +28580,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>811088</v>
+        <v>811225</v>
       </c>
       <c r="R275" t="n">
-        <v>7392240</v>
+        <v>7392170</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -28642,10 +28642,10 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>120434842</v>
+        <v>120434868</v>
       </c>
       <c r="B276" t="n">
-        <v>91874</v>
+        <v>91858</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
@@ -28654,25 +28654,25 @@
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E276" t="n">
-        <v>2059</v>
+        <v>4364</v>
       </c>
       <c r="F276" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G276" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I276" t="inlineStr"/>
@@ -28682,10 +28682,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>811110</v>
+        <v>811010</v>
       </c>
       <c r="R276" t="n">
-        <v>7392006</v>
+        <v>7392090</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -28744,10 +28744,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>120434879</v>
+        <v>120434851</v>
       </c>
       <c r="B277" t="n">
-        <v>91858</v>
+        <v>88170</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -28756,25 +28756,25 @@
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E277" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
@@ -28784,10 +28784,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>811161</v>
+        <v>811087</v>
       </c>
       <c r="R277" t="n">
-        <v>7392143</v>
+        <v>7392152</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -28846,10 +28846,10 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>120434855</v>
+        <v>120434890</v>
       </c>
       <c r="B278" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
@@ -28858,25 +28858,25 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E278" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I278" t="inlineStr"/>
@@ -28886,10 +28886,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>811078</v>
+        <v>811035</v>
       </c>
       <c r="R278" t="n">
-        <v>7392236</v>
+        <v>7392102</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -28948,10 +28948,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>120434887</v>
+        <v>120434836</v>
       </c>
       <c r="B279" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -28960,25 +28960,25 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
@@ -28988,10 +28988,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>811128</v>
+        <v>811206</v>
       </c>
       <c r="R279" t="n">
-        <v>7392175</v>
+        <v>7392173</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -29050,7 +29050,7 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>120434895</v>
+        <v>120434893</v>
       </c>
       <c r="B280" t="n">
         <v>91858</v>
@@ -29090,10 +29090,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>811053</v>
+        <v>811088</v>
       </c>
       <c r="R280" t="n">
-        <v>7392247</v>
+        <v>7392240</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -29152,10 +29152,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>120434894</v>
+        <v>120434850</v>
       </c>
       <c r="B281" t="n">
-        <v>91858</v>
+        <v>88170</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -29164,25 +29164,25 @@
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E281" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
@@ -29192,10 +29192,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>811099</v>
+        <v>811200</v>
       </c>
       <c r="R281" t="n">
-        <v>7392252</v>
+        <v>7392176</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -29254,10 +29254,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>120434829</v>
+        <v>120434846</v>
       </c>
       <c r="B282" t="n">
-        <v>91904</v>
+        <v>96891</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -29266,25 +29266,25 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>232140</v>
+        <v>221941</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
@@ -29294,10 +29294,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>811018</v>
+        <v>811187</v>
       </c>
       <c r="R282" t="n">
-        <v>7392095</v>
+        <v>7392082</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -29338,7 +29338,6 @@
       <c r="AE282" t="b">
         <v>0</v>
       </c>
-      <c r="AF282" t="inlineStr"/>
       <c r="AG282" t="b">
         <v>0</v>
       </c>
@@ -29357,10 +29356,10 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>120434867</v>
+        <v>120434823</v>
       </c>
       <c r="B283" t="n">
-        <v>91858</v>
+        <v>89650</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -29369,25 +29368,25 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
@@ -29397,10 +29396,10 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>810911</v>
+        <v>811063</v>
       </c>
       <c r="R283" t="n">
-        <v>7392181</v>
+        <v>7392237</v>
       </c>
       <c r="S283" t="n">
         <v>10</v>
@@ -29459,10 +29458,10 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>120434840</v>
+        <v>120434830</v>
       </c>
       <c r="B284" t="n">
-        <v>91862</v>
+        <v>91902</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -29471,25 +29470,25 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>4365</v>
+        <v>5449</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -29499,10 +29498,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>811025</v>
+        <v>811019</v>
       </c>
       <c r="R284" t="n">
-        <v>7392081</v>
+        <v>7392096</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -29561,7 +29560,7 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>120434890</v>
+        <v>120434865</v>
       </c>
       <c r="B285" t="n">
         <v>91858</v>
@@ -29601,10 +29600,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>811035</v>
+        <v>810887</v>
       </c>
       <c r="R285" t="n">
-        <v>7392102</v>
+        <v>7392183</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -29663,10 +29662,10 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>120434881</v>
+        <v>120434831</v>
       </c>
       <c r="B286" t="n">
-        <v>91858</v>
+        <v>91901</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -29675,25 +29674,25 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I286" t="inlineStr"/>
@@ -29703,10 +29702,10 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>811165</v>
+        <v>811112</v>
       </c>
       <c r="R286" t="n">
-        <v>7392196</v>
+        <v>7392215</v>
       </c>
       <c r="S286" t="n">
         <v>10</v>
@@ -29765,10 +29764,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>120434877</v>
+        <v>120434820</v>
       </c>
       <c r="B287" t="n">
-        <v>91858</v>
+        <v>89650</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -29777,25 +29776,25 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I287" t="inlineStr"/>
@@ -29808,7 +29807,7 @@
         <v>811135</v>
       </c>
       <c r="R287" t="n">
-        <v>7392085</v>
+        <v>7392090</v>
       </c>
       <c r="S287" t="n">
         <v>10</v>
@@ -29867,7 +29866,7 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>120434874</v>
+        <v>120434891</v>
       </c>
       <c r="B288" t="n">
         <v>91858</v>
@@ -29907,10 +29906,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>811138</v>
+        <v>811023</v>
       </c>
       <c r="R288" t="n">
-        <v>7392034</v>
+        <v>7392157</v>
       </c>
       <c r="S288" t="n">
         <v>10</v>
@@ -29969,10 +29968,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>120434886</v>
+        <v>120434837</v>
       </c>
       <c r="B289" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -29981,25 +29980,25 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
@@ -30009,10 +30008,10 @@
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>811121</v>
+        <v>811044</v>
       </c>
       <c r="R289" t="n">
-        <v>7392171</v>
+        <v>7392261</v>
       </c>
       <c r="S289" t="n">
         <v>10</v>
@@ -30071,10 +30070,10 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>120434898</v>
+        <v>120434876</v>
       </c>
       <c r="B290" t="n">
-        <v>91852</v>
+        <v>91858</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
@@ -30083,25 +30082,25 @@
       </c>
       <c r="D290" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E290" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G290" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I290" t="inlineStr"/>
@@ -30111,10 +30110,10 @@
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>811095</v>
+        <v>811136</v>
       </c>
       <c r="R290" t="n">
-        <v>7392048</v>
+        <v>7392082</v>
       </c>
       <c r="S290" t="n">
         <v>10</v>
@@ -30275,10 +30274,10 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>120434818</v>
+        <v>120434883</v>
       </c>
       <c r="B292" t="n">
-        <v>89650</v>
+        <v>91858</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -30287,25 +30286,25 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I292" t="inlineStr"/>
@@ -30315,10 +30314,10 @@
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>811170</v>
+        <v>811129</v>
       </c>
       <c r="R292" t="n">
-        <v>7391994</v>
+        <v>7392249</v>
       </c>
       <c r="S292" t="n">
         <v>10</v>
@@ -30377,10 +30376,10 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>120434899</v>
+        <v>120434855</v>
       </c>
       <c r="B293" t="n">
-        <v>91862</v>
+        <v>78278</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -30389,25 +30388,25 @@
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E293" t="n">
-        <v>4365</v>
+        <v>6446</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I293" t="inlineStr"/>
@@ -30417,10 +30416,10 @@
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>811192</v>
+        <v>811078</v>
       </c>
       <c r="R293" t="n">
-        <v>7392146</v>
+        <v>7392236</v>
       </c>
       <c r="S293" t="n">
         <v>10</v>
@@ -30479,10 +30478,10 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>120434817</v>
+        <v>120434845</v>
       </c>
       <c r="B294" t="n">
-        <v>79160</v>
+        <v>96891</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -30491,25 +30490,25 @@
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E294" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I294" t="inlineStr"/>
@@ -30519,10 +30518,10 @@
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>811018</v>
+        <v>810859</v>
       </c>
       <c r="R294" t="n">
-        <v>7392105</v>
+        <v>7392159</v>
       </c>
       <c r="S294" t="n">
         <v>10</v>
@@ -30581,10 +30580,10 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>120434838</v>
+        <v>120434829</v>
       </c>
       <c r="B295" t="n">
-        <v>91839</v>
+        <v>91904</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -30597,21 +30596,21 @@
         </is>
       </c>
       <c r="E295" t="n">
-        <v>6055</v>
+        <v>232140</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I295" t="inlineStr"/>
@@ -30621,10 +30620,10 @@
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>811032</v>
+        <v>811018</v>
       </c>
       <c r="R295" t="n">
-        <v>7392087</v>
+        <v>7392095</v>
       </c>
       <c r="S295" t="n">
         <v>10</v>
@@ -30665,6 +30664,7 @@
       <c r="AE295" t="b">
         <v>0</v>
       </c>
+      <c r="AF295" t="inlineStr"/>
       <c r="AG295" t="b">
         <v>0</v>
       </c>
@@ -30683,7 +30683,7 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>120434873</v>
+        <v>120434892</v>
       </c>
       <c r="B296" t="n">
         <v>91858</v>
@@ -30723,10 +30723,10 @@
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>811170</v>
+        <v>811071</v>
       </c>
       <c r="R296" t="n">
-        <v>7391994</v>
+        <v>7392203</v>
       </c>
       <c r="S296" t="n">
         <v>10</v>
@@ -30785,10 +30785,10 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>120434854</v>
+        <v>120434872</v>
       </c>
       <c r="B297" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -30797,25 +30797,25 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I297" t="inlineStr"/>
@@ -30825,10 +30825,10 @@
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>811151</v>
+        <v>811073</v>
       </c>
       <c r="R297" t="n">
-        <v>7392024</v>
+        <v>7391995</v>
       </c>
       <c r="S297" t="n">
         <v>10</v>
@@ -30887,10 +30887,10 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>120434832</v>
+        <v>120434854</v>
       </c>
       <c r="B298" t="n">
-        <v>91901</v>
+        <v>78278</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -30903,21 +30903,21 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>5448</v>
+        <v>6446</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I298" t="inlineStr"/>
@@ -30927,10 +30927,10 @@
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>811072</v>
+        <v>811151</v>
       </c>
       <c r="R298" t="n">
-        <v>7392186</v>
+        <v>7392024</v>
       </c>
       <c r="S298" t="n">
         <v>10</v>

--- a/artfynd/A 10151-2023 artfynd.xlsx
+++ b/artfynd/A 10151-2023 artfynd.xlsx
@@ -24255,10 +24255,10 @@
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>120434832</v>
+        <v>120434891</v>
       </c>
       <c r="B233" t="n">
-        <v>91901</v>
+        <v>91858</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
@@ -24267,25 +24267,25 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E233" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G233" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I233" t="inlineStr"/>
@@ -24295,10 +24295,10 @@
         </is>
       </c>
       <c r="Q233" t="n">
-        <v>811072</v>
+        <v>811023</v>
       </c>
       <c r="R233" t="n">
-        <v>7392186</v>
+        <v>7392157</v>
       </c>
       <c r="S233" t="n">
         <v>10</v>
@@ -24357,10 +24357,10 @@
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>120434838</v>
+        <v>120434882</v>
       </c>
       <c r="B234" t="n">
-        <v>91839</v>
+        <v>91858</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
@@ -24369,25 +24369,25 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E234" t="n">
-        <v>6055</v>
+        <v>4364</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Spadskinn</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G234" t="inlineStr">
         <is>
-          <t>Stereopsis vitellina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>(S.Lundell) D.A.Reid</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
@@ -24397,10 +24397,10 @@
         </is>
       </c>
       <c r="Q234" t="n">
-        <v>811032</v>
+        <v>811166</v>
       </c>
       <c r="R234" t="n">
-        <v>7392087</v>
+        <v>7392206</v>
       </c>
       <c r="S234" t="n">
         <v>10</v>
@@ -24459,10 +24459,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>120434864</v>
+        <v>120434830</v>
       </c>
       <c r="B235" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -24471,25 +24471,25 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E235" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -24499,10 +24499,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>810914</v>
+        <v>811019</v>
       </c>
       <c r="R235" t="n">
-        <v>7392166</v>
+        <v>7392096</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -24561,10 +24561,10 @@
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>120434899</v>
+        <v>120434822</v>
       </c>
       <c r="B236" t="n">
-        <v>91862</v>
+        <v>89650</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
@@ -24573,25 +24573,25 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E236" t="n">
-        <v>4365</v>
+        <v>1962</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G236" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
@@ -24601,10 +24601,10 @@
         </is>
       </c>
       <c r="Q236" t="n">
-        <v>811192</v>
+        <v>811056</v>
       </c>
       <c r="R236" t="n">
-        <v>7392146</v>
+        <v>7392242</v>
       </c>
       <c r="S236" t="n">
         <v>10</v>
@@ -24663,10 +24663,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>120434895</v>
+        <v>120434817</v>
       </c>
       <c r="B237" t="n">
-        <v>91858</v>
+        <v>79160</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -24675,25 +24675,25 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E237" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -24703,10 +24703,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>811053</v>
+        <v>811018</v>
       </c>
       <c r="R237" t="n">
-        <v>7392247</v>
+        <v>7392105</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -24765,10 +24765,10 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>120434879</v>
+        <v>120434899</v>
       </c>
       <c r="B238" t="n">
-        <v>91858</v>
+        <v>91862</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
@@ -24777,25 +24777,25 @@
       </c>
       <c r="D238" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E238" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G238" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
@@ -24805,10 +24805,10 @@
         </is>
       </c>
       <c r="Q238" t="n">
-        <v>811161</v>
+        <v>811192</v>
       </c>
       <c r="R238" t="n">
-        <v>7392143</v>
+        <v>7392146</v>
       </c>
       <c r="S238" t="n">
         <v>10</v>
@@ -24867,10 +24867,10 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>120434894</v>
+        <v>120434833</v>
       </c>
       <c r="B239" t="n">
-        <v>91858</v>
+        <v>91901</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
@@ -24879,25 +24879,25 @@
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E239" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
@@ -24907,10 +24907,10 @@
         </is>
       </c>
       <c r="Q239" t="n">
-        <v>811099</v>
+        <v>810850</v>
       </c>
       <c r="R239" t="n">
-        <v>7392252</v>
+        <v>7392159</v>
       </c>
       <c r="S239" t="n">
         <v>10</v>
@@ -24969,7 +24969,7 @@
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>120434873</v>
+        <v>120434883</v>
       </c>
       <c r="B240" t="n">
         <v>91858</v>
@@ -25009,10 +25009,10 @@
         </is>
       </c>
       <c r="Q240" t="n">
-        <v>811170</v>
+        <v>811129</v>
       </c>
       <c r="R240" t="n">
-        <v>7391994</v>
+        <v>7392249</v>
       </c>
       <c r="S240" t="n">
         <v>10</v>
@@ -25071,7 +25071,7 @@
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>120434877</v>
+        <v>120434878</v>
       </c>
       <c r="B241" t="n">
         <v>91858</v>
@@ -25111,7 +25111,7 @@
         </is>
       </c>
       <c r="Q241" t="n">
-        <v>811135</v>
+        <v>811137</v>
       </c>
       <c r="R241" t="n">
         <v>7392085</v>
@@ -25173,7 +25173,7 @@
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>120434889</v>
+        <v>120434876</v>
       </c>
       <c r="B242" t="n">
         <v>91858</v>
@@ -25213,10 +25213,10 @@
         </is>
       </c>
       <c r="Q242" t="n">
-        <v>811045</v>
+        <v>811136</v>
       </c>
       <c r="R242" t="n">
-        <v>7392096</v>
+        <v>7392082</v>
       </c>
       <c r="S242" t="n">
         <v>10</v>
@@ -25275,10 +25275,10 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>120434881</v>
+        <v>120434839</v>
       </c>
       <c r="B243" t="n">
-        <v>91858</v>
+        <v>91862</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
@@ -25287,25 +25287,25 @@
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E243" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G243" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
@@ -25315,10 +25315,10 @@
         </is>
       </c>
       <c r="Q243" t="n">
-        <v>811165</v>
+        <v>811144</v>
       </c>
       <c r="R243" t="n">
-        <v>7392196</v>
+        <v>7392037</v>
       </c>
       <c r="S243" t="n">
         <v>10</v>
@@ -25377,10 +25377,10 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>120434828</v>
+        <v>120434818</v>
       </c>
       <c r="B244" t="n">
-        <v>91904</v>
+        <v>89650</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
@@ -25389,25 +25389,25 @@
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E244" t="n">
-        <v>232140</v>
+        <v>1962</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G244" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
@@ -25417,10 +25417,10 @@
         </is>
       </c>
       <c r="Q244" t="n">
-        <v>811160</v>
+        <v>811170</v>
       </c>
       <c r="R244" t="n">
-        <v>7392120</v>
+        <v>7391994</v>
       </c>
       <c r="S244" t="n">
         <v>10</v>
@@ -25461,7 +25461,6 @@
       <c r="AE244" t="b">
         <v>0</v>
       </c>
-      <c r="AF244" t="inlineStr"/>
       <c r="AG244" t="b">
         <v>0</v>
       </c>
@@ -25480,7 +25479,7 @@
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>120434822</v>
+        <v>120434820</v>
       </c>
       <c r="B245" t="n">
         <v>89650</v>
@@ -25520,10 +25519,10 @@
         </is>
       </c>
       <c r="Q245" t="n">
-        <v>811056</v>
+        <v>811135</v>
       </c>
       <c r="R245" t="n">
-        <v>7392242</v>
+        <v>7392090</v>
       </c>
       <c r="S245" t="n">
         <v>10</v>
@@ -25582,7 +25581,7 @@
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>120434818</v>
+        <v>120434823</v>
       </c>
       <c r="B246" t="n">
         <v>89650</v>
@@ -25622,10 +25621,10 @@
         </is>
       </c>
       <c r="Q246" t="n">
-        <v>811170</v>
+        <v>811063</v>
       </c>
       <c r="R246" t="n">
-        <v>7391994</v>
+        <v>7392237</v>
       </c>
       <c r="S246" t="n">
         <v>10</v>
@@ -25684,7 +25683,7 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>120434869</v>
+        <v>120434874</v>
       </c>
       <c r="B247" t="n">
         <v>91858</v>
@@ -25724,10 +25723,10 @@
         </is>
       </c>
       <c r="Q247" t="n">
-        <v>811038</v>
+        <v>811138</v>
       </c>
       <c r="R247" t="n">
-        <v>7392074</v>
+        <v>7392034</v>
       </c>
       <c r="S247" t="n">
         <v>10</v>
@@ -25786,10 +25785,10 @@
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>120434878</v>
+        <v>120434828</v>
       </c>
       <c r="B248" t="n">
-        <v>91858</v>
+        <v>91904</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -25798,25 +25797,25 @@
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E248" t="n">
-        <v>4364</v>
+        <v>232140</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G248" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I248" t="inlineStr"/>
@@ -25826,10 +25825,10 @@
         </is>
       </c>
       <c r="Q248" t="n">
-        <v>811137</v>
+        <v>811160</v>
       </c>
       <c r="R248" t="n">
-        <v>7392085</v>
+        <v>7392120</v>
       </c>
       <c r="S248" t="n">
         <v>10</v>
@@ -25870,6 +25869,7 @@
       <c r="AE248" t="b">
         <v>0</v>
       </c>
+      <c r="AF248" t="inlineStr"/>
       <c r="AG248" t="b">
         <v>0</v>
       </c>
@@ -25888,10 +25888,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>120434871</v>
+        <v>120434898</v>
       </c>
       <c r="B249" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -25900,25 +25900,25 @@
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E249" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -25928,10 +25928,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>811046</v>
+        <v>811095</v>
       </c>
       <c r="R249" t="n">
-        <v>7392008</v>
+        <v>7392048</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -25990,7 +25990,7 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>120434866</v>
+        <v>120434865</v>
       </c>
       <c r="B250" t="n">
         <v>91858</v>
@@ -26030,10 +26030,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>810910</v>
+        <v>810887</v>
       </c>
       <c r="R250" t="n">
-        <v>7392182</v>
+        <v>7392183</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -26092,10 +26092,10 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>120434840</v>
+        <v>120434886</v>
       </c>
       <c r="B251" t="n">
-        <v>91862</v>
+        <v>91858</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
@@ -26104,25 +26104,25 @@
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E251" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G251" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I251" t="inlineStr"/>
@@ -26132,10 +26132,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>811025</v>
+        <v>811121</v>
       </c>
       <c r="R251" t="n">
-        <v>7392081</v>
+        <v>7392171</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -26194,10 +26194,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>120434870</v>
+        <v>120434855</v>
       </c>
       <c r="B252" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -26206,25 +26206,25 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -26234,10 +26234,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>811034</v>
+        <v>811078</v>
       </c>
       <c r="R252" t="n">
-        <v>7392011</v>
+        <v>7392236</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -26296,10 +26296,10 @@
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>120434827</v>
+        <v>120434829</v>
       </c>
       <c r="B253" t="n">
-        <v>91481</v>
+        <v>91904</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
@@ -26308,25 +26308,25 @@
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E253" t="n">
-        <v>4745</v>
+        <v>232140</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Tajgataggsvamp</t>
         </is>
       </c>
       <c r="G253" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Phellodon secretus</t>
         </is>
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Niemelä &amp; Kinnunen</t>
         </is>
       </c>
       <c r="I253" t="inlineStr"/>
@@ -26336,10 +26336,10 @@
         </is>
       </c>
       <c r="Q253" t="n">
-        <v>810903</v>
+        <v>811018</v>
       </c>
       <c r="R253" t="n">
-        <v>7392182</v>
+        <v>7392095</v>
       </c>
       <c r="S253" t="n">
         <v>10</v>
@@ -26380,6 +26380,7 @@
       <c r="AE253" t="b">
         <v>0</v>
       </c>
+      <c r="AF253" t="inlineStr"/>
       <c r="AG253" t="b">
         <v>0</v>
       </c>
@@ -26398,10 +26399,10 @@
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>120434839</v>
+        <v>120434890</v>
       </c>
       <c r="B254" t="n">
-        <v>91862</v>
+        <v>91858</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
@@ -26410,25 +26411,25 @@
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E254" t="n">
-        <v>4365</v>
+        <v>4364</v>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G254" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
@@ -26438,10 +26439,10 @@
         </is>
       </c>
       <c r="Q254" t="n">
-        <v>811144</v>
+        <v>811035</v>
       </c>
       <c r="R254" t="n">
-        <v>7392037</v>
+        <v>7392102</v>
       </c>
       <c r="S254" t="n">
         <v>10</v>
@@ -26500,10 +26501,10 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>120434847</v>
+        <v>120434870</v>
       </c>
       <c r="B255" t="n">
-        <v>96891</v>
+        <v>91858</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -26516,21 +26517,21 @@
         </is>
       </c>
       <c r="E255" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G255" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
@@ -26540,10 +26541,10 @@
         </is>
       </c>
       <c r="Q255" t="n">
-        <v>811044</v>
+        <v>811034</v>
       </c>
       <c r="R255" t="n">
-        <v>7392264</v>
+        <v>7392011</v>
       </c>
       <c r="S255" t="n">
         <v>10</v>
@@ -26602,10 +26603,10 @@
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>120434833</v>
+        <v>120434867</v>
       </c>
       <c r="B256" t="n">
-        <v>91901</v>
+        <v>91858</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
@@ -26614,25 +26615,25 @@
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E256" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G256" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
@@ -26642,10 +26643,10 @@
         </is>
       </c>
       <c r="Q256" t="n">
-        <v>810850</v>
+        <v>810911</v>
       </c>
       <c r="R256" t="n">
-        <v>7392159</v>
+        <v>7392181</v>
       </c>
       <c r="S256" t="n">
         <v>10</v>
@@ -26704,7 +26705,7 @@
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>120434887</v>
+        <v>120434877</v>
       </c>
       <c r="B257" t="n">
         <v>91858</v>
@@ -26744,10 +26745,10 @@
         </is>
       </c>
       <c r="Q257" t="n">
-        <v>811128</v>
+        <v>811135</v>
       </c>
       <c r="R257" t="n">
-        <v>7392175</v>
+        <v>7392085</v>
       </c>
       <c r="S257" t="n">
         <v>10</v>
@@ -26806,7 +26807,7 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>120434885</v>
+        <v>120434893</v>
       </c>
       <c r="B258" t="n">
         <v>91858</v>
@@ -26846,10 +26847,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>811136</v>
+        <v>811088</v>
       </c>
       <c r="R258" t="n">
-        <v>7392197</v>
+        <v>7392240</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -26908,10 +26909,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>120434874</v>
+        <v>120434851</v>
       </c>
       <c r="B259" t="n">
-        <v>91858</v>
+        <v>88170</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -26920,25 +26921,25 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -26948,10 +26949,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>811138</v>
+        <v>811087</v>
       </c>
       <c r="R259" t="n">
-        <v>7392034</v>
+        <v>7392152</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -27010,10 +27011,10 @@
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>120434898</v>
+        <v>120434842</v>
       </c>
       <c r="B260" t="n">
-        <v>91852</v>
+        <v>91874</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
@@ -27026,21 +27027,21 @@
         </is>
       </c>
       <c r="E260" t="n">
-        <v>4362</v>
+        <v>2059</v>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G260" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I260" t="inlineStr"/>
@@ -27050,10 +27051,10 @@
         </is>
       </c>
       <c r="Q260" t="n">
-        <v>811095</v>
+        <v>811110</v>
       </c>
       <c r="R260" t="n">
-        <v>7392048</v>
+        <v>7392006</v>
       </c>
       <c r="S260" t="n">
         <v>10</v>
@@ -27112,10 +27113,10 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>120434867</v>
+        <v>120434854</v>
       </c>
       <c r="B261" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
@@ -27124,25 +27125,25 @@
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E261" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G261" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I261" t="inlineStr"/>
@@ -27152,10 +27153,10 @@
         </is>
       </c>
       <c r="Q261" t="n">
-        <v>810911</v>
+        <v>811151</v>
       </c>
       <c r="R261" t="n">
-        <v>7392181</v>
+        <v>7392024</v>
       </c>
       <c r="S261" t="n">
         <v>10</v>
@@ -27214,10 +27215,10 @@
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>120434841</v>
+        <v>120434847</v>
       </c>
       <c r="B262" t="n">
-        <v>91862</v>
+        <v>96891</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
@@ -27226,25 +27227,25 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E262" t="n">
-        <v>4365</v>
+        <v>221941</v>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Smalfotad taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G262" t="inlineStr">
         <is>
-          <t>Hydnellum gracilipes</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>(P.Karst) P.Karst</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I262" t="inlineStr"/>
@@ -27254,10 +27255,10 @@
         </is>
       </c>
       <c r="Q262" t="n">
-        <v>811019</v>
+        <v>811044</v>
       </c>
       <c r="R262" t="n">
-        <v>7392096</v>
+        <v>7392264</v>
       </c>
       <c r="S262" t="n">
         <v>10</v>
@@ -27316,7 +27317,7 @@
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>120434884</v>
+        <v>120434888</v>
       </c>
       <c r="B263" t="n">
         <v>91858</v>
@@ -27356,10 +27357,10 @@
         </is>
       </c>
       <c r="Q263" t="n">
-        <v>811098</v>
+        <v>811101</v>
       </c>
       <c r="R263" t="n">
-        <v>7392240</v>
+        <v>7392164</v>
       </c>
       <c r="S263" t="n">
         <v>10</v>
@@ -27418,10 +27419,10 @@
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>120434852</v>
+        <v>120434873</v>
       </c>
       <c r="B264" t="n">
-        <v>57431</v>
+        <v>91858</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
@@ -27434,21 +27435,21 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>103031</v>
+        <v>4364</v>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G264" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I264" t="inlineStr"/>
@@ -27458,10 +27459,10 @@
         </is>
       </c>
       <c r="Q264" t="n">
-        <v>810910</v>
+        <v>811170</v>
       </c>
       <c r="R264" t="n">
-        <v>7392005</v>
+        <v>7391994</v>
       </c>
       <c r="S264" t="n">
         <v>10</v>
@@ -27520,10 +27521,10 @@
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>120434842</v>
+        <v>120434838</v>
       </c>
       <c r="B265" t="n">
-        <v>91874</v>
+        <v>91839</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
@@ -27532,25 +27533,25 @@
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E265" t="n">
-        <v>2059</v>
+        <v>6055</v>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Spadskinn</t>
         </is>
       </c>
       <c r="G265" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Stereopsis vitellina</t>
         </is>
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(S.Lundell) D.A.Reid</t>
         </is>
       </c>
       <c r="I265" t="inlineStr"/>
@@ -27560,10 +27561,10 @@
         </is>
       </c>
       <c r="Q265" t="n">
-        <v>811110</v>
+        <v>811032</v>
       </c>
       <c r="R265" t="n">
-        <v>7392006</v>
+        <v>7392087</v>
       </c>
       <c r="S265" t="n">
         <v>10</v>
@@ -27622,7 +27623,7 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>120434882</v>
+        <v>120434887</v>
       </c>
       <c r="B266" t="n">
         <v>91858</v>
@@ -27662,10 +27663,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>811166</v>
+        <v>811128</v>
       </c>
       <c r="R266" t="n">
-        <v>7392206</v>
+        <v>7392175</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -27724,10 +27725,10 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>120434849</v>
+        <v>120434864</v>
       </c>
       <c r="B267" t="n">
-        <v>88170</v>
+        <v>91858</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
@@ -27736,25 +27737,25 @@
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E267" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G267" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I267" t="inlineStr"/>
@@ -27764,10 +27765,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>811223</v>
+        <v>810914</v>
       </c>
       <c r="R267" t="n">
-        <v>7392167</v>
+        <v>7392166</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -27826,10 +27827,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>120434888</v>
+        <v>120434849</v>
       </c>
       <c r="B268" t="n">
-        <v>91858</v>
+        <v>88170</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -27838,25 +27839,25 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -27866,10 +27867,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>811101</v>
+        <v>811223</v>
       </c>
       <c r="R268" t="n">
-        <v>7392164</v>
+        <v>7392167</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -27928,10 +27929,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>120434821</v>
+        <v>120434853</v>
       </c>
       <c r="B269" t="n">
-        <v>89650</v>
+        <v>78278</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -27944,21 +27945,21 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>1962</v>
+        <v>6446</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -27968,10 +27969,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>811073</v>
+        <v>811148</v>
       </c>
       <c r="R269" t="n">
-        <v>7392186</v>
+        <v>7391971</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -28030,10 +28031,10 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>120434853</v>
+        <v>120434868</v>
       </c>
       <c r="B270" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
@@ -28042,25 +28043,25 @@
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E270" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G270" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I270" t="inlineStr"/>
@@ -28070,10 +28071,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>811148</v>
+        <v>811010</v>
       </c>
       <c r="R270" t="n">
-        <v>7391971</v>
+        <v>7392090</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -28132,10 +28133,10 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>120434817</v>
+        <v>120434884</v>
       </c>
       <c r="B271" t="n">
-        <v>79160</v>
+        <v>91858</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
@@ -28144,25 +28145,25 @@
       </c>
       <c r="D271" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E271" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G271" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I271" t="inlineStr"/>
@@ -28172,10 +28173,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>811018</v>
+        <v>811098</v>
       </c>
       <c r="R271" t="n">
-        <v>7392105</v>
+        <v>7392240</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -28234,7 +28235,7 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>120434886</v>
+        <v>120434875</v>
       </c>
       <c r="B272" t="n">
         <v>91858</v>
@@ -28274,10 +28275,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>811121</v>
+        <v>811108</v>
       </c>
       <c r="R272" t="n">
-        <v>7392171</v>
+        <v>7392073</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>
@@ -28336,10 +28337,10 @@
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>120434875</v>
+        <v>120434836</v>
       </c>
       <c r="B273" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
@@ -28348,25 +28349,25 @@
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E273" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F273" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G273" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I273" t="inlineStr"/>
@@ -28376,10 +28377,10 @@
         </is>
       </c>
       <c r="Q273" t="n">
-        <v>811108</v>
+        <v>811206</v>
       </c>
       <c r="R273" t="n">
-        <v>7392073</v>
+        <v>7392173</v>
       </c>
       <c r="S273" t="n">
         <v>10</v>
@@ -28438,10 +28439,10 @@
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>120434819</v>
+        <v>120434894</v>
       </c>
       <c r="B274" t="n">
-        <v>89650</v>
+        <v>91858</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
@@ -28450,25 +28451,25 @@
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E274" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G274" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I274" t="inlineStr"/>
@@ -28478,10 +28479,10 @@
         </is>
       </c>
       <c r="Q274" t="n">
-        <v>811135</v>
+        <v>811099</v>
       </c>
       <c r="R274" t="n">
-        <v>7392091</v>
+        <v>7392252</v>
       </c>
       <c r="S274" t="n">
         <v>10</v>
@@ -28540,10 +28541,10 @@
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>120434835</v>
+        <v>120434869</v>
       </c>
       <c r="B275" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
@@ -28552,25 +28553,25 @@
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E275" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G275" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I275" t="inlineStr"/>
@@ -28580,10 +28581,10 @@
         </is>
       </c>
       <c r="Q275" t="n">
-        <v>811225</v>
+        <v>811038</v>
       </c>
       <c r="R275" t="n">
-        <v>7392170</v>
+        <v>7392074</v>
       </c>
       <c r="S275" t="n">
         <v>10</v>
@@ -28642,7 +28643,7 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>120434868</v>
+        <v>120434880</v>
       </c>
       <c r="B276" t="n">
         <v>91858</v>
@@ -28682,10 +28683,10 @@
         </is>
       </c>
       <c r="Q276" t="n">
-        <v>811010</v>
+        <v>811219</v>
       </c>
       <c r="R276" t="n">
-        <v>7392090</v>
+        <v>7392151</v>
       </c>
       <c r="S276" t="n">
         <v>10</v>
@@ -28744,10 +28745,10 @@
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>120434851</v>
+        <v>120434819</v>
       </c>
       <c r="B277" t="n">
-        <v>88170</v>
+        <v>89650</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
@@ -28760,21 +28761,21 @@
         </is>
       </c>
       <c r="E277" t="n">
-        <v>4962</v>
+        <v>1962</v>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G277" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H277" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I277" t="inlineStr"/>
@@ -28784,10 +28785,10 @@
         </is>
       </c>
       <c r="Q277" t="n">
-        <v>811087</v>
+        <v>811135</v>
       </c>
       <c r="R277" t="n">
-        <v>7392152</v>
+        <v>7392091</v>
       </c>
       <c r="S277" t="n">
         <v>10</v>
@@ -28846,7 +28847,7 @@
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>120434890</v>
+        <v>120434892</v>
       </c>
       <c r="B278" t="n">
         <v>91858</v>
@@ -28886,10 +28887,10 @@
         </is>
       </c>
       <c r="Q278" t="n">
-        <v>811035</v>
+        <v>811071</v>
       </c>
       <c r="R278" t="n">
-        <v>7392102</v>
+        <v>7392203</v>
       </c>
       <c r="S278" t="n">
         <v>10</v>
@@ -28948,10 +28949,10 @@
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>120434836</v>
+        <v>120434881</v>
       </c>
       <c r="B279" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
@@ -28960,25 +28961,25 @@
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E279" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I279" t="inlineStr"/>
@@ -28988,10 +28989,10 @@
         </is>
       </c>
       <c r="Q279" t="n">
-        <v>811206</v>
+        <v>811165</v>
       </c>
       <c r="R279" t="n">
-        <v>7392173</v>
+        <v>7392196</v>
       </c>
       <c r="S279" t="n">
         <v>10</v>
@@ -29050,7 +29051,7 @@
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>120434893</v>
+        <v>120434885</v>
       </c>
       <c r="B280" t="n">
         <v>91858</v>
@@ -29090,10 +29091,10 @@
         </is>
       </c>
       <c r="Q280" t="n">
-        <v>811088</v>
+        <v>811136</v>
       </c>
       <c r="R280" t="n">
-        <v>7392240</v>
+        <v>7392197</v>
       </c>
       <c r="S280" t="n">
         <v>10</v>
@@ -29152,10 +29153,10 @@
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>120434850</v>
+        <v>120434837</v>
       </c>
       <c r="B281" t="n">
-        <v>88170</v>
+        <v>91902</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
@@ -29168,21 +29169,21 @@
         </is>
       </c>
       <c r="E281" t="n">
-        <v>4962</v>
+        <v>5449</v>
       </c>
       <c r="F281" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I281" t="inlineStr"/>
@@ -29192,10 +29193,10 @@
         </is>
       </c>
       <c r="Q281" t="n">
-        <v>811200</v>
+        <v>811044</v>
       </c>
       <c r="R281" t="n">
-        <v>7392176</v>
+        <v>7392261</v>
       </c>
       <c r="S281" t="n">
         <v>10</v>
@@ -29254,10 +29255,10 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>120434846</v>
+        <v>120434831</v>
       </c>
       <c r="B282" t="n">
-        <v>96891</v>
+        <v>91901</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
@@ -29266,25 +29267,25 @@
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E282" t="n">
-        <v>221941</v>
+        <v>5448</v>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G282" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I282" t="inlineStr"/>
@@ -29294,10 +29295,10 @@
         </is>
       </c>
       <c r="Q282" t="n">
-        <v>811187</v>
+        <v>811112</v>
       </c>
       <c r="R282" t="n">
-        <v>7392082</v>
+        <v>7392215</v>
       </c>
       <c r="S282" t="n">
         <v>10</v>
@@ -29356,10 +29357,10 @@
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>120434823</v>
+        <v>120434846</v>
       </c>
       <c r="B283" t="n">
-        <v>89650</v>
+        <v>96891</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
@@ -29368,25 +29369,25 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E283" t="n">
-        <v>1962</v>
+        <v>221941</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G283" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I283" t="inlineStr"/>
@@ -29396,10 +29397,10 @@
         </is>
       </c>
       <c r="Q283" t="n">
-        <v>811063</v>
+        <v>811187</v>
       </c>
       <c r="R283" t="n">
-        <v>7392237</v>
+        <v>7392082</v>
       </c>
       <c r="S283" t="n">
         <v>10</v>
@@ -29458,10 +29459,10 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>120434830</v>
+        <v>120434845</v>
       </c>
       <c r="B284" t="n">
-        <v>91902</v>
+        <v>96891</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
@@ -29470,25 +29471,25 @@
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E284" t="n">
-        <v>5449</v>
+        <v>221941</v>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G284" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I284" t="inlineStr"/>
@@ -29498,10 +29499,10 @@
         </is>
       </c>
       <c r="Q284" t="n">
-        <v>811019</v>
+        <v>810859</v>
       </c>
       <c r="R284" t="n">
-        <v>7392096</v>
+        <v>7392159</v>
       </c>
       <c r="S284" t="n">
         <v>10</v>
@@ -29560,10 +29561,10 @@
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>120434865</v>
+        <v>120434827</v>
       </c>
       <c r="B285" t="n">
-        <v>91858</v>
+        <v>91481</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
@@ -29572,25 +29573,25 @@
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E285" t="n">
-        <v>4364</v>
+        <v>4745</v>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G285" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I285" t="inlineStr"/>
@@ -29600,10 +29601,10 @@
         </is>
       </c>
       <c r="Q285" t="n">
-        <v>810887</v>
+        <v>810903</v>
       </c>
       <c r="R285" t="n">
-        <v>7392183</v>
+        <v>7392182</v>
       </c>
       <c r="S285" t="n">
         <v>10</v>
@@ -29662,10 +29663,10 @@
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>120434831</v>
+        <v>120434852</v>
       </c>
       <c r="B286" t="n">
-        <v>91901</v>
+        <v>57431</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
@@ -29674,25 +29675,25 @@
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E286" t="n">
-        <v>5448</v>
+        <v>103031</v>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G286" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I286" t="inlineStr"/>
@@ -29702,10 +29703,10 @@
         </is>
       </c>
       <c r="Q286" t="n">
-        <v>811112</v>
+        <v>810910</v>
       </c>
       <c r="R286" t="n">
-        <v>7392215</v>
+        <v>7392005</v>
       </c>
       <c r="S286" t="n">
         <v>10</v>
@@ -29764,10 +29765,10 @@
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>120434820</v>
+        <v>120434879</v>
       </c>
       <c r="B287" t="n">
-        <v>89650</v>
+        <v>91858</v>
       </c>
       <c r="C287" t="inlineStr">
         <is>
@@ -29776,25 +29777,25 @@
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E287" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G287" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H287" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I287" t="inlineStr"/>
@@ -29804,10 +29805,10 @@
         </is>
       </c>
       <c r="Q287" t="n">
-        <v>811135</v>
+        <v>811161</v>
       </c>
       <c r="R287" t="n">
-        <v>7392090</v>
+        <v>7392143</v>
       </c>
       <c r="S287" t="n">
         <v>10</v>
@@ -29866,10 +29867,10 @@
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>120434891</v>
+        <v>120434841</v>
       </c>
       <c r="B288" t="n">
-        <v>91858</v>
+        <v>91862</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
@@ -29878,25 +29879,25 @@
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E288" t="n">
-        <v>4364</v>
+        <v>4365</v>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G288" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I288" t="inlineStr"/>
@@ -29906,10 +29907,10 @@
         </is>
       </c>
       <c r="Q288" t="n">
-        <v>811023</v>
+        <v>811019</v>
       </c>
       <c r="R288" t="n">
-        <v>7392157</v>
+        <v>7392096</v>
       </c>
       <c r="S288" t="n">
         <v>10</v>
@@ -29968,10 +29969,10 @@
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>120434837</v>
+        <v>120434840</v>
       </c>
       <c r="B289" t="n">
-        <v>91902</v>
+        <v>91862</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
@@ -29980,25 +29981,25 @@
       </c>
       <c r="D289" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E289" t="n">
-        <v>5449</v>
+        <v>4365</v>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Smalfotad taggsvamp</t>
         </is>
       </c>
       <c r="G289" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum gracilipes</t>
         </is>
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(P.Karst) P.Karst</t>
         </is>
       </c>
       <c r="I289" t="inlineStr"/>
@@ -30008,10 +30009,10 @@
         </is>
       </c>
       <c r="Q289" t="n">
-        <v>811044</v>
+        <v>811025</v>
       </c>
       <c r="R289" t="n">
-        <v>7392261</v>
+        <v>7392081</v>
       </c>
       <c r="S289" t="n">
         <v>10</v>
@@ -30070,7 +30071,7 @@
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>120434876</v>
+        <v>120434866</v>
       </c>
       <c r="B290" t="n">
         <v>91858</v>
@@ -30110,10 +30111,10 @@
         </is>
       </c>
       <c r="Q290" t="n">
-        <v>811136</v>
+        <v>810910</v>
       </c>
       <c r="R290" t="n">
-        <v>7392082</v>
+        <v>7392182</v>
       </c>
       <c r="S290" t="n">
         <v>10</v>
@@ -30172,7 +30173,7 @@
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>120434880</v>
+        <v>120434895</v>
       </c>
       <c r="B291" t="n">
         <v>91858</v>
@@ -30212,10 +30213,10 @@
         </is>
       </c>
       <c r="Q291" t="n">
-        <v>811219</v>
+        <v>811053</v>
       </c>
       <c r="R291" t="n">
-        <v>7392151</v>
+        <v>7392247</v>
       </c>
       <c r="S291" t="n">
         <v>10</v>
@@ -30274,10 +30275,10 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>120434883</v>
+        <v>120434835</v>
       </c>
       <c r="B292" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
@@ -30286,25 +30287,25 @@
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E292" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G292" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I292" t="inlineStr"/>
@@ -30314,10 +30315,10 @@
         </is>
       </c>
       <c r="Q292" t="n">
-        <v>811129</v>
+        <v>811225</v>
       </c>
       <c r="R292" t="n">
-        <v>7392249</v>
+        <v>7392170</v>
       </c>
       <c r="S292" t="n">
         <v>10</v>
@@ -30376,10 +30377,10 @@
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>120434855</v>
+        <v>120434821</v>
       </c>
       <c r="B293" t="n">
-        <v>78278</v>
+        <v>89650</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
@@ -30392,21 +30393,21 @@
         </is>
       </c>
       <c r="E293" t="n">
-        <v>6446</v>
+        <v>1962</v>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I293" t="inlineStr"/>
@@ -30416,10 +30417,10 @@
         </is>
       </c>
       <c r="Q293" t="n">
-        <v>811078</v>
+        <v>811073</v>
       </c>
       <c r="R293" t="n">
-        <v>7392236</v>
+        <v>7392186</v>
       </c>
       <c r="S293" t="n">
         <v>10</v>
@@ -30478,10 +30479,10 @@
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>120434845</v>
+        <v>120434889</v>
       </c>
       <c r="B294" t="n">
-        <v>96891</v>
+        <v>91858</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
@@ -30494,21 +30495,21 @@
         </is>
       </c>
       <c r="E294" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I294" t="inlineStr"/>
@@ -30518,10 +30519,10 @@
         </is>
       </c>
       <c r="Q294" t="n">
-        <v>810859</v>
+        <v>811045</v>
       </c>
       <c r="R294" t="n">
-        <v>7392159</v>
+        <v>7392096</v>
       </c>
       <c r="S294" t="n">
         <v>10</v>
@@ -30580,10 +30581,10 @@
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>120434829</v>
+        <v>120434872</v>
       </c>
       <c r="B295" t="n">
-        <v>91904</v>
+        <v>91858</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
@@ -30592,25 +30593,25 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E295" t="n">
-        <v>232140</v>
+        <v>4364</v>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Tajgataggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>Phellodon secretus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>Niemelä &amp; Kinnunen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I295" t="inlineStr"/>
@@ -30620,10 +30621,10 @@
         </is>
       </c>
       <c r="Q295" t="n">
-        <v>811018</v>
+        <v>811073</v>
       </c>
       <c r="R295" t="n">
-        <v>7392095</v>
+        <v>7391995</v>
       </c>
       <c r="S295" t="n">
         <v>10</v>
@@ -30664,7 +30665,6 @@
       <c r="AE295" t="b">
         <v>0</v>
       </c>
-      <c r="AF295" t="inlineStr"/>
       <c r="AG295" t="b">
         <v>0</v>
       </c>
@@ -30683,7 +30683,7 @@
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>120434892</v>
+        <v>120434871</v>
       </c>
       <c r="B296" t="n">
         <v>91858</v>
@@ -30723,10 +30723,10 @@
         </is>
       </c>
       <c r="Q296" t="n">
-        <v>811071</v>
+        <v>811046</v>
       </c>
       <c r="R296" t="n">
-        <v>7392203</v>
+        <v>7392008</v>
       </c>
       <c r="S296" t="n">
         <v>10</v>
@@ -30785,10 +30785,10 @@
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>120434872</v>
+        <v>120434832</v>
       </c>
       <c r="B297" t="n">
-        <v>91858</v>
+        <v>91901</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
@@ -30797,25 +30797,25 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E297" t="n">
-        <v>4364</v>
+        <v>5448</v>
       </c>
       <c r="F297" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G297" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I297" t="inlineStr"/>
@@ -30825,10 +30825,10 @@
         </is>
       </c>
       <c r="Q297" t="n">
-        <v>811073</v>
+        <v>811072</v>
       </c>
       <c r="R297" t="n">
-        <v>7391995</v>
+        <v>7392186</v>
       </c>
       <c r="S297" t="n">
         <v>10</v>
@@ -30887,10 +30887,10 @@
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>120434854</v>
+        <v>120434850</v>
       </c>
       <c r="B298" t="n">
-        <v>78278</v>
+        <v>88170</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
@@ -30903,21 +30903,21 @@
         </is>
       </c>
       <c r="E298" t="n">
-        <v>6446</v>
+        <v>4962</v>
       </c>
       <c r="F298" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G298" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I298" t="inlineStr"/>
@@ -30927,10 +30927,10 @@
         </is>
       </c>
       <c r="Q298" t="n">
-        <v>811151</v>
+        <v>811200</v>
       </c>
       <c r="R298" t="n">
-        <v>7392024</v>
+        <v>7392176</v>
       </c>
       <c r="S298" t="n">
         <v>10</v>

--- a/artfynd/A 10151-2023 artfynd.xlsx
+++ b/artfynd/A 10151-2023 artfynd.xlsx
@@ -24459,10 +24459,10 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>120434830</v>
+        <v>120434817</v>
       </c>
       <c r="B235" t="n">
-        <v>91902</v>
+        <v>79160</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
@@ -24475,21 +24475,21 @@
         </is>
       </c>
       <c r="E235" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
@@ -24499,10 +24499,10 @@
         </is>
       </c>
       <c r="Q235" t="n">
-        <v>811019</v>
+        <v>811018</v>
       </c>
       <c r="R235" t="n">
-        <v>7392096</v>
+        <v>7392105</v>
       </c>
       <c r="S235" t="n">
         <v>10</v>
@@ -24663,10 +24663,10 @@
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>120434817</v>
+        <v>120434830</v>
       </c>
       <c r="B237" t="n">
-        <v>79160</v>
+        <v>91902</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
@@ -24679,21 +24679,21 @@
         </is>
       </c>
       <c r="E237" t="n">
-        <v>6453</v>
+        <v>5449</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
@@ -24703,10 +24703,10 @@
         </is>
       </c>
       <c r="Q237" t="n">
-        <v>811018</v>
+        <v>811019</v>
       </c>
       <c r="R237" t="n">
-        <v>7392105</v>
+        <v>7392096</v>
       </c>
       <c r="S237" t="n">
         <v>10</v>
@@ -25888,10 +25888,10 @@
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>120434898</v>
+        <v>120434855</v>
       </c>
       <c r="B249" t="n">
-        <v>91852</v>
+        <v>78278</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
@@ -25904,21 +25904,21 @@
         </is>
       </c>
       <c r="E249" t="n">
-        <v>4362</v>
+        <v>6446</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G249" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I249" t="inlineStr"/>
@@ -25928,10 +25928,10 @@
         </is>
       </c>
       <c r="Q249" t="n">
-        <v>811095</v>
+        <v>811078</v>
       </c>
       <c r="R249" t="n">
-        <v>7392048</v>
+        <v>7392236</v>
       </c>
       <c r="S249" t="n">
         <v>10</v>
@@ -25990,10 +25990,10 @@
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>120434865</v>
+        <v>120434898</v>
       </c>
       <c r="B250" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
@@ -26002,25 +26002,25 @@
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E250" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I250" t="inlineStr"/>
@@ -26030,10 +26030,10 @@
         </is>
       </c>
       <c r="Q250" t="n">
-        <v>810887</v>
+        <v>811095</v>
       </c>
       <c r="R250" t="n">
-        <v>7392183</v>
+        <v>7392048</v>
       </c>
       <c r="S250" t="n">
         <v>10</v>
@@ -26092,7 +26092,7 @@
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>120434886</v>
+        <v>120434865</v>
       </c>
       <c r="B251" t="n">
         <v>91858</v>
@@ -26132,10 +26132,10 @@
         </is>
       </c>
       <c r="Q251" t="n">
-        <v>811121</v>
+        <v>810887</v>
       </c>
       <c r="R251" t="n">
-        <v>7392171</v>
+        <v>7392183</v>
       </c>
       <c r="S251" t="n">
         <v>10</v>
@@ -26194,10 +26194,10 @@
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>120434855</v>
+        <v>120434886</v>
       </c>
       <c r="B252" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
@@ -26206,25 +26206,25 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E252" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G252" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I252" t="inlineStr"/>
@@ -26234,10 +26234,10 @@
         </is>
       </c>
       <c r="Q252" t="n">
-        <v>811078</v>
+        <v>811121</v>
       </c>
       <c r="R252" t="n">
-        <v>7392236</v>
+        <v>7392171</v>
       </c>
       <c r="S252" t="n">
         <v>10</v>
@@ -26807,10 +26807,10 @@
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>120434893</v>
+        <v>120434851</v>
       </c>
       <c r="B258" t="n">
-        <v>91858</v>
+        <v>88170</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
@@ -26819,25 +26819,25 @@
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E258" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G258" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I258" t="inlineStr"/>
@@ -26847,10 +26847,10 @@
         </is>
       </c>
       <c r="Q258" t="n">
-        <v>811088</v>
+        <v>811087</v>
       </c>
       <c r="R258" t="n">
-        <v>7392240</v>
+        <v>7392152</v>
       </c>
       <c r="S258" t="n">
         <v>10</v>
@@ -26909,10 +26909,10 @@
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>120434851</v>
+        <v>120434893</v>
       </c>
       <c r="B259" t="n">
-        <v>88170</v>
+        <v>91858</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
@@ -26921,25 +26921,25 @@
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E259" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I259" t="inlineStr"/>
@@ -26949,10 +26949,10 @@
         </is>
       </c>
       <c r="Q259" t="n">
-        <v>811087</v>
+        <v>811088</v>
       </c>
       <c r="R259" t="n">
-        <v>7392152</v>
+        <v>7392240</v>
       </c>
       <c r="S259" t="n">
         <v>10</v>
@@ -27623,10 +27623,10 @@
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>120434887</v>
+        <v>120434849</v>
       </c>
       <c r="B266" t="n">
-        <v>91858</v>
+        <v>88170</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
@@ -27635,25 +27635,25 @@
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E266" t="n">
-        <v>4364</v>
+        <v>4962</v>
       </c>
       <c r="F266" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mjölsvärting</t>
         </is>
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lyophyllum semitale</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr. : Fr.) Kühner</t>
         </is>
       </c>
       <c r="I266" t="inlineStr"/>
@@ -27663,10 +27663,10 @@
         </is>
       </c>
       <c r="Q266" t="n">
-        <v>811128</v>
+        <v>811223</v>
       </c>
       <c r="R266" t="n">
-        <v>7392175</v>
+        <v>7392167</v>
       </c>
       <c r="S266" t="n">
         <v>10</v>
@@ -27725,7 +27725,7 @@
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>120434864</v>
+        <v>120434887</v>
       </c>
       <c r="B267" t="n">
         <v>91858</v>
@@ -27765,10 +27765,10 @@
         </is>
       </c>
       <c r="Q267" t="n">
-        <v>810914</v>
+        <v>811128</v>
       </c>
       <c r="R267" t="n">
-        <v>7392166</v>
+        <v>7392175</v>
       </c>
       <c r="S267" t="n">
         <v>10</v>
@@ -27827,10 +27827,10 @@
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>120434849</v>
+        <v>120434864</v>
       </c>
       <c r="B268" t="n">
-        <v>88170</v>
+        <v>91858</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
@@ -27839,25 +27839,25 @@
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E268" t="n">
-        <v>4962</v>
+        <v>4364</v>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Mjölsvärting</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G268" t="inlineStr">
         <is>
-          <t>Lyophyllum semitale</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>(Fr. : Fr.) Kühner</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I268" t="inlineStr"/>
@@ -27867,10 +27867,10 @@
         </is>
       </c>
       <c r="Q268" t="n">
-        <v>811223</v>
+        <v>810914</v>
       </c>
       <c r="R268" t="n">
-        <v>7392167</v>
+        <v>7392166</v>
       </c>
       <c r="S268" t="n">
         <v>10</v>
@@ -27929,10 +27929,10 @@
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>120434853</v>
+        <v>120434868</v>
       </c>
       <c r="B269" t="n">
-        <v>78278</v>
+        <v>91858</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
@@ -27941,25 +27941,25 @@
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E269" t="n">
-        <v>6446</v>
+        <v>4364</v>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G269" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I269" t="inlineStr"/>
@@ -27969,10 +27969,10 @@
         </is>
       </c>
       <c r="Q269" t="n">
-        <v>811148</v>
+        <v>811010</v>
       </c>
       <c r="R269" t="n">
-        <v>7391971</v>
+        <v>7392090</v>
       </c>
       <c r="S269" t="n">
         <v>10</v>
@@ -28031,7 +28031,7 @@
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>120434868</v>
+        <v>120434884</v>
       </c>
       <c r="B270" t="n">
         <v>91858</v>
@@ -28071,10 +28071,10 @@
         </is>
       </c>
       <c r="Q270" t="n">
-        <v>811010</v>
+        <v>811098</v>
       </c>
       <c r="R270" t="n">
-        <v>7392090</v>
+        <v>7392240</v>
       </c>
       <c r="S270" t="n">
         <v>10</v>
@@ -28133,7 +28133,7 @@
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>120434884</v>
+        <v>120434875</v>
       </c>
       <c r="B271" t="n">
         <v>91858</v>
@@ -28173,10 +28173,10 @@
         </is>
       </c>
       <c r="Q271" t="n">
-        <v>811098</v>
+        <v>811108</v>
       </c>
       <c r="R271" t="n">
-        <v>7392240</v>
+        <v>7392073</v>
       </c>
       <c r="S271" t="n">
         <v>10</v>
@@ -28235,10 +28235,10 @@
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>120434875</v>
+        <v>120434853</v>
       </c>
       <c r="B272" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
@@ -28247,25 +28247,25 @@
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E272" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G272" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I272" t="inlineStr"/>
@@ -28275,10 +28275,10 @@
         </is>
       </c>
       <c r="Q272" t="n">
-        <v>811108</v>
+        <v>811148</v>
       </c>
       <c r="R272" t="n">
-        <v>7392073</v>
+        <v>7391971</v>
       </c>
       <c r="S272" t="n">
         <v>10</v>

--- a/artfynd/A 10151-2023 artfynd.xlsx
+++ b/artfynd/A 10151-2023 artfynd.xlsx
@@ -25788,7 +25788,7 @@
         <v>120434829</v>
       </c>
       <c r="B248" t="n">
-        <v>92030</v>
+        <v>92044</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>120434828</v>
       </c>
       <c r="B255" t="n">
-        <v>92030</v>
+        <v>92044</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>121791928</v>
       </c>
       <c r="B299" t="n">
-        <v>78261</v>
+        <v>78274</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>

--- a/artfynd/A 10151-2023 artfynd.xlsx
+++ b/artfynd/A 10151-2023 artfynd.xlsx
@@ -25788,7 +25788,7 @@
         <v>120434829</v>
       </c>
       <c r="B248" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
@@ -26506,7 +26506,7 @@
         <v>120434828</v>
       </c>
       <c r="B255" t="n">
-        <v>92044</v>
+        <v>92046</v>
       </c>
       <c r="C255" t="inlineStr">
         <is>
@@ -30998,7 +30998,7 @@
         <v>121791928</v>
       </c>
       <c r="B299" t="n">
-        <v>78274</v>
+        <v>78276</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>

--- a/artfynd/A 10151-2023 artfynd.xlsx
+++ b/artfynd/A 10151-2023 artfynd.xlsx
@@ -31109,7 +31109,7 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>122758250</v>
+        <v>122761645</v>
       </c>
       <c r="B300" t="n">
         <v>56688</v>
@@ -31183,12 +31183,12 @@
       </c>
       <c r="Y300" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-08-15</t>
         </is>
       </c>
       <c r="AD300" t="b">

--- a/artfynd/A 10151-2023 artfynd.xlsx
+++ b/artfynd/A 10151-2023 artfynd.xlsx
@@ -31109,7 +31109,7 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>122761645</v>
+        <v>122761510</v>
       </c>
       <c r="B300" t="n">
         <v>56688</v>
@@ -31183,12 +31183,12 @@
       </c>
       <c r="Y300" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
         <is>
-          <t>2024-08-15</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD300" t="b">

--- a/artfynd/A 10151-2023 artfynd.xlsx
+++ b/artfynd/A 10151-2023 artfynd.xlsx
@@ -31109,7 +31109,7 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>122761510</v>
+        <v>122758250</v>
       </c>
       <c r="B300" t="n">
         <v>56688</v>
@@ -31183,12 +31183,12 @@
       </c>
       <c r="Y300" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="AD300" t="b">

--- a/artfynd/A 10151-2023 artfynd.xlsx
+++ b/artfynd/A 10151-2023 artfynd.xlsx
@@ -31109,7 +31109,7 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>122758250</v>
+        <v>122761510</v>
       </c>
       <c r="B300" t="n">
         <v>56688</v>
@@ -31183,12 +31183,12 @@
       </c>
       <c r="Y300" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD300" t="b">

--- a/artfynd/A 10151-2023 artfynd.xlsx
+++ b/artfynd/A 10151-2023 artfynd.xlsx
@@ -19555,7 +19555,7 @@
         <v>119541080</v>
       </c>
       <c r="B187" t="n">
-        <v>56691</v>
+        <v>56694</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
@@ -31109,10 +31109,10 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>122758250</v>
+        <v>122761510</v>
       </c>
       <c r="B300" t="n">
-        <v>56688</v>
+        <v>56691</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
@@ -31183,12 +31183,12 @@
       </c>
       <c r="Y300" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD300" t="b">

--- a/artfynd/A 10151-2023 artfynd.xlsx
+++ b/artfynd/A 10151-2023 artfynd.xlsx
@@ -31109,7 +31109,7 @@
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>122761510</v>
+        <v>122758250</v>
       </c>
       <c r="B300" t="n">
         <v>56691</v>
@@ -31183,12 +31183,12 @@
       </c>
       <c r="Y300" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="AA300" t="inlineStr">
         <is>
-          <t>2024-08-07</t>
+          <t>2024-06-19</t>
         </is>
       </c>
       <c r="AD300" t="b">
